--- a/Design-Files/Tracker-pro-airbnb-v1.1/BOM/Altium_BOM_tracker-pro-airbnb-v1.1.xlsx
+++ b/Design-Files/Tracker-pro-airbnb-v1.1/BOM/Altium_BOM_tracker-pro-airbnb-v1.1.xlsx
@@ -1,41 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hunain\OneDrive\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView windowWidth="28800" windowHeight="12330"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="645">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="645">
   <si>
     <t>#</t>
   </si>
@@ -1037,6 +1016,9 @@
     <t>Rohm</t>
   </si>
   <si>
+    <t>Resistor</t>
+  </si>
+  <si>
     <t>R1, R21, R22, R70</t>
   </si>
   <si>
@@ -1050,9 +1032,6 @@
   </si>
   <si>
     <t>1M</t>
-  </si>
-  <si>
-    <t>Resistor</t>
   </si>
   <si>
     <t>R2, R3</t>
@@ -1976,48 +1955,76 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="13"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color theme="0"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2025,18 +2032,147 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2055,8 +2191,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -2068,9 +2390,48 @@
       <left/>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2078,7 +2439,22 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2086,101 +2462,10 @@
       <left/>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2195,7 +2480,20 @@
         <color rgb="FF000000"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2208,7 +2506,18 @@
       </right>
       <top/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2220,10 +2529,23 @@
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2238,40 +2560,279 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2280,67 +2841,110 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FF03A4CB"/>
-      <color rgb="FF2CD0B2"/>
+      <color rgb="0003A4CB"/>
+      <color rgb="002CD0B2"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2389,7 +2993,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2424,7 +3028,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2598,50 +3202,43 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:L144"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="4.42578125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.42857142857143" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.7142857142857" style="1" customWidth="1"/>
+    <col min="4" max="4" width="36" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.85546875" customWidth="1"/>
-    <col min="11" max="11" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.42578125" customWidth="1"/>
+    <col min="6" max="6" width="26.5714285714286" customWidth="1"/>
+    <col min="7" max="7" width="33.4285714285714" customWidth="1"/>
+    <col min="8" max="8" width="21.4285714285714" customWidth="1"/>
+    <col min="9" max="10" width="17.8571428571429" customWidth="1"/>
+    <col min="11" max="11" width="16.7142857142857" customWidth="1"/>
+    <col min="12" max="12" width="29.4285714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+    <row r="1" ht="15.75" spans="1:12">
+      <c r="A1" s="2"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+    </row>
+    <row r="2" ht="15.75" spans="1:12">
+      <c r="A2" s="2"/>
       <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
@@ -2666,4707 +3263,4712 @@
       <c r="I2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="J2" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="K2" s="16" t="s">
         <v>9</v>
       </c>
       <c r="L2" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="11">
-        <f>ROW(B3) - ROW($B$2)</f>
-        <v>1</v>
-      </c>
-      <c r="C3" s="12" t="s">
+    <row r="3" ht="24.75" spans="1:12">
+      <c r="A3" s="2"/>
+      <c r="B3" s="7">
+        <f>ROW(B3)-ROW($B$2)</f>
+        <v>1</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="21"/>
-      <c r="K3" s="17">
+      <c r="J3" s="17"/>
+      <c r="K3" s="18">
         <v>2</v>
       </c>
-      <c r="L3" s="7"/>
-    </row>
-    <row r="4" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="11">
-        <f t="shared" ref="B4:B143" si="0">ROW(B4) - ROW($B$2)</f>
+      <c r="L3" s="9"/>
+    </row>
+    <row r="4" ht="24.75" spans="1:12">
+      <c r="A4" s="2"/>
+      <c r="B4" s="7">
+        <f t="shared" ref="B4:B143" si="0">ROW(B4)-ROW($B$2)</f>
         <v>2</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="J4" s="22"/>
-      <c r="K4" s="18">
+      <c r="J4" s="19"/>
+      <c r="K4" s="20">
         <v>12</v>
       </c>
-      <c r="L4" s="9"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="11">
-        <f>ROW(B5) - ROW($B$2)</f>
+      <c r="L4" s="12"/>
+    </row>
+    <row r="5" ht="15.75" spans="1:12">
+      <c r="A5" s="2"/>
+      <c r="B5" s="7">
+        <f>ROW(B5)-ROW($B$2)</f>
         <v>3</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="21"/>
-      <c r="K5" s="17">
-        <v>1</v>
-      </c>
-      <c r="L5" s="7"/>
-    </row>
-    <row r="6" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="11">
+      <c r="J5" s="17"/>
+      <c r="K5" s="18">
+        <v>1</v>
+      </c>
+      <c r="L5" s="9"/>
+    </row>
+    <row r="6" ht="60.75" spans="1:12">
+      <c r="A6" s="2"/>
+      <c r="B6" s="7">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="I6" s="10" t="s">
+      <c r="I6" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="J6" s="22"/>
-      <c r="K6" s="18">
+      <c r="J6" s="19"/>
+      <c r="K6" s="20">
         <v>42</v>
       </c>
-      <c r="L6" s="9"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="11">
-        <f>ROW(B7) - ROW($B$2)</f>
+      <c r="L6" s="12"/>
+    </row>
+    <row r="7" ht="15.75" spans="1:12">
+      <c r="A7" s="2"/>
+      <c r="B7" s="7">
+        <f>ROW(B7)-ROW($B$2)</f>
         <v>5</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="21"/>
-      <c r="K7" s="17">
-        <v>1</v>
-      </c>
-      <c r="L7" s="7"/>
-    </row>
-    <row r="8" spans="1:12" ht="36" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="11">
+      <c r="J7" s="17"/>
+      <c r="K7" s="18">
+        <v>1</v>
+      </c>
+      <c r="L7" s="9"/>
+    </row>
+    <row r="8" ht="36.75" spans="1:12">
+      <c r="A8" s="2"/>
+      <c r="B8" s="7">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="J8" s="22"/>
-      <c r="K8" s="18">
+      <c r="J8" s="19"/>
+      <c r="K8" s="20">
         <v>2</v>
       </c>
-      <c r="L8" s="9"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-      <c r="B9" s="11">
-        <f>ROW(B9) - ROW($B$2)</f>
+      <c r="L8" s="12"/>
+    </row>
+    <row r="9" ht="15.75" spans="1:12">
+      <c r="A9" s="2"/>
+      <c r="B9" s="7">
+        <f>ROW(B9)-ROW($B$2)</f>
         <v>7</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="J9" s="21"/>
-      <c r="K9" s="17">
-        <v>1</v>
-      </c>
-      <c r="L9" s="7"/>
-    </row>
-    <row r="10" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="11">
+      <c r="J9" s="17"/>
+      <c r="K9" s="18">
+        <v>1</v>
+      </c>
+      <c r="L9" s="9"/>
+    </row>
+    <row r="10" ht="24.75" spans="1:12">
+      <c r="A10" s="2"/>
+      <c r="B10" s="7">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I10" s="10" t="s">
+      <c r="I10" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="J10" s="22"/>
-      <c r="K10" s="18">
+      <c r="J10" s="19"/>
+      <c r="K10" s="20">
         <v>17</v>
       </c>
-      <c r="L10" s="9"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="11">
-        <f>ROW(B11) - ROW($B$2)</f>
+      <c r="L10" s="12"/>
+    </row>
+    <row r="11" ht="15.75" spans="1:12">
+      <c r="A11" s="2"/>
+      <c r="B11" s="7">
+        <f>ROW(B11)-ROW($B$2)</f>
         <v>9</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I11" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="J11" s="21"/>
-      <c r="K11" s="17">
-        <v>1</v>
-      </c>
-      <c r="L11" s="7"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="11">
+      <c r="J11" s="17"/>
+      <c r="K11" s="18">
+        <v>1</v>
+      </c>
+      <c r="L11" s="9"/>
+    </row>
+    <row r="12" ht="15.75" spans="1:12">
+      <c r="A12" s="2"/>
+      <c r="B12" s="7">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I12" s="10" t="s">
+      <c r="I12" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="J12" s="22"/>
-      <c r="K12" s="18">
+      <c r="J12" s="19"/>
+      <c r="K12" s="20">
         <v>3</v>
       </c>
-      <c r="L12" s="9"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="11">
-        <f>ROW(B13) - ROW($B$2)</f>
+      <c r="L12" s="12"/>
+    </row>
+    <row r="13" ht="15.75" spans="1:12">
+      <c r="A13" s="2"/>
+      <c r="B13" s="7">
+        <f>ROW(B13)-ROW($B$2)</f>
         <v>11</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="G13" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I13" s="8" t="s">
+      <c r="I13" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="J13" s="21"/>
-      <c r="K13" s="17">
+      <c r="J13" s="17"/>
+      <c r="K13" s="18">
         <v>2</v>
       </c>
-      <c r="L13" s="7"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="11">
+      <c r="L13" s="9"/>
+    </row>
+    <row r="14" ht="15.75" spans="1:12">
+      <c r="A14" s="2"/>
+      <c r="B14" s="7">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="G14" s="10" t="s">
+      <c r="G14" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H14" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I14" s="10" t="s">
+      <c r="I14" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="J14" s="22"/>
-      <c r="K14" s="18">
+      <c r="J14" s="19"/>
+      <c r="K14" s="20">
         <v>2</v>
       </c>
-      <c r="L14" s="9"/>
-    </row>
-    <row r="15" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="11">
-        <f>ROW(B15) - ROW($B$2)</f>
+      <c r="L14" s="12"/>
+    </row>
+    <row r="15" ht="24.75" spans="1:12">
+      <c r="A15" s="2"/>
+      <c r="B15" s="7">
+        <f>ROW(B15)-ROW($B$2)</f>
         <v>13</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="H15" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="I15" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="J15" s="21"/>
-      <c r="K15" s="17">
-        <v>1</v>
-      </c>
-      <c r="L15" s="7"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="11">
+      <c r="J15" s="17"/>
+      <c r="K15" s="18">
+        <v>1</v>
+      </c>
+      <c r="L15" s="9"/>
+    </row>
+    <row r="16" ht="15.75" spans="1:12">
+      <c r="A16" s="2"/>
+      <c r="B16" s="7">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="G16" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="H16" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I16" s="10" t="s">
+      <c r="I16" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="J16" s="22"/>
-      <c r="K16" s="18">
-        <v>1</v>
-      </c>
-      <c r="L16" s="9"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="11">
-        <f>ROW(B17) - ROW($B$2)</f>
+      <c r="J16" s="19"/>
+      <c r="K16" s="20">
+        <v>1</v>
+      </c>
+      <c r="L16" s="12"/>
+    </row>
+    <row r="17" ht="15.75" spans="1:12">
+      <c r="A17" s="2"/>
+      <c r="B17" s="7">
+        <f>ROW(B17)-ROW($B$2)</f>
         <v>15</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="G17" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="H17" s="7" t="s">
+      <c r="H17" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="I17" s="8" t="s">
+      <c r="I17" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="J17" s="21"/>
-      <c r="K17" s="17">
+      <c r="J17" s="17"/>
+      <c r="K17" s="18">
         <v>2</v>
       </c>
-      <c r="L17" s="7"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="11">
+      <c r="L17" s="9"/>
+    </row>
+    <row r="18" ht="15.75" spans="1:12">
+      <c r="A18" s="2"/>
+      <c r="B18" s="7">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="G18" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="H18" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I18" s="10" t="s">
+      <c r="I18" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="J18" s="22"/>
-      <c r="K18" s="18">
+      <c r="J18" s="19"/>
+      <c r="K18" s="20">
         <v>3</v>
       </c>
-      <c r="L18" s="9"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="11">
-        <f>ROW(B19) - ROW($B$2)</f>
+      <c r="L18" s="12"/>
+    </row>
+    <row r="19" ht="15.75" spans="1:12">
+      <c r="A19" s="2"/>
+      <c r="B19" s="7">
+        <f>ROW(B19)-ROW($B$2)</f>
         <v>17</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="G19" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="H19" s="7" t="s">
+      <c r="H19" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I19" s="8" t="s">
+      <c r="I19" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="J19" s="21"/>
-      <c r="K19" s="17">
-        <v>1</v>
-      </c>
-      <c r="L19" s="7"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-      <c r="B20" s="11">
+      <c r="J19" s="17"/>
+      <c r="K19" s="18">
+        <v>1</v>
+      </c>
+      <c r="L19" s="9"/>
+    </row>
+    <row r="20" ht="15.75" spans="1:12">
+      <c r="A20" s="2"/>
+      <c r="B20" s="7">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="G20" s="10" t="s">
+      <c r="G20" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="H20" s="9" t="s">
+      <c r="H20" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I20" s="10" t="s">
+      <c r="I20" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="J20" s="22"/>
-      <c r="K20" s="18">
+      <c r="J20" s="19"/>
+      <c r="K20" s="20">
         <v>2</v>
       </c>
-      <c r="L20" s="9"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="11">
-        <f>ROW(B21) - ROW($B$2)</f>
+      <c r="L20" s="12"/>
+    </row>
+    <row r="21" ht="15.75" spans="1:12">
+      <c r="A21" s="2"/>
+      <c r="B21" s="7">
+        <f>ROW(B21)-ROW($B$2)</f>
         <v>19</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E21" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="G21" s="8" t="s">
+      <c r="G21" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="H21" s="7" t="s">
+      <c r="H21" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I21" s="8" t="s">
+      <c r="I21" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="J21" s="21"/>
-      <c r="K21" s="17">
-        <v>1</v>
-      </c>
-      <c r="L21" s="7"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="11">
+      <c r="J21" s="17"/>
+      <c r="K21" s="18">
+        <v>1</v>
+      </c>
+      <c r="L21" s="9"/>
+    </row>
+    <row r="22" ht="15.75" spans="1:12">
+      <c r="A22" s="2"/>
+      <c r="B22" s="7">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E22" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="F22" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="G22" s="10" t="s">
+      <c r="G22" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="H22" s="9" t="s">
+      <c r="H22" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="I22" s="10" t="s">
+      <c r="I22" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="J22" s="22"/>
-      <c r="K22" s="18">
+      <c r="J22" s="19"/>
+      <c r="K22" s="20">
         <v>2</v>
       </c>
-      <c r="L22" s="9"/>
-    </row>
-    <row r="23" spans="1:12" ht="36" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
-      <c r="B23" s="11">
-        <f>ROW(B23) - ROW($B$2)</f>
+      <c r="L22" s="12"/>
+    </row>
+    <row r="23" ht="36.75" spans="1:12">
+      <c r="A23" s="2"/>
+      <c r="B23" s="7">
+        <f>ROW(B23)-ROW($B$2)</f>
         <v>21</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="E23" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="G23" s="8" t="s">
+      <c r="G23" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="H23" s="7" t="s">
+      <c r="H23" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="I23" s="8" t="s">
+      <c r="I23" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="J23" s="21"/>
-      <c r="K23" s="17">
-        <v>1</v>
-      </c>
-      <c r="L23" s="7"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
-      <c r="B24" s="11">
+      <c r="J23" s="17"/>
+      <c r="K23" s="18">
+        <v>1</v>
+      </c>
+      <c r="L23" s="9"/>
+    </row>
+    <row r="24" ht="15.75" spans="1:12">
+      <c r="A24" s="2"/>
+      <c r="B24" s="7">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="D24" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="E24" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F24" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="G24" s="10" t="s">
+      <c r="G24" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="H24" s="9" t="s">
+      <c r="H24" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I24" s="10" t="s">
+      <c r="I24" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="J24" s="22"/>
-      <c r="K24" s="18">
+      <c r="J24" s="19"/>
+      <c r="K24" s="20">
         <v>2</v>
       </c>
-      <c r="L24" s="9"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="11">
-        <f>ROW(B25) - ROW($B$2)</f>
+      <c r="L24" s="12"/>
+    </row>
+    <row r="25" ht="15.75" spans="1:12">
+      <c r="A25" s="2"/>
+      <c r="B25" s="7">
+        <f>ROW(B25)-ROW($B$2)</f>
         <v>23</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E25" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="G25" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="H25" s="7" t="s">
+      <c r="H25" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I25" s="8" t="s">
+      <c r="I25" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="J25" s="21"/>
-      <c r="K25" s="17">
+      <c r="J25" s="17"/>
+      <c r="K25" s="18">
         <v>2</v>
       </c>
-      <c r="L25" s="7"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
-      <c r="B26" s="11">
+      <c r="L25" s="9"/>
+    </row>
+    <row r="26" ht="15.75" spans="1:12">
+      <c r="A26" s="2"/>
+      <c r="B26" s="7">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="D26" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E26" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="F26" s="9" t="s">
+      <c r="F26" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="G26" s="10" t="s">
+      <c r="G26" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="H26" s="9" t="s">
+      <c r="H26" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I26" s="10" t="s">
+      <c r="I26" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="J26" s="22"/>
-      <c r="K26" s="18">
+      <c r="J26" s="19"/>
+      <c r="K26" s="20">
         <v>3</v>
       </c>
-      <c r="L26" s="9"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="1"/>
-      <c r="B27" s="11">
-        <f>ROW(B27) - ROW($B$2)</f>
+      <c r="L26" s="12"/>
+    </row>
+    <row r="27" ht="15.75" spans="1:12">
+      <c r="A27" s="2"/>
+      <c r="B27" s="7">
+        <f>ROW(B27)-ROW($B$2)</f>
         <v>25</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="G27" s="8" t="s">
+      <c r="G27" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="H27" s="7" t="s">
+      <c r="H27" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I27" s="8" t="s">
+      <c r="I27" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="J27" s="21"/>
-      <c r="K27" s="17">
-        <v>1</v>
-      </c>
-      <c r="L27" s="7"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="1"/>
-      <c r="B28" s="11">
+      <c r="J27" s="17"/>
+      <c r="K27" s="18">
+        <v>1</v>
+      </c>
+      <c r="L27" s="9"/>
+    </row>
+    <row r="28" ht="15.75" spans="1:12">
+      <c r="A28" s="2"/>
+      <c r="B28" s="7">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="F28" s="9" t="s">
+      <c r="F28" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="G28" s="10" t="s">
+      <c r="G28" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="H28" s="9" t="s">
+      <c r="H28" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I28" s="10" t="s">
+      <c r="I28" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="J28" s="22"/>
-      <c r="K28" s="18">
-        <v>1</v>
-      </c>
-      <c r="L28" s="9"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="1"/>
-      <c r="B29" s="11">
-        <f>ROW(B29) - ROW($B$2)</f>
+      <c r="J28" s="19"/>
+      <c r="K28" s="20">
+        <v>1</v>
+      </c>
+      <c r="L28" s="12"/>
+    </row>
+    <row r="29" ht="15.75" spans="1:12">
+      <c r="A29" s="2"/>
+      <c r="B29" s="7">
+        <f>ROW(B29)-ROW($B$2)</f>
         <v>27</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="E29" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="G29" s="8" t="s">
+      <c r="G29" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="H29" s="7" t="s">
+      <c r="H29" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="8" t="s">
+      <c r="I29" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="J29" s="21"/>
-      <c r="K29" s="17">
+      <c r="J29" s="17"/>
+      <c r="K29" s="18">
         <v>4</v>
       </c>
-      <c r="L29" s="7"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="1"/>
-      <c r="B30" s="11">
+      <c r="L29" s="9"/>
+    </row>
+    <row r="30" ht="15.75" spans="1:12">
+      <c r="A30" s="2"/>
+      <c r="B30" s="7">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="D30" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="E30" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="F30" s="9" t="s">
+      <c r="F30" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G30" s="10" t="s">
+      <c r="G30" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="H30" s="9" t="s">
+      <c r="H30" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="10" t="s">
+      <c r="I30" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="J30" s="22"/>
-      <c r="K30" s="18">
-        <v>1</v>
-      </c>
-      <c r="L30" s="9"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="1"/>
-      <c r="B31" s="11">
-        <f>ROW(B31) - ROW($B$2)</f>
+      <c r="J30" s="19"/>
+      <c r="K30" s="20">
+        <v>1</v>
+      </c>
+      <c r="L30" s="12"/>
+    </row>
+    <row r="31" ht="15.75" spans="1:12">
+      <c r="A31" s="2"/>
+      <c r="B31" s="7">
+        <f>ROW(B31)-ROW($B$2)</f>
         <v>29</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="C31" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="E31" s="8" t="s">
+      <c r="E31" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="G31" s="8" t="s">
+      <c r="G31" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="H31" s="7" t="s">
+      <c r="H31" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="I31" s="8" t="s">
+      <c r="I31" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="J31" s="21"/>
-      <c r="K31" s="17">
-        <v>1</v>
-      </c>
-      <c r="L31" s="7"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
-      <c r="B32" s="11">
+      <c r="J31" s="17"/>
+      <c r="K31" s="18">
+        <v>1</v>
+      </c>
+      <c r="L31" s="9"/>
+    </row>
+    <row r="32" ht="15.75" spans="1:12">
+      <c r="A32" s="2"/>
+      <c r="B32" s="7">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D32" s="9" t="s">
+      <c r="D32" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="E32" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="F32" s="9" t="s">
+      <c r="F32" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G32" s="10" t="s">
+      <c r="G32" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="H32" s="9" t="s">
+      <c r="H32" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="I32" s="10" t="s">
+      <c r="I32" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="J32" s="22"/>
-      <c r="K32" s="18">
-        <v>1</v>
-      </c>
-      <c r="L32" s="9"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="1"/>
-      <c r="B33" s="11">
-        <f>ROW(B33) - ROW($B$2)</f>
+      <c r="J32" s="19"/>
+      <c r="K32" s="20">
+        <v>1</v>
+      </c>
+      <c r="L32" s="12"/>
+    </row>
+    <row r="33" ht="15.75" spans="1:12">
+      <c r="A33" s="2"/>
+      <c r="B33" s="7">
+        <f>ROW(B33)-ROW($B$2)</f>
         <v>31</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="E33" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F33" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="G33" s="8" t="s">
+      <c r="G33" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="H33" s="7" t="s">
+      <c r="H33" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="I33" s="8" t="s">
+      <c r="I33" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="J33" s="21"/>
-      <c r="K33" s="17">
+      <c r="J33" s="17"/>
+      <c r="K33" s="18">
         <v>4</v>
       </c>
-      <c r="L33" s="7"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="1"/>
-      <c r="B34" s="11">
+      <c r="L33" s="9"/>
+    </row>
+    <row r="34" ht="15.75" spans="1:12">
+      <c r="A34" s="2"/>
+      <c r="B34" s="7">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D34" s="9" t="s">
+      <c r="D34" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="E34" s="10" t="s">
+      <c r="E34" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="F34" s="9" t="s">
+      <c r="F34" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="G34" s="10" t="s">
+      <c r="G34" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="H34" s="9" t="s">
+      <c r="H34" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I34" s="10" t="s">
+      <c r="I34" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="J34" s="22"/>
-      <c r="K34" s="18">
-        <v>1</v>
-      </c>
-      <c r="L34" s="9"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="1"/>
-      <c r="B35" s="11">
-        <f>ROW(B35) - ROW($B$2)</f>
+      <c r="J34" s="19"/>
+      <c r="K34" s="20">
+        <v>1</v>
+      </c>
+      <c r="L34" s="12"/>
+    </row>
+    <row r="35" ht="15.75" spans="1:12">
+      <c r="A35" s="2"/>
+      <c r="B35" s="7">
+        <f>ROW(B35)-ROW($B$2)</f>
         <v>33</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D35" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="E35" s="8" t="s">
+      <c r="E35" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="F35" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="G35" s="8" t="s">
+      <c r="G35" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="H35" s="7" t="s">
+      <c r="H35" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I35" s="8" t="s">
+      <c r="I35" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="J35" s="21"/>
-      <c r="K35" s="17">
-        <v>1</v>
-      </c>
-      <c r="L35" s="7"/>
-    </row>
-    <row r="36" spans="1:12" ht="36" x14ac:dyDescent="0.25">
-      <c r="A36" s="1"/>
-      <c r="B36" s="11">
+      <c r="J35" s="17"/>
+      <c r="K35" s="18">
+        <v>1</v>
+      </c>
+      <c r="L35" s="9"/>
+    </row>
+    <row r="36" ht="36.75" spans="1:12">
+      <c r="A36" s="2"/>
+      <c r="B36" s="7">
         <v>34</v>
       </c>
-      <c r="C36" s="12" t="s">
+      <c r="C36" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="D36" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="E36" s="8" t="s">
+      <c r="E36" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="F36" s="7" t="s">
+      <c r="F36" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="G36" s="8" t="s">
+      <c r="G36" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="H36" s="7" t="s">
+      <c r="H36" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="I36" s="8" t="s">
+      <c r="I36" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="J36" s="21"/>
-      <c r="K36" s="17">
-        <v>1</v>
-      </c>
-      <c r="L36" s="7"/>
-    </row>
-    <row r="37" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A37" s="1"/>
-      <c r="B37" s="11">
+      <c r="J36" s="17"/>
+      <c r="K36" s="18">
+        <v>1</v>
+      </c>
+      <c r="L36" s="9"/>
+    </row>
+    <row r="37" ht="24.75" spans="1:12">
+      <c r="A37" s="2"/>
+      <c r="B37" s="7">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="C37" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="D37" s="9" t="s">
+      <c r="D37" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="E37" s="10" t="s">
+      <c r="E37" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="F37" s="9" t="s">
+      <c r="F37" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="G37" s="10" t="s">
+      <c r="G37" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="H37" s="9" t="s">
+      <c r="H37" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="I37" s="10" t="s">
+      <c r="I37" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="J37" s="22"/>
-      <c r="K37" s="18">
-        <v>1</v>
-      </c>
-      <c r="L37" s="9"/>
-    </row>
-    <row r="38" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A38" s="1"/>
-      <c r="B38" s="11">
-        <f>ROW(B38) - ROW($B$2)</f>
+      <c r="J37" s="19"/>
+      <c r="K37" s="20">
+        <v>1</v>
+      </c>
+      <c r="L37" s="12"/>
+    </row>
+    <row r="38" ht="24.75" spans="1:12">
+      <c r="A38" s="2"/>
+      <c r="B38" s="7">
+        <f>ROW(B38)-ROW($B$2)</f>
         <v>36</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="D38" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="E38" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="F38" s="7" t="s">
+      <c r="F38" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="G38" s="8" t="s">
+      <c r="G38" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="H38" s="7" t="s">
+      <c r="H38" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="I38" s="8" t="s">
+      <c r="I38" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="J38" s="21"/>
-      <c r="K38" s="17">
-        <v>1</v>
-      </c>
-      <c r="L38" s="7"/>
-    </row>
-    <row r="39" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A39" s="1"/>
-      <c r="B39" s="11">
+      <c r="J38" s="17"/>
+      <c r="K38" s="18">
+        <v>1</v>
+      </c>
+      <c r="L38" s="9"/>
+    </row>
+    <row r="39" ht="24.75" spans="1:12">
+      <c r="A39" s="2"/>
+      <c r="B39" s="7">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="C39" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="D39" s="9" t="s">
+      <c r="D39" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="E39" s="10" t="s">
+      <c r="E39" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="F39" s="9" t="s">
+      <c r="F39" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="G39" s="10" t="s">
+      <c r="G39" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="H39" s="9" t="s">
+      <c r="H39" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="I39" s="10" t="s">
+      <c r="I39" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="J39" s="22"/>
-      <c r="K39" s="18">
+      <c r="J39" s="19"/>
+      <c r="K39" s="20">
         <v>2</v>
       </c>
-      <c r="L39" s="9"/>
-    </row>
-    <row r="40" spans="1:12" ht="36" x14ac:dyDescent="0.25">
-      <c r="A40" s="1"/>
-      <c r="B40" s="11">
-        <f>ROW(B40) - ROW($B$2)</f>
+      <c r="L39" s="12"/>
+    </row>
+    <row r="40" ht="36.75" spans="1:12">
+      <c r="A40" s="2"/>
+      <c r="B40" s="7">
+        <f>ROW(B40)-ROW($B$2)</f>
         <v>38</v>
       </c>
-      <c r="C40" s="12" t="s">
+      <c r="C40" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="D40" s="7" t="s">
+      <c r="D40" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="E40" s="8" t="s">
+      <c r="E40" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="F40" s="7" t="s">
+      <c r="F40" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="G40" s="8" t="s">
+      <c r="G40" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="H40" s="7" t="s">
+      <c r="H40" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="I40" s="8" t="s">
+      <c r="I40" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="J40" s="21"/>
-      <c r="K40" s="17">
-        <v>1</v>
-      </c>
-      <c r="L40" s="7"/>
-    </row>
-    <row r="41" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A41" s="1"/>
-      <c r="B41" s="11">
+      <c r="J40" s="17"/>
+      <c r="K40" s="18">
+        <v>1</v>
+      </c>
+      <c r="L40" s="9"/>
+    </row>
+    <row r="41" ht="24.75" spans="1:12">
+      <c r="A41" s="2"/>
+      <c r="B41" s="7">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="C41" s="13" t="s">
+      <c r="C41" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="D41" s="9" t="s">
+      <c r="D41" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="E41" s="10" t="s">
+      <c r="E41" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="F41" s="9" t="s">
+      <c r="F41" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="G41" s="10" t="s">
+      <c r="G41" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="H41" s="9" t="s">
+      <c r="H41" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="I41" s="10" t="s">
+      <c r="I41" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="J41" s="22"/>
-      <c r="K41" s="18">
-        <v>1</v>
-      </c>
-      <c r="L41" s="9"/>
-    </row>
-    <row r="42" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A42" s="1"/>
-      <c r="B42" s="11">
-        <f>ROW(B42) - ROW($B$2)</f>
+      <c r="J41" s="19"/>
+      <c r="K41" s="20">
+        <v>1</v>
+      </c>
+      <c r="L41" s="12"/>
+    </row>
+    <row r="42" ht="24.75" spans="1:12">
+      <c r="A42" s="2"/>
+      <c r="B42" s="7">
+        <f>ROW(B42)-ROW($B$2)</f>
         <v>40</v>
       </c>
-      <c r="C42" s="12" t="s">
+      <c r="C42" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="D42" s="7" t="s">
+      <c r="D42" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="E42" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="F42" s="7" t="s">
+      <c r="F42" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="G42" s="8" t="s">
+      <c r="G42" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="H42" s="7" t="s">
+      <c r="H42" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="I42" s="8" t="s">
+      <c r="I42" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="J42" s="21"/>
-      <c r="K42" s="17">
-        <v>1</v>
-      </c>
-      <c r="L42" s="7"/>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" s="1"/>
-      <c r="B43" s="11">
+      <c r="J42" s="17"/>
+      <c r="K42" s="18">
+        <v>1</v>
+      </c>
+      <c r="L42" s="9"/>
+    </row>
+    <row r="43" ht="15.75" spans="1:12">
+      <c r="A43" s="2"/>
+      <c r="B43" s="7">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="D43" s="9" t="s">
+      <c r="D43" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="E43" s="10" t="s">
+      <c r="E43" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="F43" s="9" t="s">
+      <c r="F43" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="G43" s="10" t="s">
+      <c r="G43" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="H43" s="9" t="s">
+      <c r="H43" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="I43" s="10" t="s">
+      <c r="I43" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="J43" s="22"/>
-      <c r="K43" s="18">
-        <v>1</v>
-      </c>
-      <c r="L43" s="9"/>
-    </row>
-    <row r="44" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A44" s="1"/>
-      <c r="B44" s="11">
-        <f>ROW(B44) - ROW($B$2)</f>
+      <c r="J43" s="19"/>
+      <c r="K43" s="20">
+        <v>1</v>
+      </c>
+      <c r="L43" s="12"/>
+    </row>
+    <row r="44" ht="24.75" spans="1:12">
+      <c r="A44" s="2"/>
+      <c r="B44" s="7">
+        <f>ROW(B44)-ROW($B$2)</f>
         <v>42</v>
       </c>
-      <c r="C44" s="12" t="s">
+      <c r="C44" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="D44" s="7" t="s">
+      <c r="D44" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="E44" s="8" t="s">
+      <c r="E44" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="F44" s="7" t="s">
+      <c r="F44" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="G44" s="8" t="s">
+      <c r="G44" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="H44" s="7" t="s">
+      <c r="H44" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="I44" s="8" t="s">
+      <c r="I44" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="J44" s="21"/>
-      <c r="K44" s="17">
+      <c r="J44" s="17"/>
+      <c r="K44" s="18">
         <v>2</v>
       </c>
-      <c r="L44" s="7"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" s="1"/>
-      <c r="B45" s="11">
+      <c r="L44" s="9"/>
+    </row>
+    <row r="45" ht="15.75" spans="1:12">
+      <c r="A45" s="2"/>
+      <c r="B45" s="7">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="C45" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="D45" s="9" t="s">
+      <c r="D45" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="E45" s="10" t="s">
+      <c r="E45" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="F45" s="9" t="s">
+      <c r="F45" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="G45" s="10" t="s">
+      <c r="G45" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="H45" s="9" t="s">
+      <c r="H45" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="I45" s="10" t="s">
+      <c r="I45" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="J45" s="22"/>
-      <c r="K45" s="18">
+      <c r="J45" s="19"/>
+      <c r="K45" s="20">
         <v>5</v>
       </c>
-      <c r="L45" s="9"/>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="1"/>
-      <c r="B46" s="11">
-        <f>ROW(B46) - ROW($B$2)</f>
+      <c r="L45" s="12"/>
+    </row>
+    <row r="46" ht="15.75" spans="1:12">
+      <c r="A46" s="2"/>
+      <c r="B46" s="7">
+        <f>ROW(B46)-ROW($B$2)</f>
         <v>44</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="C46" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="D46" s="7" t="s">
+      <c r="D46" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="E46" s="8" t="s">
+      <c r="E46" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="F46" s="7" t="s">
+      <c r="F46" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="G46" s="8" t="s">
+      <c r="G46" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="H46" s="7" t="s">
+      <c r="H46" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="I46" s="8" t="s">
+      <c r="I46" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="J46" s="21"/>
-      <c r="K46" s="17">
+      <c r="J46" s="17"/>
+      <c r="K46" s="18">
         <v>3</v>
       </c>
-      <c r="L46" s="7"/>
-    </row>
-    <row r="47" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A47" s="1"/>
-      <c r="B47" s="11">
+      <c r="L46" s="9"/>
+    </row>
+    <row r="47" ht="24.75" spans="1:12">
+      <c r="A47" s="2"/>
+      <c r="B47" s="7">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="C47" s="13" t="s">
+      <c r="C47" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="D47" s="9" t="s">
+      <c r="D47" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="E47" s="10" t="s">
+      <c r="E47" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="F47" s="9" t="s">
+      <c r="F47" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="G47" s="10" t="s">
+      <c r="G47" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="H47" s="9" t="s">
+      <c r="H47" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="I47" s="10" t="s">
+      <c r="I47" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="J47" s="22"/>
-      <c r="K47" s="18">
+      <c r="J47" s="19"/>
+      <c r="K47" s="20">
         <v>2</v>
       </c>
-      <c r="L47" s="9"/>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="1"/>
-      <c r="B48" s="11">
-        <f>ROW(B48) - ROW($B$2)</f>
+      <c r="L47" s="12"/>
+    </row>
+    <row r="48" ht="15.75" spans="1:12">
+      <c r="A48" s="2"/>
+      <c r="B48" s="7">
+        <f>ROW(B48)-ROW($B$2)</f>
         <v>46</v>
       </c>
-      <c r="C48" s="12" t="s">
+      <c r="C48" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="D48" s="7" t="s">
+      <c r="D48" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="E48" s="8" t="s">
+      <c r="E48" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="F48" s="7" t="s">
+      <c r="F48" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="G48" s="8" t="s">
+      <c r="G48" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="H48" s="7" t="s">
+      <c r="H48" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="I48" s="8" t="s">
+      <c r="I48" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="J48" s="21"/>
-      <c r="K48" s="17">
+      <c r="J48" s="17"/>
+      <c r="K48" s="18">
         <v>7</v>
       </c>
-      <c r="L48" s="7"/>
-    </row>
-    <row r="49" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A49" s="1"/>
-      <c r="B49" s="11">
+      <c r="L48" s="9"/>
+    </row>
+    <row r="49" ht="24.75" spans="1:12">
+      <c r="A49" s="2"/>
+      <c r="B49" s="7">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="C49" s="13" t="s">
+      <c r="C49" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="D49" s="9" t="s">
+      <c r="D49" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="E49" s="10" t="s">
+      <c r="E49" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="F49" s="9" t="s">
+      <c r="F49" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="G49" s="10" t="s">
+      <c r="G49" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="H49" s="9" t="s">
+      <c r="H49" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="I49" s="10" t="s">
+      <c r="I49" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="J49" s="22"/>
-      <c r="K49" s="18">
-        <v>1</v>
-      </c>
-      <c r="L49" s="9"/>
-    </row>
-    <row r="50" spans="1:12" ht="48" x14ac:dyDescent="0.25">
-      <c r="A50" s="1"/>
-      <c r="B50" s="11">
-        <f>ROW(B50) - ROW($B$2)</f>
+      <c r="J49" s="19"/>
+      <c r="K49" s="20">
+        <v>1</v>
+      </c>
+      <c r="L49" s="12"/>
+    </row>
+    <row r="50" ht="36.75" spans="1:12">
+      <c r="A50" s="2"/>
+      <c r="B50" s="7">
+        <f>ROW(B50)-ROW($B$2)</f>
         <v>48</v>
       </c>
-      <c r="C50" s="12" t="s">
+      <c r="C50" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="D50" s="7" t="s">
+      <c r="D50" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="E50" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="F50" s="7" t="s">
+      <c r="F50" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="G50" s="8" t="s">
+      <c r="G50" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="H50" s="7" t="s">
+      <c r="H50" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="I50" s="8" t="s">
+      <c r="I50" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="J50" s="21"/>
-      <c r="K50" s="17">
-        <v>1</v>
-      </c>
-      <c r="L50" s="7"/>
-    </row>
-    <row r="51" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1"/>
-      <c r="B51" s="11">
+      <c r="J50" s="17"/>
+      <c r="K50" s="18">
+        <v>1</v>
+      </c>
+      <c r="L50" s="9"/>
+    </row>
+    <row r="51" ht="26.25" spans="1:12">
+      <c r="A51" s="2"/>
+      <c r="B51" s="7">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="C51" s="13" t="s">
+      <c r="C51" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="D51" s="9" t="s">
+      <c r="D51" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="E51" s="10" t="s">
+      <c r="E51" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="F51" s="9" t="s">
+      <c r="F51" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="G51" s="10" t="s">
+      <c r="G51" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="H51" s="9" t="s">
+      <c r="H51" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="I51" s="10" t="s">
+      <c r="I51" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="J51" s="22"/>
-      <c r="K51" s="18">
-        <v>1</v>
-      </c>
-      <c r="L51" s="9"/>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A52" s="1"/>
-      <c r="B52" s="11">
-        <f>ROW(B52) - ROW($B$2)</f>
+      <c r="J51" s="19"/>
+      <c r="K51" s="20">
+        <v>1</v>
+      </c>
+      <c r="L51" s="12"/>
+    </row>
+    <row r="52" ht="15.75" spans="1:12">
+      <c r="A52" s="2"/>
+      <c r="B52" s="7">
+        <f>ROW(B52)-ROW($B$2)</f>
         <v>50</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="C52" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="D52" s="7" t="s">
+      <c r="D52" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="E52" s="8" t="s">
+      <c r="E52" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="F52" s="7" t="s">
+      <c r="F52" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="G52" s="8" t="s">
+      <c r="G52" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="H52" s="7"/>
-      <c r="I52" s="8" t="s">
+      <c r="H52" s="9"/>
+      <c r="I52" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="J52" s="21"/>
-      <c r="K52" s="17">
+      <c r="J52" s="17"/>
+      <c r="K52" s="18">
         <v>2</v>
       </c>
-      <c r="L52" s="7"/>
-    </row>
-    <row r="53" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1"/>
-      <c r="B53" s="11">
+      <c r="L52" s="9"/>
+    </row>
+    <row r="53" ht="26.25" spans="1:12">
+      <c r="A53" s="2"/>
+      <c r="B53" s="7">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="C53" s="13" t="s">
+      <c r="C53" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="D53" s="9" t="s">
+      <c r="D53" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="E53" s="10" t="s">
+      <c r="E53" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="F53" s="9" t="s">
+      <c r="F53" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="G53" s="10" t="s">
+      <c r="G53" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="H53" s="9" t="s">
+      <c r="H53" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="I53" s="10">
+      <c r="I53" s="13">
         <v>532610871</v>
       </c>
-      <c r="J53" s="22"/>
-      <c r="K53" s="18">
-        <v>1</v>
-      </c>
-      <c r="L53" s="9"/>
-    </row>
-    <row r="54" spans="1:12" ht="48" x14ac:dyDescent="0.25">
-      <c r="A54" s="1"/>
-      <c r="B54" s="11">
+      <c r="J53" s="19"/>
+      <c r="K53" s="20">
+        <v>1</v>
+      </c>
+      <c r="L53" s="12"/>
+    </row>
+    <row r="54" ht="48.75" spans="1:12">
+      <c r="A54" s="2"/>
+      <c r="B54" s="7">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="C54" s="13" t="s">
+      <c r="C54" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="D54" s="9" t="s">
+      <c r="D54" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="E54" s="10" t="s">
+      <c r="E54" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="F54" s="9" t="s">
+      <c r="F54" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="G54" s="10" t="s">
+      <c r="G54" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="H54" s="9" t="s">
+      <c r="H54" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="I54" s="10" t="s">
+      <c r="I54" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="J54" s="22"/>
-      <c r="K54" s="18">
-        <v>1</v>
-      </c>
-      <c r="L54" s="9"/>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A55" s="1"/>
-      <c r="B55" s="11">
-        <f>ROW(B55) - ROW($B$2)</f>
+      <c r="J54" s="19"/>
+      <c r="K54" s="20">
+        <v>1</v>
+      </c>
+      <c r="L54" s="12"/>
+    </row>
+    <row r="55" ht="15.75" spans="1:12">
+      <c r="A55" s="2"/>
+      <c r="B55" s="7">
+        <f>ROW(B55)-ROW($B$2)</f>
         <v>53</v>
       </c>
-      <c r="C55" s="12" t="s">
+      <c r="C55" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="D55" s="7" t="s">
+      <c r="D55" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="E55" s="8" t="s">
+      <c r="E55" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="F55" s="7" t="s">
+      <c r="F55" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="G55" s="8">
+      <c r="G55" s="10">
         <v>61300311121</v>
       </c>
-      <c r="H55" s="7" t="s">
+      <c r="H55" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="I55" s="8">
+      <c r="I55" s="10">
         <v>61300311121</v>
       </c>
-      <c r="J55" s="21"/>
-      <c r="K55" s="17">
+      <c r="J55" s="17"/>
+      <c r="K55" s="18">
         <v>3</v>
       </c>
-      <c r="L55" s="7"/>
-    </row>
-    <row r="56" spans="1:12" ht="36" x14ac:dyDescent="0.25">
-      <c r="A56" s="1"/>
-      <c r="B56" s="11">
+      <c r="L55" s="9"/>
+    </row>
+    <row r="56" ht="24.75" spans="1:12">
+      <c r="A56" s="2"/>
+      <c r="B56" s="7">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="C56" s="13" t="s">
+      <c r="C56" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="D56" s="9" t="s">
+      <c r="D56" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="E56" s="10" t="s">
+      <c r="E56" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="F56" s="9" t="s">
+      <c r="F56" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="G56" s="10" t="s">
+      <c r="G56" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="H56" s="9" t="s">
+      <c r="H56" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="I56" s="10" t="s">
+      <c r="I56" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="J56" s="22"/>
-      <c r="K56" s="18">
-        <v>1</v>
-      </c>
-      <c r="L56" s="9"/>
-    </row>
-    <row r="57" spans="1:12" ht="48" x14ac:dyDescent="0.25">
-      <c r="A57" s="1"/>
-      <c r="B57" s="11">
-        <f>ROW(B57) - ROW($B$2)</f>
+      <c r="J56" s="19"/>
+      <c r="K56" s="20">
+        <v>1</v>
+      </c>
+      <c r="L56" s="12"/>
+    </row>
+    <row r="57" ht="48.75" spans="1:12">
+      <c r="A57" s="2"/>
+      <c r="B57" s="7">
+        <f>ROW(B57)-ROW($B$2)</f>
         <v>55</v>
       </c>
-      <c r="C57" s="12" t="s">
+      <c r="C57" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="D57" s="7" t="s">
+      <c r="D57" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="E57" s="8" t="s">
+      <c r="E57" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="F57" s="7" t="s">
+      <c r="F57" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="G57" s="8" t="s">
+      <c r="G57" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="H57" s="7" t="s">
+      <c r="H57" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="I57" s="8" t="s">
+      <c r="I57" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="J57" s="21"/>
-      <c r="K57" s="17">
-        <v>1</v>
-      </c>
-      <c r="L57" s="7"/>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A58" s="1"/>
-      <c r="B58" s="11">
+      <c r="J57" s="17"/>
+      <c r="K57" s="18">
+        <v>1</v>
+      </c>
+      <c r="L57" s="9"/>
+    </row>
+    <row r="58" ht="15.75" spans="1:12">
+      <c r="A58" s="2"/>
+      <c r="B58" s="7">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="C58" s="13" t="s">
+      <c r="C58" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="D58" s="9" t="s">
+      <c r="D58" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="E58" s="10" t="s">
+      <c r="E58" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="F58" s="9" t="s">
+      <c r="F58" s="12" t="s">
         <v>257</v>
       </c>
-      <c r="G58" s="10" t="s">
+      <c r="G58" s="13" t="s">
         <v>258</v>
       </c>
-      <c r="H58" s="9" t="s">
+      <c r="H58" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="I58" s="10" t="s">
+      <c r="I58" s="13" t="s">
         <v>259</v>
       </c>
-      <c r="J58" s="22"/>
-      <c r="K58" s="18">
-        <v>1</v>
-      </c>
-      <c r="L58" s="9"/>
-    </row>
-    <row r="59" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A59" s="1"/>
-      <c r="B59" s="11">
-        <f>ROW(B59) - ROW($B$2)</f>
+      <c r="J58" s="19"/>
+      <c r="K58" s="20">
+        <v>1</v>
+      </c>
+      <c r="L58" s="12"/>
+    </row>
+    <row r="59" ht="24.75" spans="1:12">
+      <c r="A59" s="2"/>
+      <c r="B59" s="7">
+        <f>ROW(B59)-ROW($B$2)</f>
         <v>57</v>
       </c>
-      <c r="C59" s="12" t="s">
+      <c r="C59" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="D59" s="7" t="s">
+      <c r="D59" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="E59" s="8" t="s">
+      <c r="E59" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="F59" s="7" t="s">
+      <c r="F59" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="G59" s="8" t="s">
+      <c r="G59" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="H59" s="7" t="s">
+      <c r="H59" s="9" t="s">
         <v>263</v>
       </c>
-      <c r="I59" s="8" t="s">
+      <c r="I59" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="J59" s="21"/>
-      <c r="K59" s="17">
-        <v>1</v>
-      </c>
-      <c r="L59" s="7"/>
-    </row>
-    <row r="60" spans="1:12" ht="36" x14ac:dyDescent="0.25">
-      <c r="A60" s="1"/>
-      <c r="B60" s="11">
+      <c r="J59" s="17"/>
+      <c r="K59" s="18">
+        <v>1</v>
+      </c>
+      <c r="L59" s="9"/>
+    </row>
+    <row r="60" ht="36.75" spans="1:12">
+      <c r="A60" s="2"/>
+      <c r="B60" s="7">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="C60" s="13" t="s">
+      <c r="C60" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="D60" s="9" t="s">
+      <c r="D60" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="E60" s="10" t="s">
+      <c r="E60" s="13" t="s">
         <v>266</v>
       </c>
-      <c r="F60" s="9" t="s">
+      <c r="F60" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="G60" s="10" t="s">
+      <c r="G60" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="H60" s="9" t="s">
+      <c r="H60" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="I60" s="10" t="s">
+      <c r="I60" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="J60" s="22"/>
-      <c r="K60" s="18">
-        <v>1</v>
-      </c>
-      <c r="L60" s="9"/>
-    </row>
-    <row r="61" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A61" s="1"/>
-      <c r="B61" s="11">
-        <f>ROW(B61) - ROW($B$2)</f>
+      <c r="J60" s="19"/>
+      <c r="K60" s="20">
+        <v>1</v>
+      </c>
+      <c r="L60" s="12"/>
+    </row>
+    <row r="61" ht="15.75" spans="1:12">
+      <c r="A61" s="2"/>
+      <c r="B61" s="7">
+        <f>ROW(B61)-ROW($B$2)</f>
         <v>59</v>
       </c>
-      <c r="C61" s="12" t="s">
+      <c r="C61" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="D61" s="7" t="s">
+      <c r="D61" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="E61" s="8" t="s">
+      <c r="E61" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="F61" s="7" t="s">
+      <c r="F61" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="G61" s="8" t="s">
+      <c r="G61" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="H61" s="7" t="s">
+      <c r="H61" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I61" s="8" t="s">
+      <c r="I61" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="J61" s="21"/>
-      <c r="K61" s="17">
-        <v>1</v>
-      </c>
-      <c r="L61" s="7"/>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A62" s="1"/>
-      <c r="B62" s="11">
+      <c r="J61" s="17"/>
+      <c r="K61" s="18">
+        <v>1</v>
+      </c>
+      <c r="L61" s="9"/>
+    </row>
+    <row r="62" ht="15.75" spans="1:12">
+      <c r="A62" s="2"/>
+      <c r="B62" s="7">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="C62" s="13" t="s">
+      <c r="C62" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="D62" s="9" t="s">
+      <c r="D62" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="E62" s="10" t="s">
+      <c r="E62" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="F62" s="9" t="s">
+      <c r="F62" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="G62" s="10" t="s">
+      <c r="G62" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="H62" s="9" t="s">
+      <c r="H62" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="I62" s="10" t="s">
+      <c r="I62" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="J62" s="22"/>
-      <c r="K62" s="18">
-        <v>1</v>
-      </c>
-      <c r="L62" s="9"/>
-    </row>
-    <row r="63" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A63" s="1"/>
-      <c r="B63" s="11">
-        <f>ROW(B63) - ROW($B$2)</f>
+      <c r="J62" s="19"/>
+      <c r="K62" s="20">
+        <v>1</v>
+      </c>
+      <c r="L62" s="12"/>
+    </row>
+    <row r="63" ht="24.75" spans="1:12">
+      <c r="A63" s="2"/>
+      <c r="B63" s="7">
+        <f>ROW(B63)-ROW($B$2)</f>
         <v>61</v>
       </c>
-      <c r="C63" s="12" t="s">
+      <c r="C63" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="D63" s="7" t="s">
+      <c r="D63" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="E63" s="8" t="s">
+      <c r="E63" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="F63" s="7" t="s">
+      <c r="F63" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="G63" s="8" t="s">
+      <c r="G63" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="H63" s="7" t="s">
+      <c r="H63" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="I63" s="8" t="s">
+      <c r="I63" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="J63" s="21"/>
-      <c r="K63" s="17">
-        <v>1</v>
-      </c>
-      <c r="L63" s="7"/>
-    </row>
-    <row r="64" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A64" s="1"/>
-      <c r="B64" s="11">
+      <c r="J63" s="17"/>
+      <c r="K63" s="18">
+        <v>1</v>
+      </c>
+      <c r="L63" s="9"/>
+    </row>
+    <row r="64" ht="24.75" spans="1:12">
+      <c r="A64" s="2"/>
+      <c r="B64" s="7">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="C64" s="13" t="s">
+      <c r="C64" s="11" t="s">
         <v>279</v>
       </c>
-      <c r="D64" s="9" t="s">
+      <c r="D64" s="12" t="s">
         <v>286</v>
       </c>
-      <c r="E64" s="10" t="s">
+      <c r="E64" s="13" t="s">
         <v>287</v>
       </c>
-      <c r="F64" s="9" t="s">
+      <c r="F64" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="G64" s="10" t="s">
+      <c r="G64" s="13" t="s">
         <v>288</v>
       </c>
-      <c r="H64" s="9" t="s">
+      <c r="H64" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="I64" s="10" t="s">
+      <c r="I64" s="13" t="s">
         <v>289</v>
       </c>
-      <c r="J64" s="22"/>
-      <c r="K64" s="18">
+      <c r="J64" s="19"/>
+      <c r="K64" s="20">
         <v>2</v>
       </c>
-      <c r="L64" s="9"/>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A65" s="1"/>
-      <c r="B65" s="11">
-        <f>ROW(B65) - ROW($B$2)</f>
+      <c r="L64" s="12"/>
+    </row>
+    <row r="65" ht="15.75" spans="1:12">
+      <c r="A65" s="2"/>
+      <c r="B65" s="7">
+        <f>ROW(B65)-ROW($B$2)</f>
         <v>63</v>
       </c>
-      <c r="C65" s="12" t="s">
+      <c r="C65" s="8" t="s">
         <v>279</v>
       </c>
-      <c r="D65" s="7" t="s">
+      <c r="D65" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="E65" s="8" t="s">
+      <c r="E65" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="F65" s="7" t="s">
+      <c r="F65" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="G65" s="8" t="s">
+      <c r="G65" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="H65" s="7" t="s">
+      <c r="H65" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="I65" s="8" t="s">
+      <c r="I65" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="J65" s="21"/>
-      <c r="K65" s="17">
-        <v>1</v>
-      </c>
-      <c r="L65" s="7"/>
-    </row>
-    <row r="66" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A66" s="1"/>
-      <c r="B66" s="11">
+      <c r="J65" s="17"/>
+      <c r="K65" s="18">
+        <v>1</v>
+      </c>
+      <c r="L65" s="9"/>
+    </row>
+    <row r="66" ht="24.75" spans="1:12">
+      <c r="A66" s="2"/>
+      <c r="B66" s="7">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="C66" s="13" t="s">
+      <c r="C66" s="11" t="s">
         <v>295</v>
       </c>
-      <c r="D66" s="9" t="s">
+      <c r="D66" s="12" t="s">
         <v>296</v>
       </c>
-      <c r="E66" s="10" t="s">
+      <c r="E66" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="F66" s="9" t="s">
+      <c r="F66" s="12" t="s">
         <v>298</v>
       </c>
-      <c r="G66" s="10" t="s">
+      <c r="G66" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="H66" s="9" t="s">
+      <c r="H66" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="I66" s="10" t="s">
+      <c r="I66" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="J66" s="22"/>
-      <c r="K66" s="18">
+      <c r="J66" s="19"/>
+      <c r="K66" s="20">
         <v>4</v>
       </c>
-      <c r="L66" s="9"/>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A67" s="1"/>
-      <c r="B67" s="11">
-        <f>ROW(B67) - ROW($B$2)</f>
+      <c r="L66" s="12"/>
+    </row>
+    <row r="67" ht="15.75" spans="1:12">
+      <c r="A67" s="2"/>
+      <c r="B67" s="7">
+        <f>ROW(B67)-ROW($B$2)</f>
         <v>65</v>
       </c>
-      <c r="C67" s="12" t="s">
+      <c r="C67" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="D67" s="7" t="s">
+      <c r="D67" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="E67" s="8" t="s">
+      <c r="E67" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="F67" s="7" t="s">
+      <c r="F67" s="9" t="s">
         <v>303</v>
       </c>
-      <c r="G67" s="8" t="s">
+      <c r="G67" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="H67" s="7" t="s">
+      <c r="H67" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="I67" s="8" t="s">
+      <c r="I67" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="J67" s="21"/>
-      <c r="K67" s="17">
-        <v>1</v>
-      </c>
-      <c r="L67" s="7"/>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A68" s="1"/>
-      <c r="B68" s="11">
-        <f>ROW(B68) - ROW($B$2)</f>
+      <c r="J67" s="17"/>
+      <c r="K67" s="18">
+        <v>1</v>
+      </c>
+      <c r="L67" s="9"/>
+    </row>
+    <row r="68" ht="15.75" spans="1:12">
+      <c r="A68" s="2"/>
+      <c r="B68" s="7">
+        <f>ROW(B68)-ROW($B$2)</f>
         <v>66</v>
       </c>
-      <c r="C68" s="12" t="s">
+      <c r="C68" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="D68" s="15" t="s">
+      <c r="D68" s="21" t="s">
         <v>306</v>
       </c>
-      <c r="E68" s="16" t="s">
+      <c r="E68" s="22" t="s">
         <v>307</v>
       </c>
-      <c r="F68" s="15" t="s">
+      <c r="F68" s="21" t="s">
         <v>308</v>
       </c>
-      <c r="G68" s="16" t="s">
+      <c r="G68" s="22" t="s">
         <v>309</v>
       </c>
-      <c r="H68" s="15" t="s">
+      <c r="H68" s="21" t="s">
         <v>310</v>
       </c>
-      <c r="I68" s="16" t="s">
+      <c r="I68" s="22" t="s">
         <v>167</v>
       </c>
       <c r="J68" s="23"/>
-      <c r="K68" s="19">
-        <v>1</v>
-      </c>
-      <c r="L68" s="15" t="s">
+      <c r="K68" s="24">
+        <v>1</v>
+      </c>
+      <c r="L68" s="21" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A69" s="1"/>
-      <c r="B69" s="11">
+    <row r="69" ht="15.75" spans="1:12">
+      <c r="A69" s="2"/>
+      <c r="B69" s="7">
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
-      <c r="C69" s="13" t="s">
+      <c r="C69" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="D69" s="9" t="s">
+      <c r="D69" s="12" t="s">
         <v>312</v>
       </c>
-      <c r="E69" s="10" t="s">
+      <c r="E69" s="13" t="s">
         <v>307</v>
       </c>
-      <c r="F69" s="9" t="s">
+      <c r="F69" s="12" t="s">
         <v>308</v>
       </c>
-      <c r="G69" s="10" t="s">
+      <c r="G69" s="13" t="s">
         <v>309</v>
       </c>
-      <c r="H69" s="9" t="s">
+      <c r="H69" s="12" t="s">
         <v>310</v>
       </c>
-      <c r="I69" s="10" t="s">
+      <c r="I69" s="13" t="s">
         <v>309</v>
       </c>
-      <c r="J69" s="22"/>
-      <c r="K69" s="18">
-        <v>1</v>
-      </c>
-      <c r="L69" s="9"/>
-    </row>
-    <row r="70" spans="1:12" ht="48" x14ac:dyDescent="0.25">
-      <c r="A70" s="1"/>
-      <c r="B70" s="11">
-        <f>ROW(B70) - ROW($B$2)</f>
+      <c r="J69" s="19"/>
+      <c r="K69" s="20">
+        <v>1</v>
+      </c>
+      <c r="L69" s="12"/>
+    </row>
+    <row r="70" ht="48.75" spans="1:12">
+      <c r="A70" s="2"/>
+      <c r="B70" s="7">
+        <f>ROW(B70)-ROW($B$2)</f>
         <v>68</v>
       </c>
-      <c r="C70" s="12" t="s">
+      <c r="C70" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="D70" s="7" t="s">
+      <c r="D70" s="9" t="s">
         <v>313</v>
       </c>
-      <c r="E70" s="8" t="s">
+      <c r="E70" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="F70" s="7" t="s">
+      <c r="F70" s="9" t="s">
         <v>315</v>
       </c>
-      <c r="G70" s="8" t="s">
+      <c r="G70" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="H70" s="7" t="s">
+      <c r="H70" s="9" t="s">
         <v>310</v>
       </c>
-      <c r="I70" s="8" t="s">
+      <c r="I70" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="J70" s="21"/>
-      <c r="K70" s="17">
-        <v>1</v>
-      </c>
-      <c r="L70" s="7"/>
-    </row>
-    <row r="71" spans="1:12" ht="36" x14ac:dyDescent="0.25">
-      <c r="A71" s="1"/>
-      <c r="B71" s="11">
+      <c r="J70" s="17"/>
+      <c r="K70" s="18">
+        <v>1</v>
+      </c>
+      <c r="L70" s="9"/>
+    </row>
+    <row r="71" ht="36.75" spans="1:12">
+      <c r="A71" s="2"/>
+      <c r="B71" s="7">
         <f t="shared" si="0"/>
         <v>69</v>
       </c>
-      <c r="C71" s="13" t="s">
+      <c r="C71" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="D71" s="9" t="s">
+      <c r="D71" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="E71" s="10" t="s">
+      <c r="E71" s="13" t="s">
         <v>318</v>
       </c>
-      <c r="F71" s="9" t="s">
+      <c r="F71" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="G71" s="10" t="s">
+      <c r="G71" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="H71" s="9" t="s">
+      <c r="H71" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="I71" s="10" t="s">
+      <c r="I71" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="J71" s="22"/>
-      <c r="K71" s="18">
+      <c r="J71" s="19"/>
+      <c r="K71" s="20">
         <v>2</v>
       </c>
-      <c r="L71" s="9"/>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A72" s="1"/>
-      <c r="B72" s="11">
-        <f>ROW(B72) - ROW($B$2)</f>
+      <c r="L71" s="12"/>
+    </row>
+    <row r="72" ht="15.75" spans="1:12">
+      <c r="A72" s="2"/>
+      <c r="B72" s="7">
+        <f>ROW(B72)-ROW($B$2)</f>
         <v>70</v>
       </c>
-      <c r="C72" s="12" t="s">
+      <c r="C72" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="D72" s="7" t="s">
+      <c r="D72" s="9" t="s">
         <v>320</v>
       </c>
-      <c r="E72" s="8" t="s">
+      <c r="E72" s="10" t="s">
         <v>321</v>
       </c>
-      <c r="F72" s="7" t="s">
+      <c r="F72" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="G72" s="8" t="s">
+      <c r="G72" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="H72" s="7" t="s">
+      <c r="H72" s="9" t="s">
         <v>310</v>
       </c>
-      <c r="I72" s="8" t="s">
+      <c r="I72" s="10" t="s">
         <v>323</v>
       </c>
-      <c r="J72" s="21"/>
-      <c r="K72" s="17">
-        <v>1</v>
-      </c>
-      <c r="L72" s="7"/>
-    </row>
-    <row r="73" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A73" s="1"/>
-      <c r="B73" s="11">
+      <c r="J72" s="17"/>
+      <c r="K72" s="18">
+        <v>1</v>
+      </c>
+      <c r="L72" s="9"/>
+    </row>
+    <row r="73" ht="24.75" spans="1:12">
+      <c r="A73" s="2"/>
+      <c r="B73" s="7">
         <f t="shared" si="0"/>
         <v>71</v>
       </c>
-      <c r="C73" s="13" t="s">
+      <c r="C73" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="D73" s="9" t="s">
+      <c r="D73" s="12" t="s">
         <v>324</v>
       </c>
-      <c r="E73" s="10" t="s">
+      <c r="E73" s="13" t="s">
         <v>325</v>
       </c>
-      <c r="F73" s="9" t="s">
+      <c r="F73" s="12" t="s">
         <v>308</v>
       </c>
-      <c r="G73" s="10" t="s">
+      <c r="G73" s="13" t="s">
         <v>326</v>
       </c>
-      <c r="H73" s="9" t="s">
+      <c r="H73" s="12" t="s">
         <v>327</v>
       </c>
-      <c r="I73" s="10" t="s">
+      <c r="I73" s="13" t="s">
         <v>326</v>
       </c>
-      <c r="J73" s="22"/>
-      <c r="K73" s="18">
-        <v>1</v>
-      </c>
-      <c r="L73" s="9"/>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A74" s="1"/>
-      <c r="B74" s="11">
-        <f>ROW(B74) - ROW($B$2)</f>
+      <c r="J73" s="19"/>
+      <c r="K73" s="20">
+        <v>1</v>
+      </c>
+      <c r="L73" s="12"/>
+    </row>
+    <row r="74" ht="15.75" spans="1:12">
+      <c r="A74" s="2"/>
+      <c r="B74" s="7">
+        <f>ROW(B74)-ROW($B$2)</f>
         <v>72</v>
       </c>
-      <c r="C74" s="12" t="s">
+      <c r="C74" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="D74" s="7" t="s">
+      <c r="D74" s="9" t="s">
         <v>328</v>
       </c>
-      <c r="E74" s="8" t="s">
+      <c r="E74" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="F74" s="7" t="s">
+      <c r="F74" s="9" t="s">
         <v>330</v>
       </c>
-      <c r="G74" s="8" t="s">
+      <c r="G74" s="10" t="s">
         <v>331</v>
       </c>
-      <c r="H74" s="7" t="s">
+      <c r="H74" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="I74" s="8" t="s">
+      <c r="I74" s="10" t="s">
         <v>331</v>
       </c>
-      <c r="J74" s="21"/>
-      <c r="K74" s="17">
-        <v>1</v>
-      </c>
-      <c r="L74" s="7"/>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A75" s="1"/>
-      <c r="B75" s="11">
+      <c r="J74" s="17"/>
+      <c r="K74" s="18">
+        <v>1</v>
+      </c>
+      <c r="L74" s="9"/>
+    </row>
+    <row r="75" spans="1:12">
+      <c r="A75" s="2"/>
+      <c r="B75" s="7">
         <f t="shared" si="0"/>
         <v>73</v>
       </c>
-      <c r="C75" s="13"/>
-      <c r="D75" s="9" t="s">
+      <c r="C75" s="11" t="s">
         <v>333</v>
       </c>
-      <c r="E75" s="10" t="s">
+      <c r="D75" s="12" t="s">
         <v>334</v>
       </c>
-      <c r="F75" s="9" t="s">
+      <c r="E75" s="13" t="s">
         <v>335</v>
       </c>
-      <c r="G75" s="10" t="s">
+      <c r="F75" s="12" t="s">
         <v>336</v>
       </c>
-      <c r="H75" s="9" t="s">
+      <c r="G75" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="H75" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I75" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="J75" s="22"/>
-      <c r="K75" s="18">
+      <c r="I75" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="J75" s="19"/>
+      <c r="K75" s="20">
         <v>4</v>
       </c>
-      <c r="L75" s="9"/>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A76" s="1"/>
-      <c r="B76" s="11">
-        <f>ROW(B76) - ROW($B$2)</f>
+      <c r="L75" s="12"/>
+    </row>
+    <row r="76" ht="15.75" spans="1:12">
+      <c r="A76" s="2"/>
+      <c r="B76" s="7">
+        <f>ROW(B76)-ROW($B$2)</f>
         <v>74</v>
       </c>
-      <c r="C76" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="D76" s="7" t="s">
+      <c r="C76" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="D76" s="9" t="s">
         <v>339</v>
       </c>
-      <c r="E76" s="8" t="s">
+      <c r="E76" s="10" t="s">
         <v>340</v>
       </c>
-      <c r="F76" s="7" t="s">
+      <c r="F76" s="9" t="s">
         <v>341</v>
       </c>
-      <c r="G76" s="8" t="s">
+      <c r="G76" s="10" t="s">
         <v>342</v>
       </c>
-      <c r="H76" s="7" t="s">
+      <c r="H76" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I76" s="8" t="s">
+      <c r="I76" s="10" t="s">
         <v>343</v>
       </c>
-      <c r="J76" s="21"/>
-      <c r="K76" s="17">
+      <c r="J76" s="17"/>
+      <c r="K76" s="18">
         <v>2</v>
       </c>
-      <c r="L76" s="7"/>
-    </row>
-    <row r="77" spans="1:12" ht="36" x14ac:dyDescent="0.25">
-      <c r="A77" s="1"/>
-      <c r="B77" s="11">
+      <c r="L76" s="9"/>
+    </row>
+    <row r="77" ht="24.75" spans="1:12">
+      <c r="A77" s="2"/>
+      <c r="B77" s="7">
         <f t="shared" si="0"/>
         <v>75</v>
       </c>
-      <c r="C77" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="D77" s="9" t="s">
+      <c r="C77" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="D77" s="12" t="s">
         <v>344</v>
       </c>
-      <c r="E77" s="10" t="s">
+      <c r="E77" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="F77" s="9" t="s">
+      <c r="F77" s="12" t="s">
         <v>341</v>
       </c>
-      <c r="G77" s="10" t="s">
+      <c r="G77" s="13" t="s">
         <v>346</v>
       </c>
-      <c r="H77" s="9" t="s">
+      <c r="H77" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I77" s="10" t="s">
+      <c r="I77" s="13" t="s">
         <v>347</v>
       </c>
-      <c r="J77" s="22"/>
-      <c r="K77" s="18">
+      <c r="J77" s="19"/>
+      <c r="K77" s="20">
         <v>20</v>
       </c>
-      <c r="L77" s="9"/>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A78" s="1"/>
-      <c r="B78" s="11">
-        <f>ROW(B78) - ROW($B$2)</f>
+      <c r="L77" s="12"/>
+    </row>
+    <row r="78" ht="15.75" spans="1:12">
+      <c r="A78" s="2"/>
+      <c r="B78" s="7">
+        <f>ROW(B78)-ROW($B$2)</f>
         <v>76</v>
       </c>
-      <c r="C78" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="D78" s="7" t="s">
+      <c r="C78" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="D78" s="9" t="s">
         <v>348</v>
       </c>
-      <c r="E78" s="8" t="s">
+      <c r="E78" s="10" t="s">
         <v>349</v>
       </c>
-      <c r="F78" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="G78" s="8" t="s">
+      <c r="F78" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="G78" s="10" t="s">
         <v>350</v>
       </c>
-      <c r="H78" s="7" t="s">
+      <c r="H78" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I78" s="8" t="s">
+      <c r="I78" s="10" t="s">
         <v>351</v>
       </c>
-      <c r="J78" s="21"/>
-      <c r="K78" s="17">
+      <c r="J78" s="17"/>
+      <c r="K78" s="18">
         <v>6</v>
       </c>
-      <c r="L78" s="7"/>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A79" s="1"/>
-      <c r="B79" s="11">
+      <c r="L78" s="9"/>
+    </row>
+    <row r="79" ht="15.75" spans="1:12">
+      <c r="A79" s="2"/>
+      <c r="B79" s="7">
         <f t="shared" si="0"/>
         <v>77</v>
       </c>
-      <c r="C79" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="D79" s="9" t="s">
+      <c r="C79" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="D79" s="12" t="s">
         <v>352</v>
       </c>
-      <c r="E79" s="10" t="s">
+      <c r="E79" s="13" t="s">
         <v>353</v>
       </c>
-      <c r="F79" s="9" t="s">
+      <c r="F79" s="12" t="s">
         <v>341</v>
       </c>
-      <c r="G79" s="10" t="s">
+      <c r="G79" s="13" t="s">
         <v>354</v>
       </c>
-      <c r="H79" s="9" t="s">
+      <c r="H79" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I79" s="10" t="s">
+      <c r="I79" s="13" t="s">
         <v>355</v>
       </c>
-      <c r="J79" s="22"/>
-      <c r="K79" s="18">
+      <c r="J79" s="19"/>
+      <c r="K79" s="20">
         <v>2</v>
       </c>
-      <c r="L79" s="9"/>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A80" s="1"/>
-      <c r="B80" s="11">
-        <f>ROW(B80) - ROW($B$2)</f>
+      <c r="L79" s="12"/>
+    </row>
+    <row r="80" spans="1:12">
+      <c r="A80" s="2"/>
+      <c r="B80" s="7">
+        <f>ROW(B80)-ROW($B$2)</f>
         <v>78</v>
       </c>
-      <c r="C80" s="12"/>
-      <c r="D80" s="7" t="s">
+      <c r="C80" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="D80" s="9" t="s">
         <v>356</v>
       </c>
-      <c r="E80" s="8" t="s">
+      <c r="E80" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="F80" s="7" t="s">
+      <c r="F80" s="9" t="s">
         <v>341</v>
       </c>
-      <c r="G80" s="8" t="s">
+      <c r="G80" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="H80" s="7" t="s">
+      <c r="H80" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I80" s="8" t="s">
+      <c r="I80" s="10" t="s">
         <v>359</v>
       </c>
-      <c r="J80" s="21"/>
-      <c r="K80" s="17">
-        <v>1</v>
-      </c>
-      <c r="L80" s="7"/>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A81" s="1"/>
-      <c r="B81" s="11">
+      <c r="J80" s="17"/>
+      <c r="K80" s="18">
+        <v>1</v>
+      </c>
+      <c r="L80" s="9"/>
+    </row>
+    <row r="81" ht="15.75" spans="1:12">
+      <c r="A81" s="2"/>
+      <c r="B81" s="7">
         <f t="shared" si="0"/>
         <v>79</v>
       </c>
-      <c r="C81" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="D81" s="9" t="s">
+      <c r="C81" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="D81" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="E81" s="10" t="s">
+      <c r="E81" s="13" t="s">
         <v>361</v>
       </c>
-      <c r="F81" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="G81" s="10" t="s">
+      <c r="F81" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="G81" s="13" t="s">
         <v>362</v>
       </c>
-      <c r="H81" s="9" t="s">
+      <c r="H81" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I81" s="10" t="s">
+      <c r="I81" s="13" t="s">
         <v>363</v>
       </c>
-      <c r="J81" s="22"/>
-      <c r="K81" s="18">
-        <v>1</v>
-      </c>
-      <c r="L81" s="9"/>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A82" s="1"/>
-      <c r="B82" s="11">
-        <f>ROW(B82) - ROW($B$2)</f>
+      <c r="J81" s="19"/>
+      <c r="K81" s="20">
+        <v>1</v>
+      </c>
+      <c r="L81" s="12"/>
+    </row>
+    <row r="82" ht="15.75" spans="1:12">
+      <c r="A82" s="2"/>
+      <c r="B82" s="7">
+        <f>ROW(B82)-ROW($B$2)</f>
         <v>80</v>
       </c>
-      <c r="C82" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="D82" s="7" t="s">
+      <c r="C82" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="D82" s="9" t="s">
         <v>364</v>
       </c>
-      <c r="E82" s="8" t="s">
+      <c r="E82" s="10" t="s">
         <v>365</v>
       </c>
-      <c r="F82" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="G82" s="8" t="s">
+      <c r="F82" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="G82" s="10" t="s">
         <v>366</v>
       </c>
-      <c r="H82" s="7" t="s">
+      <c r="H82" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I82" s="8" t="s">
+      <c r="I82" s="10" t="s">
         <v>367</v>
       </c>
-      <c r="J82" s="21"/>
-      <c r="K82" s="17">
-        <v>1</v>
-      </c>
-      <c r="L82" s="7"/>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A83" s="1"/>
-      <c r="B83" s="11">
+      <c r="J82" s="17"/>
+      <c r="K82" s="18">
+        <v>1</v>
+      </c>
+      <c r="L82" s="9"/>
+    </row>
+    <row r="83" ht="15.75" spans="1:12">
+      <c r="A83" s="2"/>
+      <c r="B83" s="7">
         <f t="shared" si="0"/>
         <v>81</v>
       </c>
-      <c r="C83" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="D83" s="9" t="s">
+      <c r="C83" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="D83" s="12" t="s">
         <v>368</v>
       </c>
-      <c r="E83" s="10" t="s">
+      <c r="E83" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="F83" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="G83" s="10" t="s">
+      <c r="F83" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="G83" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="H83" s="9" t="s">
+      <c r="H83" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I83" s="10" t="s">
+      <c r="I83" s="13" t="s">
         <v>371</v>
       </c>
-      <c r="J83" s="22"/>
-      <c r="K83" s="18">
-        <v>1</v>
-      </c>
-      <c r="L83" s="9"/>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A84" s="1"/>
-      <c r="B84" s="11">
-        <f>ROW(B84) - ROW($B$2)</f>
+      <c r="J83" s="19"/>
+      <c r="K83" s="20">
+        <v>1</v>
+      </c>
+      <c r="L83" s="12"/>
+    </row>
+    <row r="84" ht="15.75" spans="1:12">
+      <c r="A84" s="2"/>
+      <c r="B84" s="7">
+        <f>ROW(B84)-ROW($B$2)</f>
         <v>82</v>
       </c>
-      <c r="C84" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="D84" s="7" t="s">
+      <c r="C84" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="D84" s="9" t="s">
         <v>372</v>
       </c>
-      <c r="E84" s="8" t="s">
+      <c r="E84" s="10" t="s">
         <v>373</v>
       </c>
-      <c r="F84" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="G84" s="8" t="s">
+      <c r="F84" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="G84" s="10" t="s">
         <v>374</v>
       </c>
-      <c r="H84" s="7" t="s">
+      <c r="H84" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I84" s="8" t="s">
+      <c r="I84" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="J84" s="21"/>
-      <c r="K84" s="17">
-        <v>1</v>
-      </c>
-      <c r="L84" s="7"/>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A85" s="1"/>
-      <c r="B85" s="11">
+      <c r="J84" s="17"/>
+      <c r="K84" s="18">
+        <v>1</v>
+      </c>
+      <c r="L84" s="9"/>
+    </row>
+    <row r="85" ht="15.75" spans="1:12">
+      <c r="A85" s="2"/>
+      <c r="B85" s="7">
         <f t="shared" si="0"/>
         <v>83</v>
       </c>
-      <c r="C85" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="D85" s="9" t="s">
+      <c r="C85" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="D85" s="12" t="s">
         <v>375</v>
       </c>
-      <c r="E85" s="10" t="s">
+      <c r="E85" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="F85" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="G85" s="10" t="s">
+      <c r="F85" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="G85" s="13" t="s">
         <v>377</v>
       </c>
-      <c r="H85" s="9" t="s">
+      <c r="H85" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I85" s="10" t="s">
+      <c r="I85" s="13" t="s">
         <v>378</v>
       </c>
-      <c r="J85" s="22"/>
-      <c r="K85" s="18">
-        <v>1</v>
-      </c>
-      <c r="L85" s="9"/>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A86" s="1"/>
-      <c r="B86" s="11">
-        <f>ROW(B86) - ROW($B$2)</f>
+      <c r="J85" s="19"/>
+      <c r="K85" s="20">
+        <v>1</v>
+      </c>
+      <c r="L85" s="12"/>
+    </row>
+    <row r="86" ht="15.75" spans="1:12">
+      <c r="A86" s="2"/>
+      <c r="B86" s="7">
+        <f>ROW(B86)-ROW($B$2)</f>
         <v>84</v>
       </c>
-      <c r="C86" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="D86" s="7" t="s">
+      <c r="C86" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="D86" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="E86" s="8" t="s">
+      <c r="E86" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="F86" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="G86" s="8" t="s">
+      <c r="F86" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="G86" s="10" t="s">
         <v>381</v>
       </c>
-      <c r="H86" s="7" t="s">
+      <c r="H86" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I86" s="8" t="s">
+      <c r="I86" s="10" t="s">
         <v>382</v>
       </c>
-      <c r="J86" s="21"/>
-      <c r="K86" s="17">
-        <v>1</v>
-      </c>
-      <c r="L86" s="7"/>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A87" s="1"/>
-      <c r="B87" s="11">
+      <c r="J86" s="17"/>
+      <c r="K86" s="18">
+        <v>1</v>
+      </c>
+      <c r="L86" s="9"/>
+    </row>
+    <row r="87" ht="15.75" spans="1:12">
+      <c r="A87" s="2"/>
+      <c r="B87" s="7">
         <f t="shared" si="0"/>
         <v>85</v>
       </c>
-      <c r="C87" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="D87" s="9" t="s">
+      <c r="C87" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="D87" s="12" t="s">
         <v>383</v>
       </c>
-      <c r="E87" s="10" t="s">
+      <c r="E87" s="13" t="s">
         <v>384</v>
       </c>
-      <c r="F87" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="G87" s="10" t="s">
+      <c r="F87" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="G87" s="13" t="s">
         <v>385</v>
       </c>
-      <c r="H87" s="9" t="s">
+      <c r="H87" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I87" s="10" t="s">
+      <c r="I87" s="13" t="s">
         <v>386</v>
       </c>
-      <c r="J87" s="22"/>
-      <c r="K87" s="18">
-        <v>1</v>
-      </c>
-      <c r="L87" s="9"/>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A88" s="1"/>
-      <c r="B88" s="11">
-        <f>ROW(B88) - ROW($B$2)</f>
+      <c r="J87" s="19"/>
+      <c r="K87" s="20">
+        <v>1</v>
+      </c>
+      <c r="L87" s="12"/>
+    </row>
+    <row r="88" ht="15.75" spans="1:12">
+      <c r="A88" s="2"/>
+      <c r="B88" s="7">
+        <f>ROW(B88)-ROW($B$2)</f>
         <v>86</v>
       </c>
-      <c r="C88" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="D88" s="7" t="s">
+      <c r="C88" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="D88" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="E88" s="8" t="s">
+      <c r="E88" s="10" t="s">
         <v>373</v>
       </c>
-      <c r="F88" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="G88" s="8" t="s">
+      <c r="F88" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="G88" s="10" t="s">
         <v>374</v>
       </c>
-      <c r="H88" s="7" t="s">
+      <c r="H88" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I88" s="8" t="s">
+      <c r="I88" s="10" t="s">
         <v>388</v>
       </c>
-      <c r="J88" s="21"/>
-      <c r="K88" s="17">
+      <c r="J88" s="17"/>
+      <c r="K88" s="18">
         <v>2</v>
       </c>
-      <c r="L88" s="7"/>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A89" s="1"/>
-      <c r="B89" s="11">
+      <c r="L88" s="9"/>
+    </row>
+    <row r="89" ht="15.75" spans="1:12">
+      <c r="A89" s="2"/>
+      <c r="B89" s="7">
         <f t="shared" si="0"/>
         <v>87</v>
       </c>
-      <c r="C89" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="D89" s="9" t="s">
+      <c r="C89" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="D89" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="E89" s="10" t="s">
+      <c r="E89" s="13" t="s">
         <v>390</v>
       </c>
-      <c r="F89" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="G89" s="10" t="s">
+      <c r="F89" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="G89" s="13" t="s">
         <v>391</v>
       </c>
-      <c r="H89" s="9" t="s">
+      <c r="H89" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I89" s="10" t="s">
+      <c r="I89" s="13" t="s">
         <v>392</v>
       </c>
-      <c r="J89" s="22"/>
-      <c r="K89" s="18">
-        <v>1</v>
-      </c>
-      <c r="L89" s="9"/>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A90" s="1"/>
-      <c r="B90" s="11">
-        <f>ROW(B90) - ROW($B$2)</f>
+      <c r="J89" s="19"/>
+      <c r="K89" s="20">
+        <v>1</v>
+      </c>
+      <c r="L89" s="12"/>
+    </row>
+    <row r="90" ht="15.75" spans="1:12">
+      <c r="A90" s="2"/>
+      <c r="B90" s="7">
+        <f>ROW(B90)-ROW($B$2)</f>
         <v>88</v>
       </c>
-      <c r="C90" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="D90" s="7" t="s">
+      <c r="C90" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="D90" s="9" t="s">
         <v>393</v>
       </c>
-      <c r="E90" s="8" t="s">
+      <c r="E90" s="10" t="s">
         <v>394</v>
       </c>
-      <c r="F90" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="G90" s="8" t="s">
+      <c r="F90" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="G90" s="10" t="s">
         <v>395</v>
       </c>
-      <c r="H90" s="7" t="s">
+      <c r="H90" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I90" s="8" t="s">
+      <c r="I90" s="10" t="s">
         <v>347</v>
       </c>
-      <c r="J90" s="21"/>
-      <c r="K90" s="17">
+      <c r="J90" s="17"/>
+      <c r="K90" s="18">
         <v>6</v>
       </c>
-      <c r="L90" s="7"/>
-    </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A91" s="1"/>
-      <c r="B91" s="11">
+      <c r="L90" s="9"/>
+    </row>
+    <row r="91" ht="15.75" spans="1:12">
+      <c r="A91" s="2"/>
+      <c r="B91" s="7">
         <f t="shared" si="0"/>
         <v>89</v>
       </c>
-      <c r="C91" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="D91" s="9" t="s">
+      <c r="C91" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="D91" s="12" t="s">
         <v>396</v>
       </c>
-      <c r="E91" s="10" t="s">
+      <c r="E91" s="13" t="s">
         <v>397</v>
       </c>
-      <c r="F91" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="G91" s="10" t="s">
+      <c r="F91" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="G91" s="13" t="s">
         <v>398</v>
       </c>
-      <c r="H91" s="9" t="s">
+      <c r="H91" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I91" s="10" t="s">
+      <c r="I91" s="13" t="s">
         <v>399</v>
       </c>
-      <c r="J91" s="22"/>
-      <c r="K91" s="18">
+      <c r="J91" s="19"/>
+      <c r="K91" s="20">
         <v>3</v>
       </c>
-      <c r="L91" s="9"/>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A92" s="1"/>
-      <c r="B92" s="11">
-        <f>ROW(B92) - ROW($B$2)</f>
+      <c r="L91" s="12"/>
+    </row>
+    <row r="92" ht="15.75" spans="1:12">
+      <c r="A92" s="2"/>
+      <c r="B92" s="7">
+        <f>ROW(B92)-ROW($B$2)</f>
         <v>90</v>
       </c>
-      <c r="C92" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="D92" s="7" t="s">
+      <c r="C92" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="D92" s="9" t="s">
         <v>400</v>
       </c>
-      <c r="E92" s="8" t="s">
+      <c r="E92" s="10" t="s">
         <v>401</v>
       </c>
-      <c r="F92" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="G92" s="8" t="s">
+      <c r="F92" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="G92" s="10" t="s">
         <v>402</v>
       </c>
-      <c r="H92" s="7" t="s">
+      <c r="H92" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I92" s="8" t="s">
+      <c r="I92" s="10" t="s">
         <v>403</v>
       </c>
-      <c r="J92" s="21"/>
-      <c r="K92" s="17">
-        <v>1</v>
-      </c>
-      <c r="L92" s="7"/>
-    </row>
-    <row r="93" spans="1:12" ht="36" x14ac:dyDescent="0.25">
-      <c r="A93" s="1"/>
-      <c r="B93" s="11">
+      <c r="J92" s="17"/>
+      <c r="K92" s="18">
+        <v>1</v>
+      </c>
+      <c r="L92" s="9"/>
+    </row>
+    <row r="93" ht="36.75" spans="1:12">
+      <c r="A93" s="2"/>
+      <c r="B93" s="7">
         <f t="shared" si="0"/>
         <v>91</v>
       </c>
-      <c r="C93" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="D93" s="9" t="s">
+      <c r="C93" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="D93" s="12" t="s">
         <v>404</v>
       </c>
-      <c r="E93" s="10" t="s">
+      <c r="E93" s="13" t="s">
         <v>405</v>
       </c>
-      <c r="F93" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="G93" s="10" t="s">
+      <c r="F93" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="G93" s="13" t="s">
         <v>406</v>
       </c>
-      <c r="H93" s="9" t="s">
+      <c r="H93" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="I93" s="10" t="s">
+      <c r="I93" s="13" t="s">
         <v>408</v>
       </c>
-      <c r="J93" s="22"/>
-      <c r="K93" s="18">
-        <v>1</v>
-      </c>
-      <c r="L93" s="9"/>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A94" s="1"/>
-      <c r="B94" s="11">
-        <f>ROW(B94) - ROW($B$2)</f>
+      <c r="J93" s="19"/>
+      <c r="K93" s="20">
+        <v>1</v>
+      </c>
+      <c r="L93" s="12"/>
+    </row>
+    <row r="94" ht="15.75" spans="1:12">
+      <c r="A94" s="2"/>
+      <c r="B94" s="7">
+        <f>ROW(B94)-ROW($B$2)</f>
         <v>92</v>
       </c>
-      <c r="C94" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="D94" s="7" t="s">
+      <c r="C94" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="D94" s="9" t="s">
         <v>409</v>
       </c>
-      <c r="E94" s="8" t="s">
+      <c r="E94" s="10" t="s">
         <v>410</v>
       </c>
-      <c r="F94" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="G94" s="8" t="s">
+      <c r="F94" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="G94" s="10" t="s">
         <v>411</v>
       </c>
-      <c r="H94" s="7" t="s">
+      <c r="H94" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I94" s="8" t="s">
+      <c r="I94" s="10" t="s">
         <v>412</v>
       </c>
-      <c r="J94" s="21"/>
-      <c r="K94" s="17">
-        <v>1</v>
-      </c>
-      <c r="L94" s="7"/>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A95" s="1"/>
-      <c r="B95" s="11">
+      <c r="J94" s="17"/>
+      <c r="K94" s="18">
+        <v>1</v>
+      </c>
+      <c r="L94" s="9"/>
+    </row>
+    <row r="95" ht="15.75" spans="1:12">
+      <c r="A95" s="2"/>
+      <c r="B95" s="7">
         <f t="shared" si="0"/>
         <v>93</v>
       </c>
-      <c r="C95" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="D95" s="9" t="s">
+      <c r="C95" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="D95" s="12" t="s">
         <v>413</v>
       </c>
-      <c r="E95" s="10" t="s">
+      <c r="E95" s="13" t="s">
         <v>414</v>
       </c>
-      <c r="F95" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="G95" s="10" t="s">
+      <c r="F95" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="G95" s="13" t="s">
         <v>415</v>
       </c>
-      <c r="H95" s="9" t="s">
+      <c r="H95" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I95" s="10" t="s">
+      <c r="I95" s="13" t="s">
         <v>416</v>
       </c>
-      <c r="J95" s="22"/>
-      <c r="K95" s="18">
+      <c r="J95" s="19"/>
+      <c r="K95" s="20">
         <v>2</v>
       </c>
-      <c r="L95" s="9"/>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A96" s="1"/>
-      <c r="B96" s="11">
-        <f>ROW(B96) - ROW($B$2)</f>
+      <c r="L95" s="12"/>
+    </row>
+    <row r="96" ht="15.75" spans="1:12">
+      <c r="A96" s="2"/>
+      <c r="B96" s="7">
+        <f>ROW(B96)-ROW($B$2)</f>
         <v>94</v>
       </c>
-      <c r="C96" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="D96" s="7" t="s">
+      <c r="C96" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="D96" s="9" t="s">
         <v>417</v>
       </c>
-      <c r="E96" s="8" t="s">
+      <c r="E96" s="10" t="s">
         <v>418</v>
       </c>
-      <c r="F96" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="G96" s="8" t="s">
+      <c r="F96" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="G96" s="10" t="s">
         <v>419</v>
       </c>
-      <c r="H96" s="7" t="s">
+      <c r="H96" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I96" s="8" t="s">
+      <c r="I96" s="10" t="s">
         <v>420</v>
       </c>
-      <c r="J96" s="21"/>
-      <c r="K96" s="17">
-        <v>1</v>
-      </c>
-      <c r="L96" s="7"/>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A97" s="1"/>
-      <c r="B97" s="11">
+      <c r="J96" s="17"/>
+      <c r="K96" s="18">
+        <v>1</v>
+      </c>
+      <c r="L96" s="9"/>
+    </row>
+    <row r="97" ht="15.75" spans="1:12">
+      <c r="A97" s="2"/>
+      <c r="B97" s="7">
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
-      <c r="C97" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="D97" s="9" t="s">
+      <c r="C97" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="D97" s="12" t="s">
         <v>421</v>
       </c>
-      <c r="E97" s="10" t="s">
+      <c r="E97" s="13" t="s">
         <v>422</v>
       </c>
-      <c r="F97" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="G97" s="10" t="s">
+      <c r="F97" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="G97" s="13" t="s">
         <v>423</v>
       </c>
-      <c r="H97" s="9" t="s">
+      <c r="H97" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I97" s="10" t="s">
+      <c r="I97" s="13" t="s">
         <v>424</v>
       </c>
-      <c r="J97" s="22"/>
-      <c r="K97" s="18">
+      <c r="J97" s="19"/>
+      <c r="K97" s="20">
         <v>4</v>
       </c>
-      <c r="L97" s="9"/>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A98" s="1"/>
-      <c r="B98" s="11">
-        <f>ROW(B98) - ROW($B$2)</f>
+      <c r="L97" s="12"/>
+    </row>
+    <row r="98" ht="15.75" spans="1:12">
+      <c r="A98" s="2"/>
+      <c r="B98" s="7">
+        <f>ROW(B98)-ROW($B$2)</f>
         <v>96</v>
       </c>
-      <c r="C98" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="D98" s="7" t="s">
+      <c r="C98" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="D98" s="9" t="s">
         <v>425</v>
       </c>
-      <c r="E98" s="8" t="s">
+      <c r="E98" s="10" t="s">
         <v>426</v>
       </c>
-      <c r="F98" s="7" t="s">
+      <c r="F98" s="9" t="s">
         <v>427</v>
       </c>
-      <c r="G98" s="8" t="s">
+      <c r="G98" s="10" t="s">
         <v>428</v>
       </c>
-      <c r="H98" s="7" t="s">
+      <c r="H98" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I98" s="8" t="s">
+      <c r="I98" s="10" t="s">
         <v>429</v>
       </c>
-      <c r="J98" s="21"/>
-      <c r="K98" s="17">
-        <v>1</v>
-      </c>
-      <c r="L98" s="7"/>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A99" s="1"/>
-      <c r="B99" s="11">
+      <c r="J98" s="17"/>
+      <c r="K98" s="18">
+        <v>1</v>
+      </c>
+      <c r="L98" s="9"/>
+    </row>
+    <row r="99" ht="15.75" spans="1:12">
+      <c r="A99" s="2"/>
+      <c r="B99" s="7">
         <f t="shared" si="0"/>
         <v>97</v>
       </c>
-      <c r="C99" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="D99" s="9" t="s">
+      <c r="C99" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="D99" s="12" t="s">
         <v>430</v>
       </c>
-      <c r="E99" s="10" t="s">
+      <c r="E99" s="13" t="s">
         <v>431</v>
       </c>
-      <c r="F99" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="G99" s="10" t="s">
+      <c r="F99" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="G99" s="13" t="s">
         <v>432</v>
       </c>
-      <c r="H99" s="9" t="s">
+      <c r="H99" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I99" s="10" t="s">
+      <c r="I99" s="13" t="s">
         <v>433</v>
       </c>
-      <c r="J99" s="22"/>
-      <c r="K99" s="18">
-        <v>1</v>
-      </c>
-      <c r="L99" s="9"/>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A100" s="1"/>
-      <c r="B100" s="11">
-        <f>ROW(B100) - ROW($B$2)</f>
+      <c r="J99" s="19"/>
+      <c r="K99" s="20">
+        <v>1</v>
+      </c>
+      <c r="L99" s="12"/>
+    </row>
+    <row r="100" ht="15.75" spans="1:12">
+      <c r="A100" s="2"/>
+      <c r="B100" s="7">
+        <f>ROW(B100)-ROW($B$2)</f>
         <v>98</v>
       </c>
-      <c r="C100" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="D100" s="7" t="s">
+      <c r="C100" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="D100" s="9" t="s">
         <v>434</v>
       </c>
-      <c r="E100" s="8" t="s">
+      <c r="E100" s="10" t="s">
         <v>435</v>
       </c>
-      <c r="F100" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="G100" s="8" t="s">
+      <c r="F100" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="G100" s="10" t="s">
         <v>436</v>
       </c>
-      <c r="H100" s="7" t="s">
+      <c r="H100" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I100" s="8" t="s">
+      <c r="I100" s="10" t="s">
         <v>437</v>
       </c>
-      <c r="J100" s="21"/>
-      <c r="K100" s="17">
+      <c r="J100" s="17"/>
+      <c r="K100" s="18">
         <v>4</v>
       </c>
-      <c r="L100" s="7"/>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A101" s="1"/>
-      <c r="B101" s="11">
+      <c r="L100" s="9"/>
+    </row>
+    <row r="101" ht="15.75" spans="1:12">
+      <c r="A101" s="2"/>
+      <c r="B101" s="7">
         <f t="shared" si="0"/>
         <v>99</v>
       </c>
-      <c r="C101" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="D101" s="9" t="s">
+      <c r="C101" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="D101" s="12" t="s">
         <v>438</v>
       </c>
-      <c r="E101" s="10" t="s">
+      <c r="E101" s="13" t="s">
         <v>439</v>
       </c>
-      <c r="F101" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="G101" s="10" t="s">
+      <c r="F101" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="G101" s="13" t="s">
         <v>440</v>
       </c>
-      <c r="H101" s="9" t="s">
+      <c r="H101" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I101" s="10" t="s">
+      <c r="I101" s="13" t="s">
         <v>441</v>
       </c>
-      <c r="J101" s="22"/>
-      <c r="K101" s="18">
-        <v>1</v>
-      </c>
-      <c r="L101" s="9"/>
-    </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A102" s="1"/>
-      <c r="B102" s="11">
+      <c r="J101" s="19"/>
+      <c r="K101" s="20">
+        <v>1</v>
+      </c>
+      <c r="L101" s="12"/>
+    </row>
+    <row r="102" ht="15.75" spans="1:12">
+      <c r="A102" s="2"/>
+      <c r="B102" s="7">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="C102" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="D102" s="7" t="s">
+      <c r="C102" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="D102" s="9" t="s">
         <v>442</v>
       </c>
-      <c r="E102" s="8" t="s">
+      <c r="E102" s="10" t="s">
         <v>443</v>
       </c>
-      <c r="F102" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="G102" s="8" t="s">
+      <c r="F102" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="G102" s="10" t="s">
         <v>444</v>
       </c>
-      <c r="H102" s="7" t="s">
+      <c r="H102" s="9" t="s">
         <v>445</v>
       </c>
-      <c r="I102" s="8" t="s">
+      <c r="I102" s="10" t="s">
         <v>446</v>
       </c>
-      <c r="J102" s="21"/>
-      <c r="K102" s="17">
-        <v>1</v>
-      </c>
-      <c r="L102" s="7"/>
-    </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A103" s="1"/>
-      <c r="B103" s="11">
+      <c r="J102" s="17"/>
+      <c r="K102" s="18">
+        <v>1</v>
+      </c>
+      <c r="L102" s="9"/>
+    </row>
+    <row r="103" ht="15.75" spans="1:12">
+      <c r="A103" s="2"/>
+      <c r="B103" s="7">
         <f t="shared" si="0"/>
         <v>101</v>
       </c>
-      <c r="C103" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="D103" s="9" t="s">
+      <c r="C103" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="D103" s="12" t="s">
         <v>447</v>
       </c>
-      <c r="E103" s="10" t="s">
+      <c r="E103" s="13" t="s">
         <v>448</v>
       </c>
-      <c r="F103" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="G103" s="10" t="s">
+      <c r="F103" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="G103" s="13" t="s">
         <v>449</v>
       </c>
-      <c r="H103" s="9" t="s">
+      <c r="H103" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I103" s="10" t="s">
+      <c r="I103" s="13" t="s">
         <v>450</v>
       </c>
-      <c r="J103" s="22"/>
-      <c r="K103" s="18">
-        <v>1</v>
-      </c>
-      <c r="L103" s="9"/>
-    </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A104" s="1"/>
-      <c r="B104" s="11">
+      <c r="J103" s="19"/>
+      <c r="K103" s="20">
+        <v>1</v>
+      </c>
+      <c r="L103" s="12"/>
+    </row>
+    <row r="104" ht="15.75" spans="1:12">
+      <c r="A104" s="2"/>
+      <c r="B104" s="7">
         <f t="shared" si="0"/>
         <v>102</v>
       </c>
-      <c r="C104" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="D104" s="7" t="s">
+      <c r="C104" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="D104" s="9" t="s">
         <v>451</v>
       </c>
-      <c r="E104" s="8" t="s">
+      <c r="E104" s="10" t="s">
         <v>452</v>
       </c>
-      <c r="F104" s="7" t="s">
+      <c r="F104" s="9" t="s">
         <v>341</v>
       </c>
-      <c r="G104" s="8" t="s">
+      <c r="G104" s="10" t="s">
         <v>453</v>
       </c>
-      <c r="H104" s="7" t="s">
+      <c r="H104" s="9" t="s">
         <v>454</v>
       </c>
-      <c r="I104" s="8" t="s">
+      <c r="I104" s="10" t="s">
         <v>455</v>
       </c>
-      <c r="J104" s="21"/>
-      <c r="K104" s="17">
-        <v>1</v>
-      </c>
-      <c r="L104" s="7"/>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A105" s="1"/>
-      <c r="B105" s="11">
+      <c r="J104" s="17"/>
+      <c r="K104" s="18">
+        <v>1</v>
+      </c>
+      <c r="L104" s="9"/>
+    </row>
+    <row r="105" ht="15.75" spans="1:12">
+      <c r="A105" s="2"/>
+      <c r="B105" s="7">
         <f t="shared" si="0"/>
         <v>103</v>
       </c>
-      <c r="C105" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="D105" s="9" t="s">
+      <c r="C105" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="D105" s="12" t="s">
         <v>456</v>
       </c>
-      <c r="E105" s="10" t="s">
+      <c r="E105" s="13" t="s">
         <v>457</v>
       </c>
-      <c r="F105" s="9" t="s">
+      <c r="F105" s="12" t="s">
         <v>341</v>
       </c>
-      <c r="G105" s="10" t="s">
+      <c r="G105" s="13" t="s">
         <v>458</v>
       </c>
-      <c r="H105" s="9" t="s">
+      <c r="H105" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I105" s="10" t="s">
+      <c r="I105" s="13" t="s">
         <v>399</v>
       </c>
-      <c r="J105" s="22"/>
-      <c r="K105" s="18">
-        <v>1</v>
-      </c>
-      <c r="L105" s="9"/>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A106" s="1"/>
-      <c r="B106" s="11">
+      <c r="J105" s="19"/>
+      <c r="K105" s="20">
+        <v>1</v>
+      </c>
+      <c r="L105" s="12"/>
+    </row>
+    <row r="106" ht="15.75" spans="1:12">
+      <c r="A106" s="2"/>
+      <c r="B106" s="7">
         <f t="shared" si="0"/>
         <v>104</v>
       </c>
-      <c r="C106" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="D106" s="7" t="s">
+      <c r="C106" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="D106" s="9" t="s">
         <v>459</v>
       </c>
-      <c r="E106" s="8" t="s">
+      <c r="E106" s="10" t="s">
         <v>460</v>
       </c>
-      <c r="F106" s="7" t="s">
+      <c r="F106" s="9" t="s">
         <v>341</v>
       </c>
-      <c r="G106" s="8" t="s">
+      <c r="G106" s="10" t="s">
         <v>461</v>
       </c>
-      <c r="H106" s="7" t="s">
+      <c r="H106" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I106" s="8" t="s">
+      <c r="I106" s="10" t="s">
         <v>462</v>
       </c>
-      <c r="J106" s="21"/>
-      <c r="K106" s="17">
-        <v>1</v>
-      </c>
-      <c r="L106" s="7"/>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A107" s="1"/>
-      <c r="B107" s="11">
+      <c r="J106" s="17"/>
+      <c r="K106" s="18">
+        <v>1</v>
+      </c>
+      <c r="L106" s="9"/>
+    </row>
+    <row r="107" ht="15.75" spans="1:12">
+      <c r="A107" s="2"/>
+      <c r="B107" s="7">
         <f t="shared" si="0"/>
         <v>105</v>
       </c>
-      <c r="C107" s="13" t="s">
+      <c r="C107" s="11" t="s">
         <v>463</v>
       </c>
-      <c r="D107" s="9" t="s">
+      <c r="D107" s="12" t="s">
         <v>464</v>
       </c>
-      <c r="E107" s="10" t="s">
+      <c r="E107" s="13" t="s">
         <v>465</v>
       </c>
-      <c r="F107" s="9" t="s">
+      <c r="F107" s="12" t="s">
         <v>466</v>
       </c>
-      <c r="G107" s="10" t="s">
+      <c r="G107" s="13" t="s">
         <v>466</v>
       </c>
-      <c r="H107" s="9" t="s">
+      <c r="H107" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I107" s="10" t="s">
+      <c r="I107" s="13" t="s">
         <v>347</v>
       </c>
-      <c r="J107" s="22"/>
-      <c r="K107" s="18">
+      <c r="J107" s="19"/>
+      <c r="K107" s="20">
         <v>3</v>
       </c>
-      <c r="L107" s="9"/>
-    </row>
-    <row r="108" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A108" s="1"/>
-      <c r="B108" s="11">
+      <c r="L107" s="12"/>
+    </row>
+    <row r="108" ht="24.75" spans="1:12">
+      <c r="A108" s="2"/>
+      <c r="B108" s="7">
         <f t="shared" si="0"/>
         <v>106</v>
       </c>
-      <c r="C108" s="12" t="s">
+      <c r="C108" s="8" t="s">
         <v>467</v>
       </c>
-      <c r="D108" s="7" t="s">
+      <c r="D108" s="9" t="s">
         <v>468</v>
       </c>
-      <c r="E108" s="8" t="s">
+      <c r="E108" s="10" t="s">
         <v>469</v>
       </c>
-      <c r="F108" s="7" t="s">
+      <c r="F108" s="9" t="s">
         <v>470</v>
       </c>
-      <c r="G108" s="8" t="s">
+      <c r="G108" s="10" t="s">
         <v>470</v>
       </c>
-      <c r="H108" s="7" t="s">
+      <c r="H108" s="9" t="s">
         <v>471</v>
       </c>
-      <c r="I108" s="8" t="s">
+      <c r="I108" s="10" t="s">
         <v>347</v>
       </c>
-      <c r="J108" s="21"/>
-      <c r="K108" s="17">
-        <v>1</v>
-      </c>
-      <c r="L108" s="7"/>
-    </row>
-    <row r="109" spans="1:12" ht="36" x14ac:dyDescent="0.25">
-      <c r="A109" s="1"/>
-      <c r="B109" s="11">
+      <c r="J108" s="17"/>
+      <c r="K108" s="18">
+        <v>1</v>
+      </c>
+      <c r="L108" s="9"/>
+    </row>
+    <row r="109" ht="36.75" spans="1:12">
+      <c r="A109" s="2"/>
+      <c r="B109" s="7">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
-      <c r="C109" s="12" t="s">
+      <c r="C109" s="8" t="s">
         <v>472</v>
       </c>
-      <c r="D109" s="9" t="s">
+      <c r="D109" s="12" t="s">
         <v>473</v>
       </c>
-      <c r="E109" s="10" t="s">
+      <c r="E109" s="13" t="s">
         <v>474</v>
       </c>
-      <c r="F109" s="9" t="s">
+      <c r="F109" s="12" t="s">
         <v>475</v>
       </c>
-      <c r="G109" s="10" t="s">
+      <c r="G109" s="13" t="s">
         <v>476</v>
       </c>
-      <c r="H109" s="9" t="s">
+      <c r="H109" s="12" t="s">
         <v>477</v>
       </c>
-      <c r="I109" s="10" t="s">
+      <c r="I109" s="13" t="s">
         <v>476</v>
       </c>
-      <c r="J109" s="22"/>
-      <c r="K109" s="18">
-        <v>1</v>
-      </c>
-      <c r="L109" s="9"/>
-    </row>
-    <row r="110" spans="1:12" ht="36" x14ac:dyDescent="0.25">
-      <c r="A110" s="1"/>
-      <c r="B110" s="11">
+      <c r="J109" s="19"/>
+      <c r="K109" s="20">
+        <v>1</v>
+      </c>
+      <c r="L109" s="12"/>
+    </row>
+    <row r="110" ht="36.75" spans="1:12">
+      <c r="A110" s="2"/>
+      <c r="B110" s="7">
         <f t="shared" si="0"/>
         <v>108</v>
       </c>
-      <c r="C110" s="12" t="s">
+      <c r="C110" s="8" t="s">
         <v>472</v>
       </c>
-      <c r="D110" s="7" t="s">
+      <c r="D110" s="9" t="s">
         <v>478</v>
       </c>
-      <c r="E110" s="8" t="s">
+      <c r="E110" s="10" t="s">
         <v>479</v>
       </c>
-      <c r="F110" s="7" t="s">
+      <c r="F110" s="9" t="s">
         <v>480</v>
       </c>
-      <c r="G110" s="8" t="s">
+      <c r="G110" s="10" t="s">
         <v>480</v>
       </c>
-      <c r="H110" s="7" t="s">
+      <c r="H110" s="9" t="s">
         <v>481</v>
       </c>
-      <c r="I110" s="8" t="s">
+      <c r="I110" s="10" t="s">
         <v>480</v>
       </c>
-      <c r="J110" s="21"/>
-      <c r="K110" s="17">
-        <v>1</v>
-      </c>
-      <c r="L110" s="7"/>
-    </row>
-    <row r="111" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A111" s="1"/>
-      <c r="B111" s="11">
+      <c r="J110" s="17"/>
+      <c r="K110" s="18">
+        <v>1</v>
+      </c>
+      <c r="L110" s="9"/>
+    </row>
+    <row r="111" ht="24.75" spans="1:12">
+      <c r="A111" s="2"/>
+      <c r="B111" s="7">
         <f t="shared" si="0"/>
         <v>109</v>
       </c>
-      <c r="C111" s="13" t="s">
+      <c r="C111" s="11" t="s">
         <v>482</v>
       </c>
-      <c r="D111" s="9" t="s">
+      <c r="D111" s="12" t="s">
         <v>483</v>
       </c>
-      <c r="E111" s="10" t="s">
+      <c r="E111" s="13" t="s">
         <v>484</v>
       </c>
-      <c r="F111" s="9" t="s">
+      <c r="F111" s="12" t="s">
         <v>485</v>
       </c>
-      <c r="G111" s="10" t="s">
+      <c r="G111" s="13" t="s">
         <v>485</v>
       </c>
-      <c r="H111" s="9" t="s">
+      <c r="H111" s="12" t="s">
         <v>486</v>
       </c>
-      <c r="I111" s="10" t="s">
+      <c r="I111" s="13" t="s">
         <v>485</v>
       </c>
-      <c r="J111" s="22"/>
-      <c r="K111" s="18">
-        <v>1</v>
-      </c>
-      <c r="L111" s="9"/>
-    </row>
-    <row r="112" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A112" s="1"/>
-      <c r="B112" s="11">
+      <c r="J111" s="19"/>
+      <c r="K111" s="20">
+        <v>1</v>
+      </c>
+      <c r="L111" s="12"/>
+    </row>
+    <row r="112" ht="24.75" spans="1:12">
+      <c r="A112" s="2"/>
+      <c r="B112" s="7">
         <f t="shared" si="0"/>
         <v>110</v>
       </c>
-      <c r="C112" s="12" t="s">
+      <c r="C112" s="8" t="s">
         <v>487</v>
       </c>
-      <c r="D112" s="7" t="s">
+      <c r="D112" s="9" t="s">
         <v>488</v>
       </c>
-      <c r="E112" s="8" t="s">
+      <c r="E112" s="10" t="s">
         <v>489</v>
       </c>
-      <c r="F112" s="7" t="s">
+      <c r="F112" s="9" t="s">
         <v>490</v>
       </c>
-      <c r="G112" s="8" t="s">
+      <c r="G112" s="10" t="s">
         <v>490</v>
       </c>
-      <c r="H112" s="7" t="s">
+      <c r="H112" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="I112" s="8" t="s">
+      <c r="I112" s="10" t="s">
         <v>490</v>
       </c>
-      <c r="J112" s="21"/>
-      <c r="K112" s="17">
-        <v>1</v>
-      </c>
-      <c r="L112" s="7"/>
-    </row>
-    <row r="113" spans="1:12" ht="48" x14ac:dyDescent="0.25">
-      <c r="A113" s="1"/>
-      <c r="B113" s="11">
+      <c r="J112" s="17"/>
+      <c r="K112" s="18">
+        <v>1</v>
+      </c>
+      <c r="L112" s="9"/>
+    </row>
+    <row r="113" ht="48.75" spans="1:12">
+      <c r="A113" s="2"/>
+      <c r="B113" s="7">
         <f t="shared" si="0"/>
         <v>111</v>
       </c>
-      <c r="C113" s="13" t="s">
+      <c r="C113" s="11" t="s">
         <v>491</v>
       </c>
-      <c r="D113" s="9" t="s">
+      <c r="D113" s="12" t="s">
         <v>492</v>
       </c>
-      <c r="E113" s="10" t="s">
+      <c r="E113" s="13" t="s">
         <v>493</v>
       </c>
-      <c r="F113" s="9" t="s">
+      <c r="F113" s="12" t="s">
         <v>494</v>
       </c>
-      <c r="G113" s="10" t="s">
+      <c r="G113" s="13" t="s">
         <v>495</v>
       </c>
-      <c r="H113" s="9" t="s">
+      <c r="H113" s="12" t="s">
         <v>496</v>
       </c>
-      <c r="I113" s="10" t="s">
+      <c r="I113" s="13" t="s">
         <v>495</v>
       </c>
-      <c r="J113" s="22"/>
-      <c r="K113" s="18">
-        <v>1</v>
-      </c>
-      <c r="L113" s="9"/>
-    </row>
-    <row r="114" spans="1:12" ht="48" x14ac:dyDescent="0.25">
-      <c r="A114" s="1"/>
-      <c r="B114" s="11">
+      <c r="J113" s="19"/>
+      <c r="K113" s="20">
+        <v>1</v>
+      </c>
+      <c r="L113" s="12"/>
+    </row>
+    <row r="114" ht="48.75" spans="1:12">
+      <c r="A114" s="2"/>
+      <c r="B114" s="7">
         <f t="shared" si="0"/>
         <v>112</v>
       </c>
-      <c r="C114" s="12" t="s">
+      <c r="C114" s="8" t="s">
         <v>491</v>
       </c>
-      <c r="D114" s="7" t="s">
+      <c r="D114" s="9" t="s">
         <v>497</v>
       </c>
-      <c r="E114" s="8" t="s">
+      <c r="E114" s="10" t="s">
         <v>498</v>
       </c>
-      <c r="F114" s="7" t="s">
+      <c r="F114" s="9" t="s">
         <v>494</v>
       </c>
-      <c r="G114" s="8" t="s">
+      <c r="G114" s="10" t="s">
         <v>499</v>
       </c>
-      <c r="H114" s="7" t="s">
+      <c r="H114" s="9" t="s">
         <v>496</v>
       </c>
-      <c r="I114" s="8" t="s">
+      <c r="I114" s="10" t="s">
         <v>499</v>
       </c>
-      <c r="J114" s="21"/>
-      <c r="K114" s="17">
-        <v>1</v>
-      </c>
-      <c r="L114" s="7"/>
-    </row>
-    <row r="115" spans="1:12" ht="36" x14ac:dyDescent="0.25">
-      <c r="A115" s="1"/>
-      <c r="B115" s="11">
+      <c r="J114" s="17"/>
+      <c r="K114" s="18">
+        <v>1</v>
+      </c>
+      <c r="L114" s="9"/>
+    </row>
+    <row r="115" ht="36.75" spans="1:12">
+      <c r="A115" s="2"/>
+      <c r="B115" s="7">
         <f t="shared" si="0"/>
         <v>113</v>
       </c>
-      <c r="C115" s="13" t="s">
+      <c r="C115" s="11" t="s">
         <v>491</v>
       </c>
-      <c r="D115" s="9" t="s">
+      <c r="D115" s="12" t="s">
         <v>500</v>
       </c>
-      <c r="E115" s="10" t="s">
+      <c r="E115" s="13" t="s">
         <v>501</v>
       </c>
-      <c r="F115" s="9" t="s">
+      <c r="F115" s="12" t="s">
         <v>502</v>
       </c>
-      <c r="G115" s="10" t="s">
+      <c r="G115" s="13" t="s">
         <v>503</v>
       </c>
-      <c r="H115" s="9" t="s">
+      <c r="H115" s="12" t="s">
         <v>504</v>
       </c>
-      <c r="I115" s="10" t="s">
+      <c r="I115" s="13" t="s">
         <v>503</v>
       </c>
-      <c r="J115" s="22"/>
-      <c r="K115" s="18">
-        <v>1</v>
-      </c>
-      <c r="L115" s="9"/>
-    </row>
-    <row r="116" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A116" s="1"/>
-      <c r="B116" s="11">
+      <c r="J115" s="19"/>
+      <c r="K115" s="20">
+        <v>1</v>
+      </c>
+      <c r="L115" s="12"/>
+    </row>
+    <row r="116" ht="15.75" spans="1:12">
+      <c r="A116" s="2"/>
+      <c r="B116" s="7">
         <f t="shared" si="0"/>
         <v>114</v>
       </c>
-      <c r="C116" s="12" t="s">
+      <c r="C116" s="8" t="s">
         <v>491</v>
       </c>
-      <c r="D116" s="7" t="s">
+      <c r="D116" s="9" t="s">
         <v>505</v>
       </c>
-      <c r="E116" s="8" t="s">
+      <c r="E116" s="10" t="s">
         <v>506</v>
       </c>
-      <c r="F116" s="7" t="s">
+      <c r="F116" s="9" t="s">
         <v>507</v>
       </c>
-      <c r="G116" s="8" t="s">
+      <c r="G116" s="10" t="s">
         <v>508</v>
       </c>
-      <c r="H116" s="7" t="s">
+      <c r="H116" s="9" t="s">
         <v>509</v>
       </c>
-      <c r="I116" s="8" t="s">
+      <c r="I116" s="10" t="s">
         <v>508</v>
       </c>
-      <c r="J116" s="21"/>
-      <c r="K116" s="17">
-        <v>1</v>
-      </c>
-      <c r="L116" s="7"/>
-    </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A117" s="1"/>
-      <c r="B117" s="11">
+      <c r="J116" s="17"/>
+      <c r="K116" s="18">
+        <v>1</v>
+      </c>
+      <c r="L116" s="9"/>
+    </row>
+    <row r="117" ht="15.75" spans="1:12">
+      <c r="A117" s="2"/>
+      <c r="B117" s="7">
         <f t="shared" si="0"/>
         <v>115</v>
       </c>
-      <c r="C117" s="13" t="s">
+      <c r="C117" s="11" t="s">
         <v>491</v>
       </c>
-      <c r="D117" s="9" t="s">
+      <c r="D117" s="12" t="s">
         <v>510</v>
       </c>
-      <c r="E117" s="10" t="s">
+      <c r="E117" s="13" t="s">
         <v>511</v>
       </c>
-      <c r="F117" s="9" t="s">
+      <c r="F117" s="12" t="s">
         <v>512</v>
       </c>
-      <c r="G117" s="10" t="s">
+      <c r="G117" s="13" t="s">
         <v>513</v>
       </c>
-      <c r="H117" s="9" t="s">
+      <c r="H117" s="12" t="s">
         <v>514</v>
       </c>
-      <c r="I117" s="10" t="s">
+      <c r="I117" s="13" t="s">
         <v>513</v>
       </c>
-      <c r="J117" s="22"/>
-      <c r="K117" s="18">
-        <v>1</v>
-      </c>
-      <c r="L117" s="9"/>
-    </row>
-    <row r="118" spans="1:12" ht="36" x14ac:dyDescent="0.25">
-      <c r="A118" s="1"/>
-      <c r="B118" s="11">
+      <c r="J117" s="19"/>
+      <c r="K117" s="20">
+        <v>1</v>
+      </c>
+      <c r="L117" s="12"/>
+    </row>
+    <row r="118" ht="36.75" spans="1:12">
+      <c r="A118" s="2"/>
+      <c r="B118" s="7">
         <f t="shared" si="0"/>
         <v>116</v>
       </c>
-      <c r="C118" s="12" t="s">
+      <c r="C118" s="8" t="s">
         <v>491</v>
       </c>
-      <c r="D118" s="7" t="s">
+      <c r="D118" s="9" t="s">
         <v>515</v>
       </c>
-      <c r="E118" s="8" t="s">
+      <c r="E118" s="10" t="s">
         <v>516</v>
       </c>
-      <c r="F118" s="7" t="s">
+      <c r="F118" s="9" t="s">
         <v>517</v>
       </c>
-      <c r="G118" s="8" t="s">
+      <c r="G118" s="10" t="s">
         <v>518</v>
       </c>
-      <c r="H118" s="7" t="s">
+      <c r="H118" s="9" t="s">
         <v>519</v>
       </c>
-      <c r="I118" s="8" t="s">
+      <c r="I118" s="10" t="s">
         <v>518</v>
       </c>
-      <c r="J118" s="21"/>
-      <c r="K118" s="17">
-        <v>1</v>
-      </c>
-      <c r="L118" s="7"/>
-    </row>
-    <row r="119" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A119" s="1"/>
-      <c r="B119" s="11">
+      <c r="J118" s="17"/>
+      <c r="K118" s="18">
+        <v>1</v>
+      </c>
+      <c r="L118" s="9"/>
+    </row>
+    <row r="119" ht="26.25" spans="1:12">
+      <c r="A119" s="2"/>
+      <c r="B119" s="7">
         <f t="shared" si="0"/>
         <v>117</v>
       </c>
-      <c r="C119" s="13" t="s">
+      <c r="C119" s="11" t="s">
         <v>520</v>
       </c>
-      <c r="D119" s="9" t="s">
+      <c r="D119" s="12" t="s">
         <v>521</v>
       </c>
-      <c r="E119" s="10" t="s">
+      <c r="E119" s="13" t="s">
         <v>522</v>
       </c>
-      <c r="F119" s="9" t="s">
+      <c r="F119" s="12" t="s">
         <v>523</v>
       </c>
-      <c r="G119" s="10" t="s">
+      <c r="G119" s="13" t="s">
         <v>524</v>
       </c>
-      <c r="H119" s="9" t="s">
+      <c r="H119" s="12" t="s">
         <v>525</v>
       </c>
-      <c r="I119" s="10" t="s">
+      <c r="I119" s="13" t="s">
         <v>524</v>
       </c>
-      <c r="J119" s="22"/>
-      <c r="K119" s="18">
-        <v>1</v>
-      </c>
-      <c r="L119" s="9"/>
-    </row>
-    <row r="120" spans="1:12" ht="36" x14ac:dyDescent="0.25">
-      <c r="A120" s="1"/>
-      <c r="B120" s="11">
+      <c r="J119" s="19"/>
+      <c r="K119" s="20">
+        <v>1</v>
+      </c>
+      <c r="L119" s="12"/>
+    </row>
+    <row r="120" ht="36.75" spans="1:12">
+      <c r="A120" s="2"/>
+      <c r="B120" s="7">
         <f t="shared" si="0"/>
         <v>118</v>
       </c>
-      <c r="C120" s="12" t="s">
+      <c r="C120" s="8" t="s">
         <v>526</v>
       </c>
-      <c r="D120" s="7" t="s">
+      <c r="D120" s="9" t="s">
         <v>527</v>
       </c>
-      <c r="E120" s="8" t="s">
+      <c r="E120" s="10" t="s">
         <v>528</v>
       </c>
-      <c r="F120" s="7" t="s">
+      <c r="F120" s="9" t="s">
         <v>529</v>
       </c>
-      <c r="G120" s="8" t="s">
+      <c r="G120" s="10" t="s">
         <v>529</v>
       </c>
-      <c r="H120" s="7" t="s">
+      <c r="H120" s="9" t="s">
         <v>530</v>
       </c>
-      <c r="I120" s="8" t="s">
+      <c r="I120" s="10" t="s">
         <v>529</v>
       </c>
-      <c r="J120" s="21"/>
-      <c r="K120" s="17">
-        <v>1</v>
-      </c>
-      <c r="L120" s="7"/>
-    </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A121" s="1"/>
-      <c r="B121" s="11">
+      <c r="J120" s="17"/>
+      <c r="K120" s="18">
+        <v>1</v>
+      </c>
+      <c r="L120" s="9"/>
+    </row>
+    <row r="121" ht="15.75" spans="1:12">
+      <c r="A121" s="2"/>
+      <c r="B121" s="7">
         <f t="shared" si="0"/>
         <v>119</v>
       </c>
-      <c r="C121" s="13" t="s">
+      <c r="C121" s="11" t="s">
         <v>531</v>
       </c>
-      <c r="D121" s="9" t="s">
+      <c r="D121" s="12" t="s">
         <v>532</v>
       </c>
-      <c r="E121" s="10" t="s">
+      <c r="E121" s="13" t="s">
         <v>533</v>
       </c>
-      <c r="F121" s="9" t="s">
+      <c r="F121" s="12" t="s">
         <v>534</v>
       </c>
-      <c r="G121" s="10" t="s">
+      <c r="G121" s="13" t="s">
         <v>534</v>
       </c>
-      <c r="H121" s="9" t="s">
+      <c r="H121" s="12" t="s">
         <v>535</v>
       </c>
-      <c r="I121" s="10" t="s">
+      <c r="I121" s="13" t="s">
         <v>534</v>
       </c>
-      <c r="J121" s="22"/>
-      <c r="K121" s="18">
-        <v>1</v>
-      </c>
-      <c r="L121" s="9"/>
-    </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A122" s="1"/>
-      <c r="B122" s="11">
+      <c r="J121" s="19"/>
+      <c r="K121" s="20">
+        <v>1</v>
+      </c>
+      <c r="L121" s="12"/>
+    </row>
+    <row r="122" ht="15.75" spans="1:12">
+      <c r="A122" s="2"/>
+      <c r="B122" s="7">
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
-      <c r="C122" s="12" t="s">
+      <c r="C122" s="8" t="s">
         <v>491</v>
       </c>
-      <c r="D122" s="7" t="s">
+      <c r="D122" s="9" t="s">
         <v>536</v>
       </c>
-      <c r="E122" s="8" t="s">
+      <c r="E122" s="10" t="s">
         <v>537</v>
       </c>
-      <c r="F122" s="7" t="s">
+      <c r="F122" s="9" t="s">
         <v>538</v>
       </c>
-      <c r="G122" s="8" t="s">
+      <c r="G122" s="10" t="s">
         <v>539</v>
       </c>
-      <c r="H122" s="7" t="s">
+      <c r="H122" s="9" t="s">
         <v>540</v>
       </c>
-      <c r="I122" s="8" t="s">
+      <c r="I122" s="10" t="s">
         <v>539</v>
       </c>
-      <c r="J122" s="21"/>
-      <c r="K122" s="17">
-        <v>1</v>
-      </c>
-      <c r="L122" s="7"/>
-    </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A123" s="1"/>
-      <c r="B123" s="11">
+      <c r="J122" s="17"/>
+      <c r="K122" s="18">
+        <v>1</v>
+      </c>
+      <c r="L122" s="9"/>
+    </row>
+    <row r="123" ht="15.75" spans="1:12">
+      <c r="A123" s="2"/>
+      <c r="B123" s="7">
         <f t="shared" si="0"/>
         <v>121</v>
       </c>
-      <c r="C123" s="13" t="s">
+      <c r="C123" s="11" t="s">
         <v>491</v>
       </c>
-      <c r="D123" s="9" t="s">
+      <c r="D123" s="12" t="s">
         <v>541</v>
       </c>
-      <c r="E123" s="10" t="s">
+      <c r="E123" s="13" t="s">
         <v>542</v>
       </c>
-      <c r="F123" s="9" t="s">
+      <c r="F123" s="12" t="s">
         <v>543</v>
       </c>
-      <c r="G123" s="10" t="s">
+      <c r="G123" s="13" t="s">
         <v>544</v>
       </c>
-      <c r="H123" s="9" t="s">
+      <c r="H123" s="12" t="s">
         <v>514</v>
       </c>
-      <c r="I123" s="10" t="s">
+      <c r="I123" s="13" t="s">
         <v>544</v>
       </c>
-      <c r="J123" s="22"/>
-      <c r="K123" s="18">
-        <v>1</v>
-      </c>
-      <c r="L123" s="9"/>
-    </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A124" s="1"/>
-      <c r="B124" s="11">
+      <c r="J123" s="19"/>
+      <c r="K123" s="20">
+        <v>1</v>
+      </c>
+      <c r="L123" s="12"/>
+    </row>
+    <row r="124" ht="15.75" spans="1:12">
+      <c r="A124" s="2"/>
+      <c r="B124" s="7">
         <f t="shared" si="0"/>
         <v>122</v>
       </c>
-      <c r="C124" s="12" t="s">
+      <c r="C124" s="8" t="s">
         <v>491</v>
       </c>
-      <c r="D124" s="7" t="s">
+      <c r="D124" s="9" t="s">
         <v>545</v>
       </c>
-      <c r="E124" s="8" t="s">
+      <c r="E124" s="10" t="s">
         <v>546</v>
       </c>
-      <c r="F124" s="7" t="s">
+      <c r="F124" s="9" t="s">
         <v>547</v>
       </c>
-      <c r="G124" s="8" t="s">
+      <c r="G124" s="10" t="s">
         <v>548</v>
       </c>
-      <c r="H124" s="7" t="s">
+      <c r="H124" s="9" t="s">
         <v>549</v>
       </c>
-      <c r="I124" s="8" t="s">
+      <c r="I124" s="10" t="s">
         <v>548</v>
       </c>
-      <c r="J124" s="21"/>
-      <c r="K124" s="17">
-        <v>1</v>
-      </c>
-      <c r="L124" s="7"/>
-    </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A125" s="1"/>
-      <c r="B125" s="11">
+      <c r="J124" s="17"/>
+      <c r="K124" s="18">
+        <v>1</v>
+      </c>
+      <c r="L124" s="9"/>
+    </row>
+    <row r="125" ht="15.75" spans="1:12">
+      <c r="A125" s="2"/>
+      <c r="B125" s="7">
         <f t="shared" si="0"/>
         <v>123</v>
       </c>
-      <c r="C125" s="13" t="s">
+      <c r="C125" s="11" t="s">
         <v>491</v>
       </c>
-      <c r="D125" s="9" t="s">
+      <c r="D125" s="12" t="s">
         <v>550</v>
       </c>
-      <c r="E125" s="10" t="s">
+      <c r="E125" s="13" t="s">
         <v>551</v>
       </c>
-      <c r="F125" s="9" t="s">
+      <c r="F125" s="12" t="s">
         <v>552</v>
       </c>
-      <c r="G125" s="10" t="s">
+      <c r="G125" s="13" t="s">
         <v>553</v>
       </c>
-      <c r="H125" s="9" t="s">
+      <c r="H125" s="12" t="s">
         <v>549</v>
       </c>
-      <c r="I125" s="10" t="s">
+      <c r="I125" s="13" t="s">
         <v>553</v>
       </c>
-      <c r="J125" s="22"/>
-      <c r="K125" s="18">
-        <v>1</v>
-      </c>
-      <c r="L125" s="9"/>
-    </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A126" s="1"/>
-      <c r="B126" s="11">
+      <c r="J125" s="19"/>
+      <c r="K125" s="20">
+        <v>1</v>
+      </c>
+      <c r="L125" s="12"/>
+    </row>
+    <row r="126" ht="15.75" spans="1:12">
+      <c r="A126" s="2"/>
+      <c r="B126" s="7">
         <f t="shared" si="0"/>
         <v>124</v>
       </c>
-      <c r="C126" s="12" t="s">
+      <c r="C126" s="8" t="s">
         <v>491</v>
       </c>
-      <c r="D126" s="7" t="s">
+      <c r="D126" s="9" t="s">
         <v>554</v>
       </c>
-      <c r="E126" s="8" t="s">
+      <c r="E126" s="10" t="s">
         <v>555</v>
       </c>
-      <c r="F126" s="7" t="s">
+      <c r="F126" s="9" t="s">
         <v>556</v>
       </c>
-      <c r="G126" s="8" t="s">
+      <c r="G126" s="10" t="s">
         <v>557</v>
       </c>
-      <c r="H126" s="7" t="s">
+      <c r="H126" s="9" t="s">
         <v>558</v>
       </c>
-      <c r="I126" s="8" t="s">
+      <c r="I126" s="10" t="s">
         <v>557</v>
       </c>
-      <c r="J126" s="21"/>
-      <c r="K126" s="17">
-        <v>1</v>
-      </c>
-      <c r="L126" s="7"/>
-    </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A127" s="1"/>
-      <c r="B127" s="11">
+      <c r="J126" s="17"/>
+      <c r="K126" s="18">
+        <v>1</v>
+      </c>
+      <c r="L126" s="9"/>
+    </row>
+    <row r="127" ht="15.75" spans="1:12">
+      <c r="A127" s="2"/>
+      <c r="B127" s="7">
         <f t="shared" si="0"/>
         <v>125</v>
       </c>
-      <c r="C127" s="13" t="s">
+      <c r="C127" s="11" t="s">
         <v>559</v>
       </c>
-      <c r="D127" s="9" t="s">
+      <c r="D127" s="12" t="s">
         <v>560</v>
       </c>
-      <c r="E127" s="10" t="s">
+      <c r="E127" s="13" t="s">
         <v>561</v>
       </c>
-      <c r="F127" s="9" t="s">
+      <c r="F127" s="12" t="s">
         <v>562</v>
       </c>
-      <c r="G127" s="10" t="s">
+      <c r="G127" s="13" t="s">
         <v>563</v>
       </c>
-      <c r="H127" s="9" t="s">
+      <c r="H127" s="12" t="s">
         <v>564</v>
       </c>
-      <c r="I127" s="10" t="s">
+      <c r="I127" s="13" t="s">
         <v>565</v>
       </c>
-      <c r="J127" s="22"/>
-      <c r="K127" s="18">
-        <v>1</v>
-      </c>
-      <c r="L127" s="9"/>
-    </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A128" s="1"/>
-      <c r="B128" s="11">
+      <c r="J127" s="19"/>
+      <c r="K127" s="20">
+        <v>1</v>
+      </c>
+      <c r="L127" s="12"/>
+    </row>
+    <row r="128" ht="15.75" spans="1:12">
+      <c r="A128" s="2"/>
+      <c r="B128" s="7">
         <f t="shared" si="0"/>
         <v>126</v>
       </c>
-      <c r="C128" s="12" t="s">
+      <c r="C128" s="8" t="s">
         <v>566</v>
       </c>
-      <c r="D128" s="7" t="s">
+      <c r="D128" s="9" t="s">
         <v>567</v>
       </c>
-      <c r="E128" s="8" t="s">
+      <c r="E128" s="10" t="s">
         <v>568</v>
       </c>
-      <c r="F128" s="7" t="s">
+      <c r="F128" s="9" t="s">
         <v>569</v>
       </c>
-      <c r="G128" s="8" t="s">
+      <c r="G128" s="10" t="s">
         <v>569</v>
       </c>
-      <c r="H128" s="7" t="s">
+      <c r="H128" s="9" t="s">
         <v>549</v>
       </c>
-      <c r="I128" s="8" t="s">
+      <c r="I128" s="10" t="s">
         <v>569</v>
       </c>
-      <c r="J128" s="21"/>
-      <c r="K128" s="17">
+      <c r="J128" s="17"/>
+      <c r="K128" s="18">
         <v>4</v>
       </c>
-      <c r="L128" s="7"/>
-    </row>
-    <row r="129" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A129" s="1"/>
-      <c r="B129" s="11">
+      <c r="L128" s="9"/>
+    </row>
+    <row r="129" ht="24.75" spans="1:12">
+      <c r="A129" s="2"/>
+      <c r="B129" s="7">
         <f t="shared" si="0"/>
         <v>127</v>
       </c>
-      <c r="C129" s="13" t="s">
+      <c r="C129" s="11" t="s">
         <v>491</v>
       </c>
-      <c r="D129" s="9" t="s">
+      <c r="D129" s="12" t="s">
         <v>570</v>
       </c>
-      <c r="E129" s="10" t="s">
+      <c r="E129" s="13" t="s">
         <v>571</v>
       </c>
-      <c r="F129" s="9" t="s">
+      <c r="F129" s="12" t="s">
         <v>572</v>
       </c>
-      <c r="G129" s="10" t="s">
+      <c r="G129" s="13" t="s">
         <v>573</v>
       </c>
-      <c r="H129" s="9" t="s">
+      <c r="H129" s="12" t="s">
         <v>574</v>
       </c>
-      <c r="I129" s="10" t="s">
+      <c r="I129" s="13" t="s">
         <v>573</v>
       </c>
-      <c r="J129" s="22"/>
-      <c r="K129" s="18">
-        <v>1</v>
-      </c>
-      <c r="L129" s="9"/>
-    </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A130" s="1"/>
-      <c r="B130" s="11">
+      <c r="J129" s="19"/>
+      <c r="K129" s="20">
+        <v>1</v>
+      </c>
+      <c r="L129" s="12"/>
+    </row>
+    <row r="130" ht="15.75" spans="1:12">
+      <c r="A130" s="2"/>
+      <c r="B130" s="7">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
-      <c r="C130" s="12" t="s">
+      <c r="C130" s="8" t="s">
         <v>491</v>
       </c>
-      <c r="D130" s="7" t="s">
+      <c r="D130" s="9" t="s">
         <v>575</v>
       </c>
-      <c r="E130" s="8" t="s">
+      <c r="E130" s="10" t="s">
         <v>576</v>
       </c>
-      <c r="F130" s="7" t="s">
+      <c r="F130" s="9" t="s">
         <v>577</v>
       </c>
-      <c r="G130" s="8" t="s">
+      <c r="G130" s="10" t="s">
         <v>578</v>
       </c>
-      <c r="H130" s="7" t="s">
+      <c r="H130" s="9" t="s">
         <v>514</v>
       </c>
-      <c r="I130" s="8" t="s">
+      <c r="I130" s="10" t="s">
         <v>578</v>
       </c>
-      <c r="J130" s="21"/>
-      <c r="K130" s="17">
-        <v>1</v>
-      </c>
-      <c r="L130" s="7"/>
-    </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A131" s="1"/>
-      <c r="B131" s="11">
+      <c r="J130" s="17"/>
+      <c r="K130" s="18">
+        <v>1</v>
+      </c>
+      <c r="L130" s="9"/>
+    </row>
+    <row r="131" ht="15.75" spans="1:12">
+      <c r="A131" s="2"/>
+      <c r="B131" s="7">
         <f t="shared" si="0"/>
         <v>129</v>
       </c>
-      <c r="C131" s="13" t="s">
+      <c r="C131" s="11" t="s">
         <v>491</v>
       </c>
-      <c r="D131" s="9" t="s">
+      <c r="D131" s="12" t="s">
         <v>579</v>
       </c>
-      <c r="E131" s="10" t="s">
+      <c r="E131" s="13" t="s">
         <v>580</v>
       </c>
-      <c r="F131" s="9" t="s">
+      <c r="F131" s="12" t="s">
         <v>581</v>
       </c>
-      <c r="G131" s="10" t="s">
+      <c r="G131" s="13" t="s">
         <v>582</v>
       </c>
-      <c r="H131" s="9" t="s">
+      <c r="H131" s="12" t="s">
         <v>514</v>
       </c>
-      <c r="I131" s="10" t="s">
+      <c r="I131" s="13" t="s">
         <v>582</v>
       </c>
-      <c r="J131" s="22"/>
-      <c r="K131" s="18">
-        <v>1</v>
-      </c>
-      <c r="L131" s="9"/>
-    </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A132" s="1"/>
-      <c r="B132" s="11">
+      <c r="J131" s="19"/>
+      <c r="K131" s="20">
+        <v>1</v>
+      </c>
+      <c r="L131" s="12"/>
+    </row>
+    <row r="132" ht="15.75" spans="1:12">
+      <c r="A132" s="2"/>
+      <c r="B132" s="7">
         <f t="shared" si="0"/>
         <v>130</v>
       </c>
-      <c r="C132" s="12" t="s">
+      <c r="C132" s="8" t="s">
         <v>583</v>
       </c>
-      <c r="D132" s="7" t="s">
+      <c r="D132" s="9" t="s">
         <v>584</v>
       </c>
-      <c r="E132" s="8" t="s">
+      <c r="E132" s="10" t="s">
         <v>585</v>
       </c>
-      <c r="F132" s="7" t="s">
+      <c r="F132" s="9" t="s">
         <v>586</v>
       </c>
-      <c r="G132" s="8" t="s">
+      <c r="G132" s="10" t="s">
         <v>587</v>
       </c>
-      <c r="H132" s="7" t="s">
+      <c r="H132" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="I132" s="8" t="s">
+      <c r="I132" s="10" t="s">
         <v>587</v>
       </c>
-      <c r="J132" s="21"/>
-      <c r="K132" s="17">
-        <v>1</v>
-      </c>
-      <c r="L132" s="7"/>
-    </row>
-    <row r="133" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A133" s="1"/>
-      <c r="B133" s="11">
+      <c r="J132" s="17"/>
+      <c r="K132" s="18">
+        <v>1</v>
+      </c>
+      <c r="L132" s="9"/>
+    </row>
+    <row r="133" ht="24.75" spans="1:12">
+      <c r="A133" s="2"/>
+      <c r="B133" s="7">
         <f t="shared" si="0"/>
         <v>131</v>
       </c>
-      <c r="C133" s="13" t="s">
+      <c r="C133" s="11" t="s">
         <v>491</v>
       </c>
-      <c r="D133" s="9" t="s">
+      <c r="D133" s="12" t="s">
         <v>588</v>
       </c>
-      <c r="E133" s="10" t="s">
+      <c r="E133" s="13" t="s">
         <v>589</v>
       </c>
-      <c r="F133" s="9" t="s">
+      <c r="F133" s="12" t="s">
         <v>590</v>
       </c>
-      <c r="G133" s="10" t="s">
+      <c r="G133" s="13" t="s">
         <v>591</v>
       </c>
-      <c r="H133" s="9" t="s">
+      <c r="H133" s="12" t="s">
         <v>592</v>
       </c>
-      <c r="I133" s="10" t="s">
+      <c r="I133" s="13" t="s">
         <v>591</v>
       </c>
-      <c r="J133" s="22"/>
-      <c r="K133" s="18">
-        <v>1</v>
-      </c>
-      <c r="L133" s="9"/>
-    </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A134" s="1"/>
-      <c r="B134" s="11">
+      <c r="J133" s="19"/>
+      <c r="K133" s="20">
+        <v>1</v>
+      </c>
+      <c r="L133" s="12"/>
+    </row>
+    <row r="134" ht="15.75" spans="1:12">
+      <c r="A134" s="2"/>
+      <c r="B134" s="7">
         <f t="shared" si="0"/>
         <v>132</v>
       </c>
-      <c r="C134" s="12" t="s">
+      <c r="C134" s="8" t="s">
         <v>491</v>
       </c>
-      <c r="D134" s="7" t="s">
+      <c r="D134" s="9" t="s">
         <v>593</v>
       </c>
-      <c r="E134" s="8" t="s">
+      <c r="E134" s="10" t="s">
         <v>594</v>
       </c>
-      <c r="F134" s="7" t="s">
+      <c r="F134" s="9" t="s">
         <v>595</v>
       </c>
-      <c r="G134" s="8" t="s">
+      <c r="G134" s="10" t="s">
         <v>596</v>
       </c>
-      <c r="H134" s="7" t="s">
+      <c r="H134" s="9" t="s">
         <v>597</v>
       </c>
-      <c r="I134" s="8" t="s">
+      <c r="I134" s="10" t="s">
         <v>596</v>
       </c>
-      <c r="J134" s="21"/>
-      <c r="K134" s="17">
-        <v>1</v>
-      </c>
-      <c r="L134" s="7"/>
-    </row>
-    <row r="135" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A135" s="1"/>
-      <c r="B135" s="11">
+      <c r="J134" s="17"/>
+      <c r="K134" s="18">
+        <v>1</v>
+      </c>
+      <c r="L134" s="9"/>
+    </row>
+    <row r="135" ht="15.75" spans="1:12">
+      <c r="A135" s="2"/>
+      <c r="B135" s="7">
         <f t="shared" si="0"/>
         <v>133</v>
       </c>
-      <c r="C135" s="13" t="s">
+      <c r="C135" s="11" t="s">
         <v>598</v>
       </c>
-      <c r="D135" s="9" t="s">
+      <c r="D135" s="12" t="s">
         <v>599</v>
       </c>
-      <c r="E135" s="10" t="s">
+      <c r="E135" s="13" t="s">
         <v>600</v>
       </c>
-      <c r="F135" s="9" t="s">
+      <c r="F135" s="12" t="s">
         <v>601</v>
       </c>
-      <c r="G135" s="10" t="s">
+      <c r="G135" s="13" t="s">
         <v>601</v>
       </c>
-      <c r="H135" s="9" t="s">
+      <c r="H135" s="12" t="s">
         <v>602</v>
       </c>
-      <c r="I135" s="10" t="s">
+      <c r="I135" s="13" t="s">
         <v>601</v>
       </c>
-      <c r="J135" s="22"/>
-      <c r="K135" s="18">
-        <v>1</v>
-      </c>
-      <c r="L135" s="9"/>
-    </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A136" s="1"/>
-      <c r="B136" s="11">
+      <c r="J135" s="19"/>
+      <c r="K135" s="20">
+        <v>1</v>
+      </c>
+      <c r="L135" s="12"/>
+    </row>
+    <row r="136" ht="15.75" spans="1:12">
+      <c r="A136" s="2"/>
+      <c r="B136" s="7">
         <f t="shared" si="0"/>
         <v>134</v>
       </c>
-      <c r="C136" s="12" t="s">
+      <c r="C136" s="8" t="s">
         <v>491</v>
       </c>
-      <c r="D136" s="7" t="s">
+      <c r="D136" s="9" t="s">
         <v>603</v>
       </c>
-      <c r="E136" s="8" t="s">
+      <c r="E136" s="10" t="s">
         <v>604</v>
       </c>
-      <c r="F136" s="7" t="s">
+      <c r="F136" s="9" t="s">
         <v>605</v>
       </c>
-      <c r="G136" s="8" t="s">
+      <c r="G136" s="10" t="s">
         <v>606</v>
       </c>
-      <c r="H136" s="7" t="s">
+      <c r="H136" s="9" t="s">
         <v>607</v>
       </c>
-      <c r="I136" s="8" t="s">
+      <c r="I136" s="10" t="s">
         <v>606</v>
       </c>
-      <c r="J136" s="21"/>
-      <c r="K136" s="17">
-        <v>1</v>
-      </c>
-      <c r="L136" s="7"/>
-    </row>
-    <row r="137" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A137" s="1"/>
-      <c r="B137" s="11">
+      <c r="J136" s="17"/>
+      <c r="K136" s="18">
+        <v>1</v>
+      </c>
+      <c r="L136" s="9"/>
+    </row>
+    <row r="137" ht="24.75" spans="1:12">
+      <c r="A137" s="2"/>
+      <c r="B137" s="7">
         <f t="shared" si="0"/>
         <v>135</v>
       </c>
-      <c r="C137" s="13" t="s">
+      <c r="C137" s="11" t="s">
         <v>608</v>
       </c>
-      <c r="D137" s="9" t="s">
+      <c r="D137" s="12" t="s">
         <v>609</v>
       </c>
-      <c r="E137" s="10" t="s">
+      <c r="E137" s="13" t="s">
         <v>610</v>
       </c>
-      <c r="F137" s="9" t="s">
+      <c r="F137" s="12" t="s">
         <v>611</v>
       </c>
-      <c r="G137" s="10" t="s">
+      <c r="G137" s="13" t="s">
         <v>612</v>
       </c>
-      <c r="H137" s="9" t="s">
+      <c r="H137" s="12" t="s">
         <v>613</v>
       </c>
-      <c r="I137" s="10" t="s">
+      <c r="I137" s="13" t="s">
         <v>614</v>
       </c>
-      <c r="J137" s="22"/>
-      <c r="K137" s="18">
-        <v>1</v>
-      </c>
-      <c r="L137" s="9"/>
-    </row>
-    <row r="138" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A138" s="1"/>
-      <c r="B138" s="11">
+      <c r="J137" s="19"/>
+      <c r="K137" s="20">
+        <v>1</v>
+      </c>
+      <c r="L137" s="12"/>
+    </row>
+    <row r="138" ht="24.75" spans="1:12">
+      <c r="A138" s="2"/>
+      <c r="B138" s="7">
         <f t="shared" si="0"/>
         <v>136</v>
       </c>
-      <c r="C138" s="12" t="s">
+      <c r="C138" s="8" t="s">
         <v>608</v>
       </c>
-      <c r="D138" s="7" t="s">
+      <c r="D138" s="9" t="s">
         <v>615</v>
       </c>
-      <c r="E138" s="8" t="s">
+      <c r="E138" s="10" t="s">
         <v>616</v>
       </c>
-      <c r="F138" s="7" t="s">
+      <c r="F138" s="9" t="s">
         <v>617</v>
       </c>
-      <c r="G138" s="8" t="s">
+      <c r="G138" s="10" t="s">
         <v>618</v>
       </c>
-      <c r="H138" s="7" t="s">
+      <c r="H138" s="9" t="s">
         <v>619</v>
       </c>
-      <c r="I138" s="8" t="s">
+      <c r="I138" s="10" t="s">
         <v>620</v>
       </c>
-      <c r="J138" s="21"/>
-      <c r="K138" s="17">
-        <v>1</v>
-      </c>
-      <c r="L138" s="7"/>
-    </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A139" s="1"/>
-      <c r="B139" s="11">
+      <c r="J138" s="17"/>
+      <c r="K138" s="18">
+        <v>1</v>
+      </c>
+      <c r="L138" s="9"/>
+    </row>
+    <row r="139" ht="15.75" spans="1:12">
+      <c r="A139" s="2"/>
+      <c r="B139" s="7">
         <f t="shared" si="0"/>
         <v>137</v>
       </c>
-      <c r="C139" s="13" t="s">
+      <c r="C139" s="11" t="s">
         <v>608</v>
       </c>
-      <c r="D139" s="9" t="s">
+      <c r="D139" s="12" t="s">
         <v>621</v>
       </c>
-      <c r="E139" s="10" t="s">
+      <c r="E139" s="13" t="s">
         <v>622</v>
       </c>
-      <c r="F139" s="9" t="s">
+      <c r="F139" s="12" t="s">
         <v>623</v>
       </c>
-      <c r="G139" s="10" t="s">
+      <c r="G139" s="13" t="s">
         <v>623</v>
       </c>
-      <c r="H139" s="9" t="s">
+      <c r="H139" s="12" t="s">
         <v>624</v>
       </c>
-      <c r="I139" s="10" t="s">
+      <c r="I139" s="13" t="s">
         <v>625</v>
       </c>
-      <c r="J139" s="22"/>
-      <c r="K139" s="18">
-        <v>1</v>
-      </c>
-      <c r="L139" s="9"/>
-    </row>
-    <row r="140" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A140" s="1"/>
-      <c r="B140" s="11">
+      <c r="J139" s="19"/>
+      <c r="K139" s="20">
+        <v>1</v>
+      </c>
+      <c r="L139" s="12"/>
+    </row>
+    <row r="140" ht="24.75" spans="1:12">
+      <c r="A140" s="2"/>
+      <c r="B140" s="7">
         <f t="shared" si="0"/>
         <v>138</v>
       </c>
-      <c r="C140" s="12" t="s">
+      <c r="C140" s="8" t="s">
         <v>608</v>
       </c>
-      <c r="D140" s="7" t="s">
+      <c r="D140" s="9" t="s">
         <v>626</v>
       </c>
-      <c r="E140" s="8" t="s">
+      <c r="E140" s="10" t="s">
         <v>627</v>
       </c>
-      <c r="F140" s="7" t="s">
+      <c r="F140" s="9" t="s">
         <v>628</v>
       </c>
-      <c r="G140" s="8" t="s">
+      <c r="G140" s="10" t="s">
         <v>629</v>
       </c>
-      <c r="H140" s="7" t="s">
+      <c r="H140" s="9" t="s">
         <v>619</v>
       </c>
-      <c r="I140" s="8" t="s">
+      <c r="I140" s="10" t="s">
         <v>630</v>
       </c>
       <c r="J140" s="25"/>
-      <c r="K140" s="17">
-        <v>1</v>
-      </c>
-      <c r="L140" s="7"/>
-    </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A141" s="1"/>
-      <c r="B141" s="11">
+      <c r="K140" s="18">
+        <v>1</v>
+      </c>
+      <c r="L140" s="9"/>
+    </row>
+    <row r="141" spans="1:12">
+      <c r="A141" s="2"/>
+      <c r="B141" s="7">
         <f t="shared" si="0"/>
         <v>139</v>
       </c>
-      <c r="C141" s="13" t="s">
+      <c r="C141" s="11" t="s">
         <v>608</v>
       </c>
-      <c r="D141" s="9" t="s">
+      <c r="D141" s="12" t="s">
         <v>631</v>
       </c>
-      <c r="E141" s="10" t="s">
+      <c r="E141" s="13" t="s">
         <v>632</v>
       </c>
-      <c r="F141" s="9" t="s">
+      <c r="F141" s="12" t="s">
         <v>633</v>
       </c>
-      <c r="G141" s="10" t="s">
+      <c r="G141" s="13" t="s">
         <v>634</v>
       </c>
-      <c r="H141" s="9" t="s">
+      <c r="H141" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I141" s="10" t="s">
+      <c r="I141" s="13" t="s">
         <v>635</v>
       </c>
-      <c r="J141" s="22"/>
-      <c r="K141" s="18">
-        <v>1</v>
-      </c>
-      <c r="L141" s="9"/>
-    </row>
-    <row r="142" spans="1:12" ht="48" x14ac:dyDescent="0.25">
-      <c r="B142" s="11">
+      <c r="J141" s="19"/>
+      <c r="K141" s="20">
+        <v>1</v>
+      </c>
+      <c r="L141" s="12"/>
+    </row>
+    <row r="142" ht="48.75" spans="2:12">
+      <c r="B142" s="7">
         <f t="shared" si="0"/>
         <v>140</v>
       </c>
-      <c r="C142" s="13" t="s">
+      <c r="C142" s="11" t="s">
         <v>636</v>
       </c>
-      <c r="D142" s="9" t="s">
+      <c r="D142" s="12" t="s">
         <v>637</v>
       </c>
-      <c r="E142" s="10" t="s">
+      <c r="E142" s="13" t="s">
         <v>638</v>
       </c>
-      <c r="F142" s="9" t="s">
+      <c r="F142" s="12" t="s">
         <v>637</v>
       </c>
-      <c r="G142" s="10" t="s">
+      <c r="G142" s="13" t="s">
         <v>639</v>
       </c>
-      <c r="H142" s="9" t="s">
+      <c r="H142" s="12" t="s">
         <v>637</v>
       </c>
-      <c r="I142" s="10" t="s">
+      <c r="I142" s="13" t="s">
         <v>640</v>
       </c>
       <c r="J142" s="26" t="s">
         <v>641</v>
       </c>
-      <c r="K142" s="18">
-        <v>1</v>
-      </c>
-      <c r="L142" s="9"/>
-    </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B143" s="11">
+      <c r="K142" s="20">
+        <v>1</v>
+      </c>
+      <c r="L142" s="12"/>
+    </row>
+    <row r="143" spans="2:12">
+      <c r="B143" s="7">
         <f t="shared" si="0"/>
         <v>141</v>
       </c>
-      <c r="C143" s="13" t="s">
+      <c r="C143" s="11" t="s">
         <v>636</v>
       </c>
-      <c r="D143" s="9" t="s">
+      <c r="D143" s="12" t="s">
         <v>637</v>
       </c>
-      <c r="E143" s="10" t="s">
+      <c r="E143" s="13" t="s">
         <v>642</v>
       </c>
-      <c r="F143" s="9" t="s">
+      <c r="F143" s="12" t="s">
         <v>637</v>
       </c>
-      <c r="G143" s="10" t="s">
+      <c r="G143" s="13" t="s">
         <v>643</v>
       </c>
-      <c r="H143" s="9" t="s">
+      <c r="H143" s="12" t="s">
         <v>637</v>
       </c>
-      <c r="I143" s="10" t="s">
+      <c r="I143" s="13" t="s">
         <v>637</v>
       </c>
-      <c r="J143" s="7"/>
-      <c r="K143" s="18">
-        <v>1</v>
-      </c>
-      <c r="L143" s="9"/>
-    </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B144" s="11">
-        <f t="shared" ref="B144" si="1">ROW(B144) - ROW($B$2)</f>
+      <c r="J143" s="9"/>
+      <c r="K143" s="20">
+        <v>1</v>
+      </c>
+      <c r="L143" s="12"/>
+    </row>
+    <row r="144" spans="2:12">
+      <c r="B144" s="7">
+        <f t="shared" ref="B144" si="1">ROW(B144)-ROW($B$2)</f>
         <v>142</v>
       </c>
-      <c r="C144" s="13" t="s">
+      <c r="C144" s="11" t="s">
         <v>636</v>
       </c>
-      <c r="D144" s="9" t="s">
+      <c r="D144" s="12" t="s">
         <v>637</v>
       </c>
-      <c r="E144" s="10" t="s">
+      <c r="E144" s="13" t="s">
         <v>642</v>
       </c>
-      <c r="F144" s="9" t="s">
+      <c r="F144" s="12" t="s">
         <v>637</v>
       </c>
-      <c r="G144" s="10" t="s">
+      <c r="G144" s="13" t="s">
         <v>644</v>
       </c>
-      <c r="H144" s="9" t="s">
+      <c r="H144" s="12" t="s">
         <v>637</v>
       </c>
-      <c r="I144" s="10" t="s">
+      <c r="I144" s="13" t="s">
         <v>637</v>
       </c>
-      <c r="J144" s="24" t="s">
+      <c r="J144" s="27" t="s">
         <v>641</v>
       </c>
-      <c r="K144" s="18">
-        <v>1</v>
-      </c>
-      <c r="L144" s="9"/>
+      <c r="K144" s="20">
+        <v>1</v>
+      </c>
+      <c r="L144" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="I1:L1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="J142" r:id="rId1"/>
-    <hyperlink ref="J144" r:id="rId2"/>
+    <hyperlink ref="J142" r:id="rId1" display="Aliexpress"/>
+    <hyperlink ref="J144" r:id="rId2" display="Aliexpress"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Design-Files/Tracker-pro-airbnb-v1.1/BOM/Altium_BOM_tracker-pro-airbnb-v1.1.xlsx
+++ b/Design-Files/Tracker-pro-airbnb-v1.1/BOM/Altium_BOM_tracker-pro-airbnb-v1.1.xlsx
@@ -1,20 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ashan moten\Downloads\Tracker-pro-airbnb-v1.1\Tracker-pro-airbnb-v1.1\BOM\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12330"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="645">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="644">
   <si>
     <t>#</t>
   </si>
@@ -475,16 +480,6 @@
     <t>C121</t>
   </si>
   <si>
-    <t xml:space="preserve">100uF 100V 280mA@120Hz ±20% SMD,D12.5xL13.5mm Aluminum Electrolytic Capacitors </t>
-  </si>
-  <si>
-    <t>RVT2A101M1213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-ROQANG</t>
-  </si>
-  <si>
     <t>Diode</t>
   </si>
   <si>
@@ -1950,19 +1945,19 @@
   </si>
   <si>
     <t>ZE08-CH2O</t>
+  </si>
+  <si>
+    <t>100uF 80V 735mA@100kHz ±20% SMD,D8xL14.5mm Aluminum Electrolytic Capacitors - SMD ROHS</t>
+  </si>
+  <si>
+    <t>VKMD1451K101MV</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
-  </numFmts>
-  <fonts count="28">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2021,13 +2016,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
@@ -2036,143 +2024,34 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <sz val="10"/>
+      <color indexed="13"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="10"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <sz val="9"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2191,194 +2070,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="23">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -2560,251 +2253,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2841,9 +2295,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2877,74 +2328,44 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="0003A4CB"/>
-      <color rgb="002CD0B2"/>
+      <color rgb="FF03A4CB"/>
+      <color rgb="FF2CD0B2"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -3202,28 +2623,29 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:L144"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="4.42857142857143" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.7142857142857" style="1" customWidth="1"/>
+    <col min="2" max="2" width="4.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="36" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="26.5714285714286" customWidth="1"/>
-    <col min="7" max="7" width="33.4285714285714" customWidth="1"/>
-    <col min="8" max="8" width="21.4285714285714" customWidth="1"/>
-    <col min="9" max="10" width="17.8571428571429" customWidth="1"/>
-    <col min="11" max="11" width="16.7142857142857" customWidth="1"/>
-    <col min="12" max="12" width="29.4285714285714" customWidth="1"/>
+    <col min="6" max="6" width="26.5703125" customWidth="1"/>
+    <col min="7" max="7" width="33.42578125" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" customWidth="1"/>
+    <col min="9" max="10" width="17.85546875" customWidth="1"/>
+    <col min="11" max="11" width="16.7109375" customWidth="1"/>
+    <col min="12" max="12" width="29.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" spans="1:12">
+    <row r="1" spans="1:12">
       <c r="A1" s="2"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -3232,12 +2654,12 @@
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-    </row>
-    <row r="2" ht="15.75" spans="1:12">
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="2"/>
       <c r="B2" s="5" t="s">
         <v>0</v>
@@ -3263,17 +2685,17 @@
       <c r="I2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="J2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="16" t="s">
+      <c r="K2" s="15" t="s">
         <v>9</v>
       </c>
       <c r="L2" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" ht="24.75" spans="1:12">
+    <row r="3" spans="1:12" ht="24">
       <c r="A3" s="2"/>
       <c r="B3" s="7">
         <f>ROW(B3)-ROW($B$2)</f>
@@ -3300,13 +2722,13 @@
       <c r="I3" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="17"/>
-      <c r="K3" s="18">
+      <c r="J3" s="16"/>
+      <c r="K3" s="17">
         <v>2</v>
       </c>
       <c r="L3" s="9"/>
     </row>
-    <row r="4" ht="24.75" spans="1:12">
+    <row r="4" spans="1:12" ht="24">
       <c r="A4" s="2"/>
       <c r="B4" s="7">
         <f t="shared" ref="B4:B143" si="0">ROW(B4)-ROW($B$2)</f>
@@ -3333,13 +2755,13 @@
       <c r="I4" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="J4" s="19"/>
-      <c r="K4" s="20">
+      <c r="J4" s="18"/>
+      <c r="K4" s="19">
         <v>12</v>
       </c>
       <c r="L4" s="12"/>
     </row>
-    <row r="5" ht="15.75" spans="1:12">
+    <row r="5" spans="1:12">
       <c r="A5" s="2"/>
       <c r="B5" s="7">
         <f>ROW(B5)-ROW($B$2)</f>
@@ -3366,13 +2788,13 @@
       <c r="I5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="17"/>
-      <c r="K5" s="18">
+      <c r="J5" s="16"/>
+      <c r="K5" s="17">
         <v>1</v>
       </c>
       <c r="L5" s="9"/>
     </row>
-    <row r="6" ht="60.75" spans="1:12">
+    <row r="6" spans="1:12" ht="60">
       <c r="A6" s="2"/>
       <c r="B6" s="7">
         <f t="shared" si="0"/>
@@ -3399,13 +2821,13 @@
       <c r="I6" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="J6" s="19"/>
-      <c r="K6" s="20">
+      <c r="J6" s="18"/>
+      <c r="K6" s="19">
         <v>42</v>
       </c>
       <c r="L6" s="12"/>
     </row>
-    <row r="7" ht="15.75" spans="1:12">
+    <row r="7" spans="1:12">
       <c r="A7" s="2"/>
       <c r="B7" s="7">
         <f>ROW(B7)-ROW($B$2)</f>
@@ -3432,13 +2854,13 @@
       <c r="I7" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="17"/>
-      <c r="K7" s="18">
+      <c r="J7" s="16"/>
+      <c r="K7" s="17">
         <v>1</v>
       </c>
       <c r="L7" s="9"/>
     </row>
-    <row r="8" ht="36.75" spans="1:12">
+    <row r="8" spans="1:12" ht="36">
       <c r="A8" s="2"/>
       <c r="B8" s="7">
         <f t="shared" si="0"/>
@@ -3465,13 +2887,13 @@
       <c r="I8" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="J8" s="19"/>
-      <c r="K8" s="20">
+      <c r="J8" s="18"/>
+      <c r="K8" s="19">
         <v>2</v>
       </c>
       <c r="L8" s="12"/>
     </row>
-    <row r="9" ht="15.75" spans="1:12">
+    <row r="9" spans="1:12">
       <c r="A9" s="2"/>
       <c r="B9" s="7">
         <f>ROW(B9)-ROW($B$2)</f>
@@ -3498,13 +2920,13 @@
       <c r="I9" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="J9" s="17"/>
-      <c r="K9" s="18">
+      <c r="J9" s="16"/>
+      <c r="K9" s="17">
         <v>1</v>
       </c>
       <c r="L9" s="9"/>
     </row>
-    <row r="10" ht="24.75" spans="1:12">
+    <row r="10" spans="1:12" ht="24">
       <c r="A10" s="2"/>
       <c r="B10" s="7">
         <f t="shared" si="0"/>
@@ -3531,13 +2953,13 @@
       <c r="I10" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="J10" s="19"/>
-      <c r="K10" s="20">
+      <c r="J10" s="18"/>
+      <c r="K10" s="19">
         <v>17</v>
       </c>
       <c r="L10" s="12"/>
     </row>
-    <row r="11" ht="15.75" spans="1:12">
+    <row r="11" spans="1:12">
       <c r="A11" s="2"/>
       <c r="B11" s="7">
         <f>ROW(B11)-ROW($B$2)</f>
@@ -3564,13 +2986,13 @@
       <c r="I11" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="J11" s="17"/>
-      <c r="K11" s="18">
+      <c r="J11" s="16"/>
+      <c r="K11" s="17">
         <v>1</v>
       </c>
       <c r="L11" s="9"/>
     </row>
-    <row r="12" ht="15.75" spans="1:12">
+    <row r="12" spans="1:12">
       <c r="A12" s="2"/>
       <c r="B12" s="7">
         <f t="shared" si="0"/>
@@ -3597,13 +3019,13 @@
       <c r="I12" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="J12" s="19"/>
-      <c r="K12" s="20">
+      <c r="J12" s="18"/>
+      <c r="K12" s="19">
         <v>3</v>
       </c>
       <c r="L12" s="12"/>
     </row>
-    <row r="13" ht="15.75" spans="1:12">
+    <row r="13" spans="1:12">
       <c r="A13" s="2"/>
       <c r="B13" s="7">
         <f>ROW(B13)-ROW($B$2)</f>
@@ -3630,13 +3052,13 @@
       <c r="I13" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="J13" s="17"/>
-      <c r="K13" s="18">
+      <c r="J13" s="16"/>
+      <c r="K13" s="17">
         <v>2</v>
       </c>
       <c r="L13" s="9"/>
     </row>
-    <row r="14" ht="15.75" spans="1:12">
+    <row r="14" spans="1:12">
       <c r="A14" s="2"/>
       <c r="B14" s="7">
         <f t="shared" si="0"/>
@@ -3663,13 +3085,13 @@
       <c r="I14" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="J14" s="19"/>
-      <c r="K14" s="20">
+      <c r="J14" s="18"/>
+      <c r="K14" s="19">
         <v>2</v>
       </c>
       <c r="L14" s="12"/>
     </row>
-    <row r="15" ht="24.75" spans="1:12">
+    <row r="15" spans="1:12" ht="24">
       <c r="A15" s="2"/>
       <c r="B15" s="7">
         <f>ROW(B15)-ROW($B$2)</f>
@@ -3696,13 +3118,13 @@
       <c r="I15" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="J15" s="17"/>
-      <c r="K15" s="18">
+      <c r="J15" s="16"/>
+      <c r="K15" s="17">
         <v>1</v>
       </c>
       <c r="L15" s="9"/>
     </row>
-    <row r="16" ht="15.75" spans="1:12">
+    <row r="16" spans="1:12">
       <c r="A16" s="2"/>
       <c r="B16" s="7">
         <f t="shared" si="0"/>
@@ -3729,13 +3151,13 @@
       <c r="I16" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="J16" s="19"/>
-      <c r="K16" s="20">
+      <c r="J16" s="18"/>
+      <c r="K16" s="19">
         <v>1</v>
       </c>
       <c r="L16" s="12"/>
     </row>
-    <row r="17" ht="15.75" spans="1:12">
+    <row r="17" spans="1:12">
       <c r="A17" s="2"/>
       <c r="B17" s="7">
         <f>ROW(B17)-ROW($B$2)</f>
@@ -3762,13 +3184,13 @@
       <c r="I17" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="J17" s="17"/>
-      <c r="K17" s="18">
+      <c r="J17" s="16"/>
+      <c r="K17" s="17">
         <v>2</v>
       </c>
       <c r="L17" s="9"/>
     </row>
-    <row r="18" ht="15.75" spans="1:12">
+    <row r="18" spans="1:12">
       <c r="A18" s="2"/>
       <c r="B18" s="7">
         <f t="shared" si="0"/>
@@ -3795,13 +3217,13 @@
       <c r="I18" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="J18" s="19"/>
-      <c r="K18" s="20">
+      <c r="J18" s="18"/>
+      <c r="K18" s="19">
         <v>3</v>
       </c>
       <c r="L18" s="12"/>
     </row>
-    <row r="19" ht="15.75" spans="1:12">
+    <row r="19" spans="1:12">
       <c r="A19" s="2"/>
       <c r="B19" s="7">
         <f>ROW(B19)-ROW($B$2)</f>
@@ -3828,13 +3250,13 @@
       <c r="I19" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="J19" s="17"/>
-      <c r="K19" s="18">
+      <c r="J19" s="16"/>
+      <c r="K19" s="17">
         <v>1</v>
       </c>
       <c r="L19" s="9"/>
     </row>
-    <row r="20" ht="15.75" spans="1:12">
+    <row r="20" spans="1:12">
       <c r="A20" s="2"/>
       <c r="B20" s="7">
         <f t="shared" si="0"/>
@@ -3861,13 +3283,13 @@
       <c r="I20" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="J20" s="19"/>
-      <c r="K20" s="20">
+      <c r="J20" s="18"/>
+      <c r="K20" s="19">
         <v>2</v>
       </c>
       <c r="L20" s="12"/>
     </row>
-    <row r="21" ht="15.75" spans="1:12">
+    <row r="21" spans="1:12">
       <c r="A21" s="2"/>
       <c r="B21" s="7">
         <f>ROW(B21)-ROW($B$2)</f>
@@ -3894,13 +3316,13 @@
       <c r="I21" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="J21" s="17"/>
-      <c r="K21" s="18">
+      <c r="J21" s="16"/>
+      <c r="K21" s="17">
         <v>1</v>
       </c>
       <c r="L21" s="9"/>
     </row>
-    <row r="22" ht="15.75" spans="1:12">
+    <row r="22" spans="1:12">
       <c r="A22" s="2"/>
       <c r="B22" s="7">
         <f t="shared" si="0"/>
@@ -3927,13 +3349,13 @@
       <c r="I22" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="J22" s="19"/>
-      <c r="K22" s="20">
+      <c r="J22" s="18"/>
+      <c r="K22" s="19">
         <v>2</v>
       </c>
       <c r="L22" s="12"/>
     </row>
-    <row r="23" ht="36.75" spans="1:12">
+    <row r="23" spans="1:12" ht="36">
       <c r="A23" s="2"/>
       <c r="B23" s="7">
         <f>ROW(B23)-ROW($B$2)</f>
@@ -3960,13 +3382,13 @@
       <c r="I23" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="J23" s="17"/>
-      <c r="K23" s="18">
+      <c r="J23" s="16"/>
+      <c r="K23" s="17">
         <v>1</v>
       </c>
       <c r="L23" s="9"/>
     </row>
-    <row r="24" ht="15.75" spans="1:12">
+    <row r="24" spans="1:12">
       <c r="A24" s="2"/>
       <c r="B24" s="7">
         <f t="shared" si="0"/>
@@ -3993,13 +3415,13 @@
       <c r="I24" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="J24" s="19"/>
-      <c r="K24" s="20">
+      <c r="J24" s="18"/>
+      <c r="K24" s="19">
         <v>2</v>
       </c>
       <c r="L24" s="12"/>
     </row>
-    <row r="25" ht="15.75" spans="1:12">
+    <row r="25" spans="1:12">
       <c r="A25" s="2"/>
       <c r="B25" s="7">
         <f>ROW(B25)-ROW($B$2)</f>
@@ -4026,13 +3448,13 @@
       <c r="I25" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="J25" s="17"/>
-      <c r="K25" s="18">
+      <c r="J25" s="16"/>
+      <c r="K25" s="17">
         <v>2</v>
       </c>
       <c r="L25" s="9"/>
     </row>
-    <row r="26" ht="15.75" spans="1:12">
+    <row r="26" spans="1:12">
       <c r="A26" s="2"/>
       <c r="B26" s="7">
         <f t="shared" si="0"/>
@@ -4059,13 +3481,13 @@
       <c r="I26" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="J26" s="19"/>
-      <c r="K26" s="20">
+      <c r="J26" s="18"/>
+      <c r="K26" s="19">
         <v>3</v>
       </c>
       <c r="L26" s="12"/>
     </row>
-    <row r="27" ht="15.75" spans="1:12">
+    <row r="27" spans="1:12">
       <c r="A27" s="2"/>
       <c r="B27" s="7">
         <f>ROW(B27)-ROW($B$2)</f>
@@ -4092,13 +3514,13 @@
       <c r="I27" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="J27" s="17"/>
-      <c r="K27" s="18">
+      <c r="J27" s="16"/>
+      <c r="K27" s="17">
         <v>1</v>
       </c>
       <c r="L27" s="9"/>
     </row>
-    <row r="28" ht="15.75" spans="1:12">
+    <row r="28" spans="1:12">
       <c r="A28" s="2"/>
       <c r="B28" s="7">
         <f t="shared" si="0"/>
@@ -4125,13 +3547,13 @@
       <c r="I28" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="J28" s="19"/>
-      <c r="K28" s="20">
+      <c r="J28" s="18"/>
+      <c r="K28" s="19">
         <v>1</v>
       </c>
       <c r="L28" s="12"/>
     </row>
-    <row r="29" ht="15.75" spans="1:12">
+    <row r="29" spans="1:12">
       <c r="A29" s="2"/>
       <c r="B29" s="7">
         <f>ROW(B29)-ROW($B$2)</f>
@@ -4158,13 +3580,13 @@
       <c r="I29" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="J29" s="17"/>
-      <c r="K29" s="18">
+      <c r="J29" s="16"/>
+      <c r="K29" s="17">
         <v>4</v>
       </c>
       <c r="L29" s="9"/>
     </row>
-    <row r="30" ht="15.75" spans="1:12">
+    <row r="30" spans="1:12">
       <c r="A30" s="2"/>
       <c r="B30" s="7">
         <f t="shared" si="0"/>
@@ -4191,13 +3613,13 @@
       <c r="I30" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="J30" s="19"/>
-      <c r="K30" s="20">
+      <c r="J30" s="18"/>
+      <c r="K30" s="19">
         <v>1</v>
       </c>
       <c r="L30" s="12"/>
     </row>
-    <row r="31" ht="15.75" spans="1:12">
+    <row r="31" spans="1:12">
       <c r="A31" s="2"/>
       <c r="B31" s="7">
         <f>ROW(B31)-ROW($B$2)</f>
@@ -4224,13 +3646,13 @@
       <c r="I31" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="J31" s="17"/>
-      <c r="K31" s="18">
+      <c r="J31" s="16"/>
+      <c r="K31" s="17">
         <v>1</v>
       </c>
       <c r="L31" s="9"/>
     </row>
-    <row r="32" ht="15.75" spans="1:12">
+    <row r="32" spans="1:12">
       <c r="A32" s="2"/>
       <c r="B32" s="7">
         <f t="shared" si="0"/>
@@ -4257,13 +3679,13 @@
       <c r="I32" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="J32" s="19"/>
-      <c r="K32" s="20">
+      <c r="J32" s="18"/>
+      <c r="K32" s="19">
         <v>1</v>
       </c>
       <c r="L32" s="12"/>
     </row>
-    <row r="33" ht="15.75" spans="1:12">
+    <row r="33" spans="1:12">
       <c r="A33" s="2"/>
       <c r="B33" s="7">
         <f>ROW(B33)-ROW($B$2)</f>
@@ -4290,13 +3712,13 @@
       <c r="I33" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="J33" s="17"/>
-      <c r="K33" s="18">
+      <c r="J33" s="16"/>
+      <c r="K33" s="17">
         <v>4</v>
       </c>
       <c r="L33" s="9"/>
     </row>
-    <row r="34" ht="15.75" spans="1:12">
+    <row r="34" spans="1:12">
       <c r="A34" s="2"/>
       <c r="B34" s="7">
         <f t="shared" si="0"/>
@@ -4323,13 +3745,13 @@
       <c r="I34" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="J34" s="19"/>
-      <c r="K34" s="20">
+      <c r="J34" s="18"/>
+      <c r="K34" s="19">
         <v>1</v>
       </c>
       <c r="L34" s="12"/>
     </row>
-    <row r="35" ht="15.75" spans="1:12">
+    <row r="35" spans="1:12">
       <c r="A35" s="2"/>
       <c r="B35" s="7">
         <f>ROW(B35)-ROW($B$2)</f>
@@ -4356,1294 +3778,1295 @@
       <c r="I35" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="J35" s="17"/>
-      <c r="K35" s="18">
+      <c r="J35" s="16"/>
+      <c r="K35" s="17">
         <v>1</v>
       </c>
       <c r="L35" s="9"/>
     </row>
-    <row r="36" ht="36.75" spans="1:12">
-      <c r="A36" s="2"/>
-      <c r="B36" s="7">
+    <row r="36" spans="1:12" ht="36">
+      <c r="A36" s="28"/>
+      <c r="B36" s="29">
+        <f t="shared" ref="B36" si="1">ROW(B36) - ROW($B$2)</f>
         <v>34</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="30" t="s">
         <v>16</v>
       </c>
       <c r="D36" s="9" t="s">
         <v>152</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>153</v>
+        <v>642</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>154</v>
+        <v>643</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>154</v>
+        <v>643</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>155</v>
+        <v>107</v>
       </c>
       <c r="I36" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="J36" s="17"/>
-      <c r="K36" s="18">
-        <v>1</v>
-      </c>
-      <c r="L36" s="9"/>
-    </row>
-    <row r="37" ht="24.75" spans="1:12">
+      <c r="J36" s="31"/>
+      <c r="K36" s="17">
+        <v>1</v>
+      </c>
+      <c r="L36" s="12"/>
+    </row>
+    <row r="37" spans="1:12" ht="24">
       <c r="A37" s="2"/>
       <c r="B37" s="7">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="C37" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="F37" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="D37" s="12" t="s">
+      <c r="G37" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="E37" s="13" t="s">
+      <c r="H37" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="F37" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="G37" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="H37" s="12" t="s">
-        <v>161</v>
-      </c>
       <c r="I37" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="J37" s="19"/>
-      <c r="K37" s="20">
+        <v>157</v>
+      </c>
+      <c r="J37" s="18"/>
+      <c r="K37" s="19">
         <v>1</v>
       </c>
       <c r="L37" s="12"/>
     </row>
-    <row r="38" ht="24.75" spans="1:12">
+    <row r="38" spans="1:12" ht="24">
       <c r="A38" s="2"/>
       <c r="B38" s="7">
         <f>ROW(B38)-ROW($B$2)</f>
         <v>36</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D38" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="G38" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="E38" s="10" t="s">
+      <c r="H38" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="F38" s="9" t="s">
+      <c r="I38" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="G38" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="H38" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="I38" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="J38" s="17"/>
-      <c r="K38" s="18">
+      <c r="J38" s="16"/>
+      <c r="K38" s="17">
         <v>1</v>
       </c>
       <c r="L38" s="9"/>
     </row>
-    <row r="39" ht="24.75" spans="1:12">
+    <row r="39" spans="1:12" ht="24">
       <c r="A39" s="2"/>
       <c r="B39" s="7">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E39" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="H39" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="F39" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="G39" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="H39" s="12" t="s">
-        <v>166</v>
-      </c>
       <c r="I39" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="J39" s="19"/>
-      <c r="K39" s="20">
+        <v>162</v>
+      </c>
+      <c r="J39" s="18"/>
+      <c r="K39" s="19">
         <v>2</v>
       </c>
       <c r="L39" s="12"/>
     </row>
-    <row r="40" ht="36.75" spans="1:12">
+    <row r="40" spans="1:12" ht="36">
       <c r="A40" s="2"/>
       <c r="B40" s="7">
         <f>ROW(B40)-ROW($B$2)</f>
         <v>38</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D40" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="G40" s="10" t="s">
         <v>169</v>
-      </c>
-      <c r="E40" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="G40" s="10" t="s">
-        <v>172</v>
       </c>
       <c r="H40" s="9" t="s">
         <v>15</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="J40" s="17"/>
-      <c r="K40" s="18">
+        <v>169</v>
+      </c>
+      <c r="J40" s="16"/>
+      <c r="K40" s="17">
         <v>1</v>
       </c>
       <c r="L40" s="9"/>
     </row>
-    <row r="41" ht="24.75" spans="1:12">
+    <row r="41" spans="1:12" ht="24">
       <c r="A41" s="2"/>
       <c r="B41" s="7">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D41" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="E41" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="F41" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="G41" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="E41" s="13" t="s">
+      <c r="H41" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="F41" s="12" t="s">
-        <v>175</v>
-      </c>
-      <c r="G41" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="H41" s="12" t="s">
-        <v>177</v>
-      </c>
       <c r="I41" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="J41" s="19"/>
-      <c r="K41" s="20">
+        <v>173</v>
+      </c>
+      <c r="J41" s="18"/>
+      <c r="K41" s="19">
         <v>1</v>
       </c>
       <c r="L41" s="12"/>
     </row>
-    <row r="42" ht="24.75" spans="1:12">
+    <row r="42" spans="1:12" ht="24">
       <c r="A42" s="2"/>
       <c r="B42" s="7">
         <f>ROW(B42)-ROW($B$2)</f>
         <v>40</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D42" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="G42" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="H42" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="E42" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="G42" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="H42" s="9" t="s">
-        <v>181</v>
-      </c>
       <c r="I42" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="J42" s="17"/>
-      <c r="K42" s="18">
+        <v>177</v>
+      </c>
+      <c r="J42" s="16"/>
+      <c r="K42" s="17">
         <v>1</v>
       </c>
       <c r="L42" s="9"/>
     </row>
-    <row r="43" ht="15.75" spans="1:12">
+    <row r="43" spans="1:12">
       <c r="A43" s="2"/>
       <c r="B43" s="7">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D43" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="E43" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="F43" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="G43" s="13" t="s">
         <v>182</v>
-      </c>
-      <c r="E43" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="F43" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="G43" s="13" t="s">
-        <v>185</v>
       </c>
       <c r="H43" s="12" t="s">
         <v>15</v>
       </c>
       <c r="I43" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="J43" s="19"/>
-      <c r="K43" s="20">
+        <v>182</v>
+      </c>
+      <c r="J43" s="18"/>
+      <c r="K43" s="19">
         <v>1</v>
       </c>
       <c r="L43" s="12"/>
     </row>
-    <row r="44" ht="24.75" spans="1:12">
+    <row r="44" spans="1:12" ht="24">
       <c r="A44" s="2"/>
       <c r="B44" s="7">
         <f>ROW(B44)-ROW($B$2)</f>
         <v>42</v>
       </c>
       <c r="C44" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="E44" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="F44" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="D44" s="9" t="s">
+      <c r="G44" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="E44" s="10" t="s">
+      <c r="H44" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="F44" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="G44" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="H44" s="9" t="s">
-        <v>191</v>
-      </c>
       <c r="I44" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="J44" s="17"/>
-      <c r="K44" s="18">
+        <v>187</v>
+      </c>
+      <c r="J44" s="16"/>
+      <c r="K44" s="17">
         <v>2</v>
       </c>
       <c r="L44" s="9"/>
     </row>
-    <row r="45" ht="15.75" spans="1:12">
+    <row r="45" spans="1:12">
       <c r="A45" s="2"/>
       <c r="B45" s="7">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
       <c r="C45" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="E45" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="F45" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="D45" s="12" t="s">
+      <c r="G45" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="E45" s="13" t="s">
+      <c r="H45" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="F45" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="G45" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="H45" s="12" t="s">
-        <v>197</v>
-      </c>
       <c r="I45" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="J45" s="19"/>
-      <c r="K45" s="20">
+        <v>193</v>
+      </c>
+      <c r="J45" s="18"/>
+      <c r="K45" s="19">
         <v>5</v>
       </c>
       <c r="L45" s="12"/>
     </row>
-    <row r="46" ht="15.75" spans="1:12">
+    <row r="46" spans="1:12">
       <c r="A46" s="2"/>
       <c r="B46" s="7">
         <f>ROW(B46)-ROW($B$2)</f>
         <v>44</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D46" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="G46" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="E46" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="G46" s="10" t="s">
-        <v>201</v>
-      </c>
       <c r="H46" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="J46" s="17"/>
-      <c r="K46" s="18">
+        <v>198</v>
+      </c>
+      <c r="J46" s="16"/>
+      <c r="K46" s="17">
         <v>3</v>
       </c>
       <c r="L46" s="9"/>
     </row>
-    <row r="47" ht="24.75" spans="1:12">
+    <row r="47" spans="1:12" ht="24">
       <c r="A47" s="2"/>
       <c r="B47" s="7">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D47" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E47" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="F47" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="G47" s="13" t="s">
         <v>202</v>
-      </c>
-      <c r="E47" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="F47" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="G47" s="13" t="s">
-        <v>205</v>
       </c>
       <c r="H47" s="12" t="s">
         <v>102</v>
       </c>
       <c r="I47" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="J47" s="19"/>
-      <c r="K47" s="20">
+        <v>202</v>
+      </c>
+      <c r="J47" s="18"/>
+      <c r="K47" s="19">
         <v>2</v>
       </c>
       <c r="L47" s="12"/>
     </row>
-    <row r="48" ht="15.75" spans="1:12">
+    <row r="48" spans="1:12">
       <c r="A48" s="2"/>
       <c r="B48" s="7">
         <f>ROW(B48)-ROW($B$2)</f>
         <v>46</v>
       </c>
       <c r="C48" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="F48" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="D48" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="E48" s="10" t="s">
+      <c r="G48" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="H48" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="F48" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="G48" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="H48" s="9" t="s">
-        <v>197</v>
-      </c>
       <c r="I48" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="J48" s="17"/>
-      <c r="K48" s="18">
+        <v>204</v>
+      </c>
+      <c r="J48" s="16"/>
+      <c r="K48" s="17">
         <v>7</v>
       </c>
       <c r="L48" s="9"/>
     </row>
-    <row r="49" ht="24.75" spans="1:12">
+    <row r="49" spans="1:12" ht="24">
       <c r="A49" s="2"/>
       <c r="B49" s="7">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="C49" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="F49" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="D49" s="12" t="s">
+      <c r="G49" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="E49" s="13" t="s">
+      <c r="H49" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="F49" s="12" t="s">
-        <v>211</v>
-      </c>
-      <c r="G49" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="H49" s="12" t="s">
-        <v>213</v>
-      </c>
       <c r="I49" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="J49" s="19"/>
-      <c r="K49" s="20">
+        <v>209</v>
+      </c>
+      <c r="J49" s="18"/>
+      <c r="K49" s="19">
         <v>1</v>
       </c>
       <c r="L49" s="12"/>
     </row>
-    <row r="50" ht="36.75" spans="1:12">
+    <row r="50" spans="1:12" ht="48">
       <c r="A50" s="2"/>
       <c r="B50" s="7">
         <f>ROW(B50)-ROW($B$2)</f>
         <v>48</v>
       </c>
       <c r="C50" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="F50" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="D50" s="9" t="s">
+      <c r="G50" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="H50" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="E50" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="G50" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="H50" s="9" t="s">
-        <v>218</v>
-      </c>
       <c r="I50" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="J50" s="17"/>
-      <c r="K50" s="18">
+        <v>214</v>
+      </c>
+      <c r="J50" s="16"/>
+      <c r="K50" s="17">
         <v>1</v>
       </c>
       <c r="L50" s="9"/>
     </row>
-    <row r="51" ht="26.25" spans="1:12">
+    <row r="51" spans="1:12" ht="25.5">
       <c r="A51" s="2"/>
       <c r="B51" s="7">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="C51" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="E51" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="F51" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="D51" s="12" t="s">
+      <c r="G51" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="H51" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="E51" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="F51" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="G51" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="H51" s="12" t="s">
-        <v>223</v>
-      </c>
       <c r="I51" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="J51" s="19"/>
-      <c r="K51" s="20">
+        <v>219</v>
+      </c>
+      <c r="J51" s="18"/>
+      <c r="K51" s="19">
         <v>1</v>
       </c>
       <c r="L51" s="12"/>
     </row>
-    <row r="52" ht="15.75" spans="1:12">
+    <row r="52" spans="1:12">
       <c r="A52" s="2"/>
       <c r="B52" s="7">
         <f>ROW(B52)-ROW($B$2)</f>
         <v>50</v>
       </c>
       <c r="C52" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="F52" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="D52" s="9" t="s">
+      <c r="G52" s="10" t="s">
         <v>225</v>
-      </c>
-      <c r="E52" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="F52" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="G52" s="10" t="s">
-        <v>228</v>
       </c>
       <c r="H52" s="9"/>
       <c r="I52" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="J52" s="17"/>
-      <c r="K52" s="18">
+        <v>225</v>
+      </c>
+      <c r="J52" s="16"/>
+      <c r="K52" s="17">
         <v>2</v>
       </c>
       <c r="L52" s="9"/>
     </row>
-    <row r="53" ht="26.25" spans="1:12">
+    <row r="53" spans="1:12" ht="25.5">
       <c r="A53" s="2"/>
       <c r="B53" s="7">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
       <c r="C53" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="E53" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="F53" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="D53" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="E53" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="F53" s="12" t="s">
-        <v>232</v>
-      </c>
       <c r="G53" s="13" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H53" s="12" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I53" s="13">
         <v>532610871</v>
       </c>
-      <c r="J53" s="19"/>
-      <c r="K53" s="20">
+      <c r="J53" s="18"/>
+      <c r="K53" s="19">
         <v>1</v>
       </c>
       <c r="L53" s="12"/>
     </row>
-    <row r="54" ht="48.75" spans="1:12">
+    <row r="54" spans="1:12" ht="48">
       <c r="A54" s="2"/>
       <c r="B54" s="7">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
       <c r="C54" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="E54" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="F54" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="D54" s="12" t="s">
+      <c r="G54" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="E54" s="13" t="s">
+      <c r="H54" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="F54" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="G54" s="13" t="s">
-        <v>237</v>
-      </c>
-      <c r="H54" s="12" t="s">
-        <v>238</v>
-      </c>
       <c r="I54" s="13" t="s">
-        <v>237</v>
-      </c>
-      <c r="J54" s="19"/>
-      <c r="K54" s="20">
+        <v>234</v>
+      </c>
+      <c r="J54" s="18"/>
+      <c r="K54" s="19">
         <v>1</v>
       </c>
       <c r="L54" s="12"/>
     </row>
-    <row r="55" ht="15.75" spans="1:12">
+    <row r="55" spans="1:12">
       <c r="A55" s="2"/>
       <c r="B55" s="7">
         <f>ROW(B55)-ROW($B$2)</f>
         <v>53</v>
       </c>
       <c r="C55" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="E55" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="F55" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="D55" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="E55" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="F55" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="G55" s="10">
         <v>61300311121</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="I55" s="10">
         <v>61300311121</v>
       </c>
-      <c r="J55" s="17"/>
-      <c r="K55" s="18">
+      <c r="J55" s="16"/>
+      <c r="K55" s="17">
         <v>3</v>
       </c>
       <c r="L55" s="9"/>
     </row>
-    <row r="56" ht="24.75" spans="1:12">
+    <row r="56" spans="1:12" ht="36">
       <c r="A56" s="2"/>
       <c r="B56" s="7">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
       <c r="C56" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="E56" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="F56" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="D56" s="12" t="s">
+      <c r="G56" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="E56" s="13" t="s">
-        <v>246</v>
-      </c>
-      <c r="F56" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="G56" s="13" t="s">
-        <v>248</v>
-      </c>
       <c r="H56" s="12" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="I56" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="J56" s="19"/>
-      <c r="K56" s="20">
+        <v>244</v>
+      </c>
+      <c r="J56" s="18"/>
+      <c r="K56" s="19">
         <v>1</v>
       </c>
       <c r="L56" s="12"/>
     </row>
-    <row r="57" ht="48.75" spans="1:12">
+    <row r="57" spans="1:12" ht="48">
       <c r="A57" s="2"/>
       <c r="B57" s="7">
         <f>ROW(B57)-ROW($B$2)</f>
         <v>55</v>
       </c>
       <c r="C57" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="F57" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="D57" s="9" t="s">
+      <c r="G57" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="H57" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="E57" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="F57" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="G57" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>253</v>
-      </c>
       <c r="I57" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="J57" s="17"/>
-      <c r="K57" s="18">
+        <v>249</v>
+      </c>
+      <c r="J57" s="16"/>
+      <c r="K57" s="17">
         <v>1</v>
       </c>
       <c r="L57" s="9"/>
     </row>
-    <row r="58" ht="15.75" spans="1:12">
+    <row r="58" spans="1:12">
       <c r="A58" s="2"/>
       <c r="B58" s="7">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
       <c r="C58" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="E58" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="F58" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="D58" s="12" t="s">
+      <c r="G58" s="13" t="s">
         <v>255</v>
-      </c>
-      <c r="E58" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="F58" s="12" t="s">
-        <v>257</v>
-      </c>
-      <c r="G58" s="13" t="s">
-        <v>258</v>
       </c>
       <c r="H58" s="12" t="s">
         <v>31</v>
       </c>
       <c r="I58" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="J58" s="19"/>
-      <c r="K58" s="20">
+        <v>256</v>
+      </c>
+      <c r="J58" s="18"/>
+      <c r="K58" s="19">
         <v>1</v>
       </c>
       <c r="L58" s="12"/>
     </row>
-    <row r="59" ht="24.75" spans="1:12">
+    <row r="59" spans="1:12" ht="24">
       <c r="A59" s="2"/>
       <c r="B59" s="7">
         <f>ROW(B59)-ROW($B$2)</f>
         <v>57</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D59" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="E59" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="G59" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="H59" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="E59" s="10" t="s">
+      <c r="I59" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="F59" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="G59" s="10" t="s">
-        <v>262</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="I59" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="J59" s="17"/>
-      <c r="K59" s="18">
+      <c r="J59" s="16"/>
+      <c r="K59" s="17">
         <v>1</v>
       </c>
       <c r="L59" s="9"/>
     </row>
-    <row r="60" ht="36.75" spans="1:12">
+    <row r="60" spans="1:12" ht="36">
       <c r="A60" s="2"/>
       <c r="B60" s="7">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D60" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="E60" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="F60" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="G60" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="H60" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="E60" s="13" t="s">
+      <c r="I60" s="13" t="s">
         <v>266</v>
       </c>
-      <c r="F60" s="12" t="s">
-        <v>267</v>
-      </c>
-      <c r="G60" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="H60" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="I60" s="13" t="s">
-        <v>269</v>
-      </c>
-      <c r="J60" s="19"/>
-      <c r="K60" s="20">
+      <c r="J60" s="18"/>
+      <c r="K60" s="19">
         <v>1</v>
       </c>
       <c r="L60" s="12"/>
     </row>
-    <row r="61" ht="15.75" spans="1:12">
+    <row r="61" spans="1:12" ht="24">
       <c r="A61" s="2"/>
       <c r="B61" s="7">
         <f>ROW(B61)-ROW($B$2)</f>
         <v>59</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D61" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="E61" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="G61" s="10" t="s">
         <v>270</v>
-      </c>
-      <c r="E61" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="F61" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="G61" s="10" t="s">
-        <v>273</v>
       </c>
       <c r="H61" s="9" t="s">
         <v>31</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>274</v>
-      </c>
-      <c r="J61" s="17"/>
-      <c r="K61" s="18">
+        <v>271</v>
+      </c>
+      <c r="J61" s="16"/>
+      <c r="K61" s="17">
         <v>1</v>
       </c>
       <c r="L61" s="9"/>
     </row>
-    <row r="62" ht="15.75" spans="1:12">
+    <row r="62" spans="1:12">
       <c r="A62" s="2"/>
       <c r="B62" s="7">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D62" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="E62" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="F62" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="G62" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="H62" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="I62" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="E62" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="F62" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="G62" s="13" t="s">
-        <v>277</v>
-      </c>
-      <c r="H62" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="I62" s="13" t="s">
-        <v>278</v>
-      </c>
-      <c r="J62" s="19"/>
-      <c r="K62" s="20">
+      <c r="J62" s="18"/>
+      <c r="K62" s="19">
         <v>1</v>
       </c>
       <c r="L62" s="12"/>
     </row>
-    <row r="63" ht="24.75" spans="1:12">
+    <row r="63" spans="1:12" ht="24">
       <c r="A63" s="2"/>
       <c r="B63" s="7">
         <f>ROW(B63)-ROW($B$2)</f>
         <v>61</v>
       </c>
       <c r="C63" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="E63" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="F63" s="9" t="s">
         <v>279</v>
       </c>
-      <c r="D63" s="9" t="s">
+      <c r="G63" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="E63" s="10" t="s">
+      <c r="H63" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="F63" s="9" t="s">
+      <c r="I63" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="G63" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="I63" s="10" t="s">
-        <v>285</v>
-      </c>
-      <c r="J63" s="17"/>
-      <c r="K63" s="18">
+      <c r="J63" s="16"/>
+      <c r="K63" s="17">
         <v>1</v>
       </c>
       <c r="L63" s="9"/>
     </row>
-    <row r="64" ht="24.75" spans="1:12">
+    <row r="64" spans="1:12" ht="24">
       <c r="A64" s="2"/>
       <c r="B64" s="7">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
       <c r="C64" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="D64" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="E64" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="F64" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="D64" s="12" t="s">
+      <c r="G64" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="H64" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="I64" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="E64" s="13" t="s">
-        <v>287</v>
-      </c>
-      <c r="F64" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="G64" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="H64" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="I64" s="13" t="s">
-        <v>289</v>
-      </c>
-      <c r="J64" s="19"/>
-      <c r="K64" s="20">
+      <c r="J64" s="18"/>
+      <c r="K64" s="19">
         <v>2</v>
       </c>
       <c r="L64" s="12"/>
     </row>
-    <row r="65" ht="15.75" spans="1:12">
+    <row r="65" spans="1:12">
       <c r="A65" s="2"/>
       <c r="B65" s="7">
         <f>ROW(B65)-ROW($B$2)</f>
         <v>63</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D65" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="E65" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="G65" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="E65" s="10" t="s">
+      <c r="H65" s="9" t="s">
         <v>291</v>
       </c>
-      <c r="F65" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="G65" s="10" t="s">
-        <v>293</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>294</v>
-      </c>
       <c r="I65" s="10" t="s">
-        <v>293</v>
-      </c>
-      <c r="J65" s="17"/>
-      <c r="K65" s="18">
+        <v>290</v>
+      </c>
+      <c r="J65" s="16"/>
+      <c r="K65" s="17">
         <v>1</v>
       </c>
       <c r="L65" s="9"/>
     </row>
-    <row r="66" ht="24.75" spans="1:12">
+    <row r="66" spans="1:12" ht="24">
       <c r="A66" s="2"/>
       <c r="B66" s="7">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="C66" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="E66" s="13" t="s">
+        <v>294</v>
+      </c>
+      <c r="F66" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="D66" s="12" t="s">
+      <c r="G66" s="13" t="s">
+        <v>295</v>
+      </c>
+      <c r="H66" s="12" t="s">
         <v>296</v>
       </c>
-      <c r="E66" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="F66" s="12" t="s">
-        <v>298</v>
-      </c>
-      <c r="G66" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="H66" s="12" t="s">
-        <v>299</v>
-      </c>
       <c r="I66" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="J66" s="19"/>
-      <c r="K66" s="20">
+        <v>295</v>
+      </c>
+      <c r="J66" s="18"/>
+      <c r="K66" s="19">
         <v>4</v>
       </c>
       <c r="L66" s="12"/>
     </row>
-    <row r="67" ht="15.75" spans="1:12">
+    <row r="67" spans="1:12">
       <c r="A67" s="2"/>
       <c r="B67" s="7">
         <f>ROW(B67)-ROW($B$2)</f>
         <v>65</v>
       </c>
       <c r="C67" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="E67" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="F67" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="D67" s="9" t="s">
+      <c r="G67" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="H67" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="E67" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="F67" s="9" t="s">
-        <v>303</v>
-      </c>
-      <c r="G67" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>304</v>
-      </c>
       <c r="I67" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="J67" s="17"/>
-      <c r="K67" s="18">
+        <v>300</v>
+      </c>
+      <c r="J67" s="16"/>
+      <c r="K67" s="17">
         <v>1</v>
       </c>
       <c r="L67" s="9"/>
     </row>
-    <row r="68" ht="15.75" spans="1:12">
+    <row r="68" spans="1:12">
       <c r="A68" s="2"/>
       <c r="B68" s="7">
         <f>ROW(B68)-ROW($B$2)</f>
         <v>66</v>
       </c>
       <c r="C68" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="D68" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="E68" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="F68" s="20" t="s">
         <v>305</v>
       </c>
-      <c r="D68" s="21" t="s">
+      <c r="G68" s="21" t="s">
         <v>306</v>
       </c>
-      <c r="E68" s="22" t="s">
+      <c r="H68" s="20" t="s">
         <v>307</v>
       </c>
-      <c r="F68" s="21" t="s">
+      <c r="I68" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="J68" s="22"/>
+      <c r="K68" s="23">
+        <v>1</v>
+      </c>
+      <c r="L68" s="20" t="s">
         <v>308</v>
       </c>
-      <c r="G68" s="22" t="s">
-        <v>309</v>
-      </c>
-      <c r="H68" s="21" t="s">
-        <v>310</v>
-      </c>
-      <c r="I68" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="J68" s="23"/>
-      <c r="K68" s="24">
-        <v>1</v>
-      </c>
-      <c r="L68" s="21" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="69" ht="15.75" spans="1:12">
+    </row>
+    <row r="69" spans="1:12">
       <c r="A69" s="2"/>
       <c r="B69" s="7">
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
       <c r="C69" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="E69" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="F69" s="12" t="s">
         <v>305</v>
       </c>
-      <c r="D69" s="12" t="s">
-        <v>312</v>
-      </c>
-      <c r="E69" s="13" t="s">
+      <c r="G69" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="H69" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="F69" s="12" t="s">
-        <v>308</v>
-      </c>
-      <c r="G69" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="H69" s="12" t="s">
-        <v>310</v>
-      </c>
       <c r="I69" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="J69" s="19"/>
-      <c r="K69" s="20">
+        <v>306</v>
+      </c>
+      <c r="J69" s="18"/>
+      <c r="K69" s="19">
         <v>1</v>
       </c>
       <c r="L69" s="12"/>
     </row>
-    <row r="70" ht="48.75" spans="1:12">
+    <row r="70" spans="1:12" ht="48">
       <c r="A70" s="2"/>
       <c r="B70" s="7">
         <f>ROW(B70)-ROW($B$2)</f>
         <v>68</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D70" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="E70" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="F70" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="G70" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="E70" s="10" t="s">
-        <v>314</v>
-      </c>
-      <c r="F70" s="9" t="s">
-        <v>315</v>
-      </c>
-      <c r="G70" s="10" t="s">
-        <v>316</v>
-      </c>
       <c r="H70" s="9" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="I70" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="J70" s="17"/>
-      <c r="K70" s="18">
+        <v>313</v>
+      </c>
+      <c r="J70" s="16"/>
+      <c r="K70" s="17">
         <v>1</v>
       </c>
       <c r="L70" s="9"/>
     </row>
-    <row r="71" ht="36.75" spans="1:12">
+    <row r="71" spans="1:12" ht="36">
       <c r="A71" s="2"/>
       <c r="B71" s="7">
         <f t="shared" si="0"/>
         <v>69</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F71" s="12" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G71" s="13" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="H71" s="12" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I71" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="J71" s="19"/>
-      <c r="K71" s="20">
+        <v>316</v>
+      </c>
+      <c r="J71" s="18"/>
+      <c r="K71" s="19">
         <v>2</v>
       </c>
       <c r="L71" s="12"/>
     </row>
-    <row r="72" ht="15.75" spans="1:12">
+    <row r="72" spans="1:12">
       <c r="A72" s="2"/>
       <c r="B72" s="7">
         <f>ROW(B72)-ROW($B$2)</f>
         <v>70</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D72" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="F72" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="G72" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="H72" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="I72" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="E72" s="10" t="s">
-        <v>321</v>
-      </c>
-      <c r="F72" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="G72" s="10" t="s">
-        <v>322</v>
-      </c>
-      <c r="H72" s="9" t="s">
-        <v>310</v>
-      </c>
-      <c r="I72" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="J72" s="17"/>
-      <c r="K72" s="18">
+      <c r="J72" s="16"/>
+      <c r="K72" s="17">
         <v>1</v>
       </c>
       <c r="L72" s="9"/>
     </row>
-    <row r="73" ht="24.75" spans="1:12">
+    <row r="73" spans="1:12" ht="24">
       <c r="A73" s="2"/>
       <c r="B73" s="7">
         <f t="shared" si="0"/>
         <v>71</v>
       </c>
       <c r="C73" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="E73" s="13" t="s">
+        <v>322</v>
+      </c>
+      <c r="F73" s="12" t="s">
         <v>305</v>
       </c>
-      <c r="D73" s="12" t="s">
+      <c r="G73" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="H73" s="12" t="s">
         <v>324</v>
       </c>
-      <c r="E73" s="13" t="s">
-        <v>325</v>
-      </c>
-      <c r="F73" s="12" t="s">
-        <v>308</v>
-      </c>
-      <c r="G73" s="13" t="s">
-        <v>326</v>
-      </c>
-      <c r="H73" s="12" t="s">
-        <v>327</v>
-      </c>
       <c r="I73" s="13" t="s">
-        <v>326</v>
-      </c>
-      <c r="J73" s="19"/>
-      <c r="K73" s="20">
+        <v>323</v>
+      </c>
+      <c r="J73" s="18"/>
+      <c r="K73" s="19">
         <v>1</v>
       </c>
       <c r="L73" s="12"/>
     </row>
-    <row r="74" ht="15.75" spans="1:12">
+    <row r="74" spans="1:12">
       <c r="A74" s="2"/>
       <c r="B74" s="7">
         <f>ROW(B74)-ROW($B$2)</f>
         <v>72</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D74" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="E74" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="F74" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="G74" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="E74" s="10" t="s">
+      <c r="H74" s="9" t="s">
         <v>329</v>
       </c>
-      <c r="F74" s="9" t="s">
-        <v>330</v>
-      </c>
-      <c r="G74" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="H74" s="9" t="s">
-        <v>332</v>
-      </c>
       <c r="I74" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="J74" s="17"/>
-      <c r="K74" s="18">
+        <v>328</v>
+      </c>
+      <c r="J74" s="16"/>
+      <c r="K74" s="17">
         <v>1</v>
       </c>
       <c r="L74" s="9"/>
@@ -5655,160 +5078,160 @@
         <v>73</v>
       </c>
       <c r="C75" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="E75" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="F75" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="D75" s="12" t="s">
+      <c r="G75" s="13" t="s">
         <v>334</v>
-      </c>
-      <c r="E75" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="F75" s="12" t="s">
-        <v>336</v>
-      </c>
-      <c r="G75" s="13" t="s">
-        <v>337</v>
       </c>
       <c r="H75" s="12" t="s">
         <v>21</v>
       </c>
       <c r="I75" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="J75" s="19"/>
-      <c r="K75" s="20">
+        <v>335</v>
+      </c>
+      <c r="J75" s="18"/>
+      <c r="K75" s="19">
         <v>4</v>
       </c>
       <c r="L75" s="12"/>
     </row>
-    <row r="76" ht="15.75" spans="1:12">
+    <row r="76" spans="1:12">
       <c r="A76" s="2"/>
       <c r="B76" s="7">
         <f>ROW(B76)-ROW($B$2)</f>
         <v>74</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D76" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="F76" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="G76" s="10" t="s">
         <v>339</v>
-      </c>
-      <c r="E76" s="10" t="s">
-        <v>340</v>
-      </c>
-      <c r="F76" s="9" t="s">
-        <v>341</v>
-      </c>
-      <c r="G76" s="10" t="s">
-        <v>342</v>
       </c>
       <c r="H76" s="9" t="s">
         <v>21</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>343</v>
-      </c>
-      <c r="J76" s="17"/>
-      <c r="K76" s="18">
+        <v>340</v>
+      </c>
+      <c r="J76" s="16"/>
+      <c r="K76" s="17">
         <v>2</v>
       </c>
       <c r="L76" s="9"/>
     </row>
-    <row r="77" ht="24.75" spans="1:12">
+    <row r="77" spans="1:12" ht="36">
       <c r="A77" s="2"/>
       <c r="B77" s="7">
         <f t="shared" si="0"/>
         <v>75</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="F77" s="12" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G77" s="13" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="H77" s="12" t="s">
         <v>21</v>
       </c>
       <c r="I77" s="13" t="s">
-        <v>347</v>
-      </c>
-      <c r="J77" s="19"/>
-      <c r="K77" s="20">
+        <v>344</v>
+      </c>
+      <c r="J77" s="18"/>
+      <c r="K77" s="19">
         <v>20</v>
       </c>
       <c r="L77" s="12"/>
     </row>
-    <row r="78" ht="15.75" spans="1:12">
+    <row r="78" spans="1:12">
       <c r="A78" s="2"/>
       <c r="B78" s="7">
         <f>ROW(B78)-ROW($B$2)</f>
         <v>76</v>
       </c>
       <c r="C78" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="E78" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="F78" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="D78" s="9" t="s">
-        <v>348</v>
-      </c>
-      <c r="E78" s="10" t="s">
-        <v>349</v>
-      </c>
-      <c r="F78" s="9" t="s">
-        <v>336</v>
-      </c>
       <c r="G78" s="10" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="H78" s="9" t="s">
         <v>21</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>351</v>
-      </c>
-      <c r="J78" s="17"/>
-      <c r="K78" s="18">
+        <v>348</v>
+      </c>
+      <c r="J78" s="16"/>
+      <c r="K78" s="17">
         <v>6</v>
       </c>
       <c r="L78" s="9"/>
     </row>
-    <row r="79" ht="15.75" spans="1:12">
+    <row r="79" spans="1:12">
       <c r="A79" s="2"/>
       <c r="B79" s="7">
         <f t="shared" si="0"/>
         <v>77</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F79" s="12" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G79" s="13" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="H79" s="12" t="s">
         <v>21</v>
       </c>
       <c r="I79" s="13" t="s">
-        <v>355</v>
-      </c>
-      <c r="J79" s="19"/>
-      <c r="K79" s="20">
+        <v>352</v>
+      </c>
+      <c r="J79" s="18"/>
+      <c r="K79" s="19">
         <v>2</v>
       </c>
       <c r="L79" s="12"/>
@@ -5820,2008 +5243,2008 @@
         <v>78</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="F80" s="9" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G80" s="10" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="H80" s="9" t="s">
         <v>21</v>
       </c>
       <c r="I80" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="J80" s="17"/>
-      <c r="K80" s="18">
+        <v>356</v>
+      </c>
+      <c r="J80" s="16"/>
+      <c r="K80" s="17">
         <v>1</v>
       </c>
       <c r="L80" s="9"/>
     </row>
-    <row r="81" ht="15.75" spans="1:12">
+    <row r="81" spans="1:12">
       <c r="A81" s="2"/>
       <c r="B81" s="7">
         <f t="shared" si="0"/>
         <v>79</v>
       </c>
       <c r="C81" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="D81" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="E81" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="F81" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="D81" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="E81" s="13" t="s">
-        <v>361</v>
-      </c>
-      <c r="F81" s="12" t="s">
-        <v>336</v>
-      </c>
       <c r="G81" s="13" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="H81" s="12" t="s">
         <v>21</v>
       </c>
       <c r="I81" s="13" t="s">
-        <v>363</v>
-      </c>
-      <c r="J81" s="19"/>
-      <c r="K81" s="20">
+        <v>360</v>
+      </c>
+      <c r="J81" s="18"/>
+      <c r="K81" s="19">
         <v>1</v>
       </c>
       <c r="L81" s="12"/>
     </row>
-    <row r="82" ht="15.75" spans="1:12">
+    <row r="82" spans="1:12">
       <c r="A82" s="2"/>
       <c r="B82" s="7">
         <f>ROW(B82)-ROW($B$2)</f>
         <v>80</v>
       </c>
       <c r="C82" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="E82" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="F82" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="D82" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="E82" s="10" t="s">
-        <v>365</v>
-      </c>
-      <c r="F82" s="9" t="s">
-        <v>336</v>
-      </c>
       <c r="G82" s="10" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="H82" s="9" t="s">
         <v>21</v>
       </c>
       <c r="I82" s="10" t="s">
-        <v>367</v>
-      </c>
-      <c r="J82" s="17"/>
-      <c r="K82" s="18">
+        <v>364</v>
+      </c>
+      <c r="J82" s="16"/>
+      <c r="K82" s="17">
         <v>1</v>
       </c>
       <c r="L82" s="9"/>
     </row>
-    <row r="83" ht="15.75" spans="1:12">
+    <row r="83" spans="1:12">
       <c r="A83" s="2"/>
       <c r="B83" s="7">
         <f t="shared" si="0"/>
         <v>81</v>
       </c>
       <c r="C83" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="D83" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="E83" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="F83" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="D83" s="12" t="s">
-        <v>368</v>
-      </c>
-      <c r="E83" s="13" t="s">
-        <v>369</v>
-      </c>
-      <c r="F83" s="12" t="s">
-        <v>336</v>
-      </c>
       <c r="G83" s="13" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="H83" s="12" t="s">
         <v>21</v>
       </c>
       <c r="I83" s="13" t="s">
-        <v>371</v>
-      </c>
-      <c r="J83" s="19"/>
-      <c r="K83" s="20">
+        <v>368</v>
+      </c>
+      <c r="J83" s="18"/>
+      <c r="K83" s="19">
         <v>1</v>
       </c>
       <c r="L83" s="12"/>
     </row>
-    <row r="84" ht="15.75" spans="1:12">
+    <row r="84" spans="1:12">
       <c r="A84" s="2"/>
       <c r="B84" s="7">
         <f>ROW(B84)-ROW($B$2)</f>
         <v>82</v>
       </c>
       <c r="C84" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="E84" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="F84" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="D84" s="9" t="s">
-        <v>372</v>
-      </c>
-      <c r="E84" s="10" t="s">
-        <v>373</v>
-      </c>
-      <c r="F84" s="9" t="s">
-        <v>336</v>
-      </c>
       <c r="G84" s="10" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="H84" s="9" t="s">
         <v>21</v>
       </c>
       <c r="I84" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="J84" s="17"/>
-      <c r="K84" s="18">
+        <v>164</v>
+      </c>
+      <c r="J84" s="16"/>
+      <c r="K84" s="17">
         <v>1</v>
       </c>
       <c r="L84" s="9"/>
     </row>
-    <row r="85" ht="15.75" spans="1:12">
+    <row r="85" spans="1:12">
       <c r="A85" s="2"/>
       <c r="B85" s="7">
         <f t="shared" si="0"/>
         <v>83</v>
       </c>
       <c r="C85" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="D85" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="E85" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="F85" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="D85" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="E85" s="13" t="s">
-        <v>376</v>
-      </c>
-      <c r="F85" s="12" t="s">
-        <v>336</v>
-      </c>
       <c r="G85" s="13" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="H85" s="12" t="s">
         <v>21</v>
       </c>
       <c r="I85" s="13" t="s">
-        <v>378</v>
-      </c>
-      <c r="J85" s="19"/>
-      <c r="K85" s="20">
+        <v>375</v>
+      </c>
+      <c r="J85" s="18"/>
+      <c r="K85" s="19">
         <v>1</v>
       </c>
       <c r="L85" s="12"/>
     </row>
-    <row r="86" ht="15.75" spans="1:12">
+    <row r="86" spans="1:12">
       <c r="A86" s="2"/>
       <c r="B86" s="7">
         <f>ROW(B86)-ROW($B$2)</f>
         <v>84</v>
       </c>
       <c r="C86" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="E86" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="F86" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="D86" s="9" t="s">
-        <v>379</v>
-      </c>
-      <c r="E86" s="10" t="s">
-        <v>380</v>
-      </c>
-      <c r="F86" s="9" t="s">
-        <v>336</v>
-      </c>
       <c r="G86" s="10" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="H86" s="9" t="s">
         <v>21</v>
       </c>
       <c r="I86" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="J86" s="17"/>
-      <c r="K86" s="18">
+        <v>379</v>
+      </c>
+      <c r="J86" s="16"/>
+      <c r="K86" s="17">
         <v>1</v>
       </c>
       <c r="L86" s="9"/>
     </row>
-    <row r="87" ht="15.75" spans="1:12">
+    <row r="87" spans="1:12">
       <c r="A87" s="2"/>
       <c r="B87" s="7">
         <f t="shared" si="0"/>
         <v>85</v>
       </c>
       <c r="C87" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="D87" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="E87" s="13" t="s">
+        <v>381</v>
+      </c>
+      <c r="F87" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="D87" s="12" t="s">
-        <v>383</v>
-      </c>
-      <c r="E87" s="13" t="s">
-        <v>384</v>
-      </c>
-      <c r="F87" s="12" t="s">
-        <v>336</v>
-      </c>
       <c r="G87" s="13" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="H87" s="12" t="s">
         <v>21</v>
       </c>
       <c r="I87" s="13" t="s">
-        <v>386</v>
-      </c>
-      <c r="J87" s="19"/>
-      <c r="K87" s="20">
+        <v>383</v>
+      </c>
+      <c r="J87" s="18"/>
+      <c r="K87" s="19">
         <v>1</v>
       </c>
       <c r="L87" s="12"/>
     </row>
-    <row r="88" ht="15.75" spans="1:12">
+    <row r="88" spans="1:12">
       <c r="A88" s="2"/>
       <c r="B88" s="7">
         <f>ROW(B88)-ROW($B$2)</f>
         <v>86</v>
       </c>
       <c r="C88" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="E88" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="F88" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="D88" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="E88" s="10" t="s">
-        <v>373</v>
-      </c>
-      <c r="F88" s="9" t="s">
-        <v>336</v>
-      </c>
       <c r="G88" s="10" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="H88" s="9" t="s">
         <v>21</v>
       </c>
       <c r="I88" s="10" t="s">
-        <v>388</v>
-      </c>
-      <c r="J88" s="17"/>
-      <c r="K88" s="18">
+        <v>385</v>
+      </c>
+      <c r="J88" s="16"/>
+      <c r="K88" s="17">
         <v>2</v>
       </c>
       <c r="L88" s="9"/>
     </row>
-    <row r="89" ht="15.75" spans="1:12">
+    <row r="89" spans="1:12">
       <c r="A89" s="2"/>
       <c r="B89" s="7">
         <f t="shared" si="0"/>
         <v>87</v>
       </c>
       <c r="C89" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="D89" s="12" t="s">
+        <v>386</v>
+      </c>
+      <c r="E89" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="F89" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="D89" s="12" t="s">
-        <v>389</v>
-      </c>
-      <c r="E89" s="13" t="s">
-        <v>390</v>
-      </c>
-      <c r="F89" s="12" t="s">
-        <v>336</v>
-      </c>
       <c r="G89" s="13" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="H89" s="12" t="s">
         <v>21</v>
       </c>
       <c r="I89" s="13" t="s">
-        <v>392</v>
-      </c>
-      <c r="J89" s="19"/>
-      <c r="K89" s="20">
+        <v>389</v>
+      </c>
+      <c r="J89" s="18"/>
+      <c r="K89" s="19">
         <v>1</v>
       </c>
       <c r="L89" s="12"/>
     </row>
-    <row r="90" ht="15.75" spans="1:12">
+    <row r="90" spans="1:12">
       <c r="A90" s="2"/>
       <c r="B90" s="7">
         <f>ROW(B90)-ROW($B$2)</f>
         <v>88</v>
       </c>
       <c r="C90" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="E90" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="F90" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="D90" s="9" t="s">
-        <v>393</v>
-      </c>
-      <c r="E90" s="10" t="s">
-        <v>394</v>
-      </c>
-      <c r="F90" s="9" t="s">
-        <v>336</v>
-      </c>
       <c r="G90" s="10" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="H90" s="9" t="s">
         <v>21</v>
       </c>
       <c r="I90" s="10" t="s">
-        <v>347</v>
-      </c>
-      <c r="J90" s="17"/>
-      <c r="K90" s="18">
+        <v>344</v>
+      </c>
+      <c r="J90" s="16"/>
+      <c r="K90" s="17">
         <v>6</v>
       </c>
       <c r="L90" s="9"/>
     </row>
-    <row r="91" ht="15.75" spans="1:12">
+    <row r="91" spans="1:12">
       <c r="A91" s="2"/>
       <c r="B91" s="7">
         <f t="shared" si="0"/>
         <v>89</v>
       </c>
       <c r="C91" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="D91" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="E91" s="13" t="s">
+        <v>394</v>
+      </c>
+      <c r="F91" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="D91" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="E91" s="13" t="s">
-        <v>397</v>
-      </c>
-      <c r="F91" s="12" t="s">
-        <v>336</v>
-      </c>
       <c r="G91" s="13" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="H91" s="12" t="s">
         <v>21</v>
       </c>
       <c r="I91" s="13" t="s">
-        <v>399</v>
-      </c>
-      <c r="J91" s="19"/>
-      <c r="K91" s="20">
+        <v>396</v>
+      </c>
+      <c r="J91" s="18"/>
+      <c r="K91" s="19">
         <v>3</v>
       </c>
       <c r="L91" s="12"/>
     </row>
-    <row r="92" ht="15.75" spans="1:12">
+    <row r="92" spans="1:12">
       <c r="A92" s="2"/>
       <c r="B92" s="7">
         <f>ROW(B92)-ROW($B$2)</f>
         <v>90</v>
       </c>
       <c r="C92" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="E92" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="F92" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="D92" s="9" t="s">
-        <v>400</v>
-      </c>
-      <c r="E92" s="10" t="s">
-        <v>401</v>
-      </c>
-      <c r="F92" s="9" t="s">
-        <v>336</v>
-      </c>
       <c r="G92" s="10" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="H92" s="9" t="s">
         <v>21</v>
       </c>
       <c r="I92" s="10" t="s">
-        <v>403</v>
-      </c>
-      <c r="J92" s="17"/>
-      <c r="K92" s="18">
+        <v>400</v>
+      </c>
+      <c r="J92" s="16"/>
+      <c r="K92" s="17">
         <v>1</v>
       </c>
       <c r="L92" s="9"/>
     </row>
-    <row r="93" ht="36.75" spans="1:12">
+    <row r="93" spans="1:12" ht="36">
       <c r="A93" s="2"/>
       <c r="B93" s="7">
         <f t="shared" si="0"/>
         <v>91</v>
       </c>
       <c r="C93" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="D93" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="E93" s="13" t="s">
+        <v>402</v>
+      </c>
+      <c r="F93" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="D93" s="12" t="s">
+      <c r="G93" s="13" t="s">
+        <v>403</v>
+      </c>
+      <c r="H93" s="12" t="s">
         <v>404</v>
       </c>
-      <c r="E93" s="13" t="s">
+      <c r="I93" s="13" t="s">
         <v>405</v>
       </c>
-      <c r="F93" s="12" t="s">
-        <v>336</v>
-      </c>
-      <c r="G93" s="13" t="s">
-        <v>406</v>
-      </c>
-      <c r="H93" s="12" t="s">
-        <v>407</v>
-      </c>
-      <c r="I93" s="13" t="s">
-        <v>408</v>
-      </c>
-      <c r="J93" s="19"/>
-      <c r="K93" s="20">
+      <c r="J93" s="18"/>
+      <c r="K93" s="19">
         <v>1</v>
       </c>
       <c r="L93" s="12"/>
     </row>
-    <row r="94" ht="15.75" spans="1:12">
+    <row r="94" spans="1:12">
       <c r="A94" s="2"/>
       <c r="B94" s="7">
         <f>ROW(B94)-ROW($B$2)</f>
         <v>92</v>
       </c>
       <c r="C94" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="D94" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="E94" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="F94" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="D94" s="9" t="s">
-        <v>409</v>
-      </c>
-      <c r="E94" s="10" t="s">
-        <v>410</v>
-      </c>
-      <c r="F94" s="9" t="s">
-        <v>336</v>
-      </c>
       <c r="G94" s="10" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="H94" s="9" t="s">
         <v>21</v>
       </c>
       <c r="I94" s="10" t="s">
-        <v>412</v>
-      </c>
-      <c r="J94" s="17"/>
-      <c r="K94" s="18">
+        <v>409</v>
+      </c>
+      <c r="J94" s="16"/>
+      <c r="K94" s="17">
         <v>1</v>
       </c>
       <c r="L94" s="9"/>
     </row>
-    <row r="95" ht="15.75" spans="1:12">
+    <row r="95" spans="1:12">
       <c r="A95" s="2"/>
       <c r="B95" s="7">
         <f t="shared" si="0"/>
         <v>93</v>
       </c>
       <c r="C95" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="D95" s="12" t="s">
+        <v>410</v>
+      </c>
+      <c r="E95" s="13" t="s">
+        <v>411</v>
+      </c>
+      <c r="F95" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="D95" s="12" t="s">
-        <v>413</v>
-      </c>
-      <c r="E95" s="13" t="s">
-        <v>414</v>
-      </c>
-      <c r="F95" s="12" t="s">
-        <v>336</v>
-      </c>
       <c r="G95" s="13" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="H95" s="12" t="s">
         <v>21</v>
       </c>
       <c r="I95" s="13" t="s">
-        <v>416</v>
-      </c>
-      <c r="J95" s="19"/>
-      <c r="K95" s="20">
+        <v>413</v>
+      </c>
+      <c r="J95" s="18"/>
+      <c r="K95" s="19">
         <v>2</v>
       </c>
       <c r="L95" s="12"/>
     </row>
-    <row r="96" ht="15.75" spans="1:12">
+    <row r="96" spans="1:12">
       <c r="A96" s="2"/>
       <c r="B96" s="7">
         <f>ROW(B96)-ROW($B$2)</f>
         <v>94</v>
       </c>
       <c r="C96" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="D96" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="E96" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="F96" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="D96" s="9" t="s">
-        <v>417</v>
-      </c>
-      <c r="E96" s="10" t="s">
-        <v>418</v>
-      </c>
-      <c r="F96" s="9" t="s">
-        <v>336</v>
-      </c>
       <c r="G96" s="10" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="H96" s="9" t="s">
         <v>21</v>
       </c>
       <c r="I96" s="10" t="s">
-        <v>420</v>
-      </c>
-      <c r="J96" s="17"/>
-      <c r="K96" s="18">
+        <v>417</v>
+      </c>
+      <c r="J96" s="16"/>
+      <c r="K96" s="17">
         <v>1</v>
       </c>
       <c r="L96" s="9"/>
     </row>
-    <row r="97" ht="15.75" spans="1:12">
+    <row r="97" spans="1:12">
       <c r="A97" s="2"/>
       <c r="B97" s="7">
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
       <c r="C97" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="D97" s="12" t="s">
+        <v>418</v>
+      </c>
+      <c r="E97" s="13" t="s">
+        <v>419</v>
+      </c>
+      <c r="F97" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="D97" s="12" t="s">
-        <v>421</v>
-      </c>
-      <c r="E97" s="13" t="s">
-        <v>422</v>
-      </c>
-      <c r="F97" s="12" t="s">
-        <v>336</v>
-      </c>
       <c r="G97" s="13" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="H97" s="12" t="s">
         <v>21</v>
       </c>
       <c r="I97" s="13" t="s">
-        <v>424</v>
-      </c>
-      <c r="J97" s="19"/>
-      <c r="K97" s="20">
+        <v>421</v>
+      </c>
+      <c r="J97" s="18"/>
+      <c r="K97" s="19">
         <v>4</v>
       </c>
       <c r="L97" s="12"/>
     </row>
-    <row r="98" ht="15.75" spans="1:12">
+    <row r="98" spans="1:12">
       <c r="A98" s="2"/>
       <c r="B98" s="7">
         <f>ROW(B98)-ROW($B$2)</f>
         <v>96</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D98" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="E98" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="F98" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="G98" s="10" t="s">
         <v>425</v>
-      </c>
-      <c r="E98" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="F98" s="9" t="s">
-        <v>427</v>
-      </c>
-      <c r="G98" s="10" t="s">
-        <v>428</v>
       </c>
       <c r="H98" s="9" t="s">
         <v>21</v>
       </c>
       <c r="I98" s="10" t="s">
-        <v>429</v>
-      </c>
-      <c r="J98" s="17"/>
-      <c r="K98" s="18">
+        <v>426</v>
+      </c>
+      <c r="J98" s="16"/>
+      <c r="K98" s="17">
         <v>1</v>
       </c>
       <c r="L98" s="9"/>
     </row>
-    <row r="99" ht="15.75" spans="1:12">
+    <row r="99" spans="1:12">
       <c r="A99" s="2"/>
       <c r="B99" s="7">
         <f t="shared" si="0"/>
         <v>97</v>
       </c>
       <c r="C99" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="D99" s="12" t="s">
+        <v>427</v>
+      </c>
+      <c r="E99" s="13" t="s">
+        <v>428</v>
+      </c>
+      <c r="F99" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="D99" s="12" t="s">
-        <v>430</v>
-      </c>
-      <c r="E99" s="13" t="s">
-        <v>431</v>
-      </c>
-      <c r="F99" s="12" t="s">
-        <v>336</v>
-      </c>
       <c r="G99" s="13" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="H99" s="12" t="s">
         <v>21</v>
       </c>
       <c r="I99" s="13" t="s">
-        <v>433</v>
-      </c>
-      <c r="J99" s="19"/>
-      <c r="K99" s="20">
+        <v>430</v>
+      </c>
+      <c r="J99" s="18"/>
+      <c r="K99" s="19">
         <v>1</v>
       </c>
       <c r="L99" s="12"/>
     </row>
-    <row r="100" ht="15.75" spans="1:12">
+    <row r="100" spans="1:12">
       <c r="A100" s="2"/>
       <c r="B100" s="7">
         <f>ROW(B100)-ROW($B$2)</f>
         <v>98</v>
       </c>
       <c r="C100" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="D100" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="E100" s="10" t="s">
+        <v>432</v>
+      </c>
+      <c r="F100" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="D100" s="9" t="s">
-        <v>434</v>
-      </c>
-      <c r="E100" s="10" t="s">
-        <v>435</v>
-      </c>
-      <c r="F100" s="9" t="s">
-        <v>336</v>
-      </c>
       <c r="G100" s="10" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="H100" s="9" t="s">
         <v>21</v>
       </c>
       <c r="I100" s="10" t="s">
-        <v>437</v>
-      </c>
-      <c r="J100" s="17"/>
-      <c r="K100" s="18">
+        <v>434</v>
+      </c>
+      <c r="J100" s="16"/>
+      <c r="K100" s="17">
         <v>4</v>
       </c>
       <c r="L100" s="9"/>
     </row>
-    <row r="101" ht="15.75" spans="1:12">
+    <row r="101" spans="1:12">
       <c r="A101" s="2"/>
       <c r="B101" s="7">
         <f t="shared" si="0"/>
         <v>99</v>
       </c>
       <c r="C101" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="D101" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="E101" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="F101" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="D101" s="12" t="s">
-        <v>438</v>
-      </c>
-      <c r="E101" s="13" t="s">
-        <v>439</v>
-      </c>
-      <c r="F101" s="12" t="s">
-        <v>336</v>
-      </c>
       <c r="G101" s="13" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H101" s="12" t="s">
         <v>21</v>
       </c>
       <c r="I101" s="13" t="s">
-        <v>441</v>
-      </c>
-      <c r="J101" s="19"/>
-      <c r="K101" s="20">
+        <v>438</v>
+      </c>
+      <c r="J101" s="18"/>
+      <c r="K101" s="19">
         <v>1</v>
       </c>
       <c r="L101" s="12"/>
     </row>
-    <row r="102" ht="15.75" spans="1:12">
+    <row r="102" spans="1:12">
       <c r="A102" s="2"/>
       <c r="B102" s="7">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
       <c r="C102" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="D102" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="E102" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="F102" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="D102" s="9" t="s">
+      <c r="G102" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="H102" s="9" t="s">
         <v>442</v>
       </c>
-      <c r="E102" s="10" t="s">
+      <c r="I102" s="10" t="s">
         <v>443</v>
       </c>
-      <c r="F102" s="9" t="s">
-        <v>336</v>
-      </c>
-      <c r="G102" s="10" t="s">
-        <v>444</v>
-      </c>
-      <c r="H102" s="9" t="s">
-        <v>445</v>
-      </c>
-      <c r="I102" s="10" t="s">
-        <v>446</v>
-      </c>
-      <c r="J102" s="17"/>
-      <c r="K102" s="18">
+      <c r="J102" s="16"/>
+      <c r="K102" s="17">
         <v>1</v>
       </c>
       <c r="L102" s="9"/>
     </row>
-    <row r="103" ht="15.75" spans="1:12">
+    <row r="103" spans="1:12">
       <c r="A103" s="2"/>
       <c r="B103" s="7">
         <f t="shared" si="0"/>
         <v>101</v>
       </c>
       <c r="C103" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="D103" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="E103" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="F103" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="D103" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="E103" s="13" t="s">
-        <v>448</v>
-      </c>
-      <c r="F103" s="12" t="s">
-        <v>336</v>
-      </c>
       <c r="G103" s="13" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="H103" s="12" t="s">
         <v>21</v>
       </c>
       <c r="I103" s="13" t="s">
-        <v>450</v>
-      </c>
-      <c r="J103" s="19"/>
-      <c r="K103" s="20">
+        <v>447</v>
+      </c>
+      <c r="J103" s="18"/>
+      <c r="K103" s="19">
         <v>1</v>
       </c>
       <c r="L103" s="12"/>
     </row>
-    <row r="104" ht="15.75" spans="1:12">
+    <row r="104" spans="1:12">
       <c r="A104" s="2"/>
       <c r="B104" s="7">
         <f t="shared" si="0"/>
         <v>102</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D104" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="E104" s="10" t="s">
+        <v>449</v>
+      </c>
+      <c r="F104" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="G104" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="H104" s="9" t="s">
         <v>451</v>
       </c>
-      <c r="E104" s="10" t="s">
+      <c r="I104" s="10" t="s">
         <v>452</v>
       </c>
-      <c r="F104" s="9" t="s">
-        <v>341</v>
-      </c>
-      <c r="G104" s="10" t="s">
-        <v>453</v>
-      </c>
-      <c r="H104" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="I104" s="10" t="s">
-        <v>455</v>
-      </c>
-      <c r="J104" s="17"/>
-      <c r="K104" s="18">
+      <c r="J104" s="16"/>
+      <c r="K104" s="17">
         <v>1</v>
       </c>
       <c r="L104" s="9"/>
     </row>
-    <row r="105" ht="15.75" spans="1:12">
+    <row r="105" spans="1:12">
       <c r="A105" s="2"/>
       <c r="B105" s="7">
         <f t="shared" si="0"/>
         <v>103</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D105" s="12" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E105" s="13" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="F105" s="12" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G105" s="13" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="H105" s="12" t="s">
         <v>21</v>
       </c>
       <c r="I105" s="13" t="s">
-        <v>399</v>
-      </c>
-      <c r="J105" s="19"/>
-      <c r="K105" s="20">
+        <v>396</v>
+      </c>
+      <c r="J105" s="18"/>
+      <c r="K105" s="19">
         <v>1</v>
       </c>
       <c r="L105" s="12"/>
     </row>
-    <row r="106" ht="15.75" spans="1:12">
+    <row r="106" spans="1:12">
       <c r="A106" s="2"/>
       <c r="B106" s="7">
         <f t="shared" si="0"/>
         <v>104</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="E106" s="10" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="F106" s="9" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G106" s="10" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="H106" s="9" t="s">
         <v>21</v>
       </c>
       <c r="I106" s="10" t="s">
-        <v>462</v>
-      </c>
-      <c r="J106" s="17"/>
-      <c r="K106" s="18">
+        <v>459</v>
+      </c>
+      <c r="J106" s="16"/>
+      <c r="K106" s="17">
         <v>1</v>
       </c>
       <c r="L106" s="9"/>
     </row>
-    <row r="107" ht="15.75" spans="1:12">
+    <row r="107" spans="1:12">
       <c r="A107" s="2"/>
       <c r="B107" s="7">
         <f t="shared" si="0"/>
         <v>105</v>
       </c>
       <c r="C107" s="11" t="s">
+        <v>460</v>
+      </c>
+      <c r="D107" s="12" t="s">
+        <v>461</v>
+      </c>
+      <c r="E107" s="13" t="s">
+        <v>462</v>
+      </c>
+      <c r="F107" s="12" t="s">
         <v>463</v>
       </c>
-      <c r="D107" s="12" t="s">
-        <v>464</v>
-      </c>
-      <c r="E107" s="13" t="s">
-        <v>465</v>
-      </c>
-      <c r="F107" s="12" t="s">
-        <v>466</v>
-      </c>
       <c r="G107" s="13" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="H107" s="12" t="s">
         <v>21</v>
       </c>
       <c r="I107" s="13" t="s">
-        <v>347</v>
-      </c>
-      <c r="J107" s="19"/>
-      <c r="K107" s="20">
+        <v>344</v>
+      </c>
+      <c r="J107" s="18"/>
+      <c r="K107" s="19">
         <v>3</v>
       </c>
       <c r="L107" s="12"/>
     </row>
-    <row r="108" ht="24.75" spans="1:12">
+    <row r="108" spans="1:12" ht="24">
       <c r="A108" s="2"/>
       <c r="B108" s="7">
         <f t="shared" si="0"/>
         <v>106</v>
       </c>
       <c r="C108" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="D108" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="E108" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="F108" s="9" t="s">
         <v>467</v>
       </c>
-      <c r="D108" s="9" t="s">
+      <c r="G108" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="H108" s="9" t="s">
         <v>468</v>
       </c>
-      <c r="E108" s="10" t="s">
-        <v>469</v>
-      </c>
-      <c r="F108" s="9" t="s">
-        <v>470</v>
-      </c>
-      <c r="G108" s="10" t="s">
-        <v>470</v>
-      </c>
-      <c r="H108" s="9" t="s">
-        <v>471</v>
-      </c>
       <c r="I108" s="10" t="s">
-        <v>347</v>
-      </c>
-      <c r="J108" s="17"/>
-      <c r="K108" s="18">
+        <v>344</v>
+      </c>
+      <c r="J108" s="16"/>
+      <c r="K108" s="17">
         <v>1</v>
       </c>
       <c r="L108" s="9"/>
     </row>
-    <row r="109" ht="36.75" spans="1:12">
+    <row r="109" spans="1:12" ht="36">
       <c r="A109" s="2"/>
       <c r="B109" s="7">
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
       <c r="C109" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="D109" s="12" t="s">
+        <v>470</v>
+      </c>
+      <c r="E109" s="13" t="s">
+        <v>471</v>
+      </c>
+      <c r="F109" s="12" t="s">
         <v>472</v>
       </c>
-      <c r="D109" s="12" t="s">
+      <c r="G109" s="13" t="s">
         <v>473</v>
       </c>
-      <c r="E109" s="13" t="s">
+      <c r="H109" s="12" t="s">
         <v>474</v>
       </c>
-      <c r="F109" s="12" t="s">
-        <v>475</v>
-      </c>
-      <c r="G109" s="13" t="s">
-        <v>476</v>
-      </c>
-      <c r="H109" s="12" t="s">
-        <v>477</v>
-      </c>
       <c r="I109" s="13" t="s">
-        <v>476</v>
-      </c>
-      <c r="J109" s="19"/>
-      <c r="K109" s="20">
+        <v>473</v>
+      </c>
+      <c r="J109" s="18"/>
+      <c r="K109" s="19">
         <v>1</v>
       </c>
       <c r="L109" s="12"/>
     </row>
-    <row r="110" ht="36.75" spans="1:12">
+    <row r="110" spans="1:12" ht="36">
       <c r="A110" s="2"/>
       <c r="B110" s="7">
         <f t="shared" si="0"/>
         <v>108</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D110" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="E110" s="10" t="s">
+        <v>476</v>
+      </c>
+      <c r="F110" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="G110" s="10" t="s">
+        <v>477</v>
+      </c>
+      <c r="H110" s="9" t="s">
         <v>478</v>
       </c>
-      <c r="E110" s="10" t="s">
-        <v>479</v>
-      </c>
-      <c r="F110" s="9" t="s">
-        <v>480</v>
-      </c>
-      <c r="G110" s="10" t="s">
-        <v>480</v>
-      </c>
-      <c r="H110" s="9" t="s">
-        <v>481</v>
-      </c>
       <c r="I110" s="10" t="s">
-        <v>480</v>
-      </c>
-      <c r="J110" s="17"/>
-      <c r="K110" s="18">
+        <v>477</v>
+      </c>
+      <c r="J110" s="16"/>
+      <c r="K110" s="17">
         <v>1</v>
       </c>
       <c r="L110" s="9"/>
     </row>
-    <row r="111" ht="24.75" spans="1:12">
+    <row r="111" spans="1:12" ht="24">
       <c r="A111" s="2"/>
       <c r="B111" s="7">
         <f t="shared" si="0"/>
         <v>109</v>
       </c>
       <c r="C111" s="11" t="s">
+        <v>479</v>
+      </c>
+      <c r="D111" s="12" t="s">
+        <v>480</v>
+      </c>
+      <c r="E111" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="F111" s="12" t="s">
         <v>482</v>
       </c>
-      <c r="D111" s="12" t="s">
+      <c r="G111" s="13" t="s">
+        <v>482</v>
+      </c>
+      <c r="H111" s="12" t="s">
         <v>483</v>
       </c>
-      <c r="E111" s="13" t="s">
-        <v>484</v>
-      </c>
-      <c r="F111" s="12" t="s">
-        <v>485</v>
-      </c>
-      <c r="G111" s="13" t="s">
-        <v>485</v>
-      </c>
-      <c r="H111" s="12" t="s">
-        <v>486</v>
-      </c>
       <c r="I111" s="13" t="s">
-        <v>485</v>
-      </c>
-      <c r="J111" s="19"/>
-      <c r="K111" s="20">
+        <v>482</v>
+      </c>
+      <c r="J111" s="18"/>
+      <c r="K111" s="19">
         <v>1</v>
       </c>
       <c r="L111" s="12"/>
     </row>
-    <row r="112" ht="24.75" spans="1:12">
+    <row r="112" spans="1:12" ht="24">
       <c r="A112" s="2"/>
       <c r="B112" s="7">
         <f t="shared" si="0"/>
         <v>110</v>
       </c>
       <c r="C112" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="D112" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="E112" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="F112" s="9" t="s">
         <v>487</v>
       </c>
-      <c r="D112" s="9" t="s">
-        <v>488</v>
-      </c>
-      <c r="E112" s="10" t="s">
-        <v>489</v>
-      </c>
-      <c r="F112" s="9" t="s">
-        <v>490</v>
-      </c>
       <c r="G112" s="10" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="H112" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="I112" s="10" t="s">
-        <v>490</v>
-      </c>
-      <c r="J112" s="17"/>
-      <c r="K112" s="18">
+        <v>487</v>
+      </c>
+      <c r="J112" s="16"/>
+      <c r="K112" s="17">
         <v>1</v>
       </c>
       <c r="L112" s="9"/>
     </row>
-    <row r="113" ht="48.75" spans="1:12">
+    <row r="113" spans="1:12" ht="48">
       <c r="A113" s="2"/>
       <c r="B113" s="7">
         <f t="shared" si="0"/>
         <v>111</v>
       </c>
       <c r="C113" s="11" t="s">
+        <v>488</v>
+      </c>
+      <c r="D113" s="12" t="s">
+        <v>489</v>
+      </c>
+      <c r="E113" s="13" t="s">
+        <v>490</v>
+      </c>
+      <c r="F113" s="12" t="s">
         <v>491</v>
       </c>
-      <c r="D113" s="12" t="s">
+      <c r="G113" s="13" t="s">
         <v>492</v>
       </c>
-      <c r="E113" s="13" t="s">
+      <c r="H113" s="12" t="s">
         <v>493</v>
       </c>
-      <c r="F113" s="12" t="s">
-        <v>494</v>
-      </c>
-      <c r="G113" s="13" t="s">
-        <v>495</v>
-      </c>
-      <c r="H113" s="12" t="s">
-        <v>496</v>
-      </c>
       <c r="I113" s="13" t="s">
-        <v>495</v>
-      </c>
-      <c r="J113" s="19"/>
-      <c r="K113" s="20">
+        <v>492</v>
+      </c>
+      <c r="J113" s="18"/>
+      <c r="K113" s="19">
         <v>1</v>
       </c>
       <c r="L113" s="12"/>
     </row>
-    <row r="114" ht="48.75" spans="1:12">
+    <row r="114" spans="1:12" ht="48">
       <c r="A114" s="2"/>
       <c r="B114" s="7">
         <f t="shared" si="0"/>
         <v>112</v>
       </c>
       <c r="C114" s="8" t="s">
+        <v>488</v>
+      </c>
+      <c r="D114" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="E114" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="F114" s="9" t="s">
         <v>491</v>
       </c>
-      <c r="D114" s="9" t="s">
-        <v>497</v>
-      </c>
-      <c r="E114" s="10" t="s">
-        <v>498</v>
-      </c>
-      <c r="F114" s="9" t="s">
-        <v>494</v>
-      </c>
       <c r="G114" s="10" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="H114" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="I114" s="10" t="s">
         <v>496</v>
       </c>
-      <c r="I114" s="10" t="s">
-        <v>499</v>
-      </c>
-      <c r="J114" s="17"/>
-      <c r="K114" s="18">
+      <c r="J114" s="16"/>
+      <c r="K114" s="17">
         <v>1</v>
       </c>
       <c r="L114" s="9"/>
     </row>
-    <row r="115" ht="36.75" spans="1:12">
+    <row r="115" spans="1:12" ht="36">
       <c r="A115" s="2"/>
       <c r="B115" s="7">
         <f t="shared" si="0"/>
         <v>113</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D115" s="12" t="s">
+        <v>497</v>
+      </c>
+      <c r="E115" s="13" t="s">
+        <v>498</v>
+      </c>
+      <c r="F115" s="12" t="s">
+        <v>499</v>
+      </c>
+      <c r="G115" s="13" t="s">
         <v>500</v>
       </c>
-      <c r="E115" s="13" t="s">
+      <c r="H115" s="12" t="s">
         <v>501</v>
       </c>
-      <c r="F115" s="12" t="s">
-        <v>502</v>
-      </c>
-      <c r="G115" s="13" t="s">
-        <v>503</v>
-      </c>
-      <c r="H115" s="12" t="s">
-        <v>504</v>
-      </c>
       <c r="I115" s="13" t="s">
-        <v>503</v>
-      </c>
-      <c r="J115" s="19"/>
-      <c r="K115" s="20">
+        <v>500</v>
+      </c>
+      <c r="J115" s="18"/>
+      <c r="K115" s="19">
         <v>1</v>
       </c>
       <c r="L115" s="12"/>
     </row>
-    <row r="116" ht="15.75" spans="1:12">
+    <row r="116" spans="1:12" ht="24">
       <c r="A116" s="2"/>
       <c r="B116" s="7">
         <f t="shared" si="0"/>
         <v>114</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D116" s="9" t="s">
+        <v>502</v>
+      </c>
+      <c r="E116" s="10" t="s">
+        <v>503</v>
+      </c>
+      <c r="F116" s="9" t="s">
+        <v>504</v>
+      </c>
+      <c r="G116" s="10" t="s">
         <v>505</v>
       </c>
-      <c r="E116" s="10" t="s">
+      <c r="H116" s="9" t="s">
         <v>506</v>
       </c>
-      <c r="F116" s="9" t="s">
-        <v>507</v>
-      </c>
-      <c r="G116" s="10" t="s">
-        <v>508</v>
-      </c>
-      <c r="H116" s="9" t="s">
-        <v>509</v>
-      </c>
       <c r="I116" s="10" t="s">
-        <v>508</v>
-      </c>
-      <c r="J116" s="17"/>
-      <c r="K116" s="18">
+        <v>505</v>
+      </c>
+      <c r="J116" s="16"/>
+      <c r="K116" s="17">
         <v>1</v>
       </c>
       <c r="L116" s="9"/>
     </row>
-    <row r="117" ht="15.75" spans="1:12">
+    <row r="117" spans="1:12">
       <c r="A117" s="2"/>
       <c r="B117" s="7">
         <f t="shared" si="0"/>
         <v>115</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D117" s="12" t="s">
+        <v>507</v>
+      </c>
+      <c r="E117" s="13" t="s">
+        <v>508</v>
+      </c>
+      <c r="F117" s="12" t="s">
+        <v>509</v>
+      </c>
+      <c r="G117" s="13" t="s">
         <v>510</v>
       </c>
-      <c r="E117" s="13" t="s">
+      <c r="H117" s="12" t="s">
         <v>511</v>
       </c>
-      <c r="F117" s="12" t="s">
-        <v>512</v>
-      </c>
-      <c r="G117" s="13" t="s">
-        <v>513</v>
-      </c>
-      <c r="H117" s="12" t="s">
-        <v>514</v>
-      </c>
       <c r="I117" s="13" t="s">
-        <v>513</v>
-      </c>
-      <c r="J117" s="19"/>
-      <c r="K117" s="20">
+        <v>510</v>
+      </c>
+      <c r="J117" s="18"/>
+      <c r="K117" s="19">
         <v>1</v>
       </c>
       <c r="L117" s="12"/>
     </row>
-    <row r="118" ht="36.75" spans="1:12">
+    <row r="118" spans="1:12" ht="36">
       <c r="A118" s="2"/>
       <c r="B118" s="7">
         <f t="shared" si="0"/>
         <v>116</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D118" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="E118" s="10" t="s">
+        <v>513</v>
+      </c>
+      <c r="F118" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="G118" s="10" t="s">
         <v>515</v>
       </c>
-      <c r="E118" s="10" t="s">
+      <c r="H118" s="9" t="s">
         <v>516</v>
       </c>
-      <c r="F118" s="9" t="s">
-        <v>517</v>
-      </c>
-      <c r="G118" s="10" t="s">
-        <v>518</v>
-      </c>
-      <c r="H118" s="9" t="s">
-        <v>519</v>
-      </c>
       <c r="I118" s="10" t="s">
-        <v>518</v>
-      </c>
-      <c r="J118" s="17"/>
-      <c r="K118" s="18">
+        <v>515</v>
+      </c>
+      <c r="J118" s="16"/>
+      <c r="K118" s="17">
         <v>1</v>
       </c>
       <c r="L118" s="9"/>
     </row>
-    <row r="119" ht="26.25" spans="1:12">
+    <row r="119" spans="1:12" ht="25.5">
       <c r="A119" s="2"/>
       <c r="B119" s="7">
         <f t="shared" si="0"/>
         <v>117</v>
       </c>
       <c r="C119" s="11" t="s">
+        <v>517</v>
+      </c>
+      <c r="D119" s="12" t="s">
+        <v>518</v>
+      </c>
+      <c r="E119" s="13" t="s">
+        <v>519</v>
+      </c>
+      <c r="F119" s="12" t="s">
         <v>520</v>
       </c>
-      <c r="D119" s="12" t="s">
+      <c r="G119" s="13" t="s">
         <v>521</v>
       </c>
-      <c r="E119" s="13" t="s">
+      <c r="H119" s="12" t="s">
         <v>522</v>
       </c>
-      <c r="F119" s="12" t="s">
-        <v>523</v>
-      </c>
-      <c r="G119" s="13" t="s">
-        <v>524</v>
-      </c>
-      <c r="H119" s="12" t="s">
-        <v>525</v>
-      </c>
       <c r="I119" s="13" t="s">
-        <v>524</v>
-      </c>
-      <c r="J119" s="19"/>
-      <c r="K119" s="20">
+        <v>521</v>
+      </c>
+      <c r="J119" s="18"/>
+      <c r="K119" s="19">
         <v>1</v>
       </c>
       <c r="L119" s="12"/>
     </row>
-    <row r="120" ht="36.75" spans="1:12">
+    <row r="120" spans="1:12" ht="36">
       <c r="A120" s="2"/>
       <c r="B120" s="7">
         <f t="shared" si="0"/>
         <v>118</v>
       </c>
       <c r="C120" s="8" t="s">
+        <v>523</v>
+      </c>
+      <c r="D120" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="E120" s="10" t="s">
+        <v>525</v>
+      </c>
+      <c r="F120" s="9" t="s">
         <v>526</v>
       </c>
-      <c r="D120" s="9" t="s">
+      <c r="G120" s="10" t="s">
+        <v>526</v>
+      </c>
+      <c r="H120" s="9" t="s">
         <v>527</v>
       </c>
-      <c r="E120" s="10" t="s">
-        <v>528</v>
-      </c>
-      <c r="F120" s="9" t="s">
-        <v>529</v>
-      </c>
-      <c r="G120" s="10" t="s">
-        <v>529</v>
-      </c>
-      <c r="H120" s="9" t="s">
-        <v>530</v>
-      </c>
       <c r="I120" s="10" t="s">
-        <v>529</v>
-      </c>
-      <c r="J120" s="17"/>
-      <c r="K120" s="18">
+        <v>526</v>
+      </c>
+      <c r="J120" s="16"/>
+      <c r="K120" s="17">
         <v>1</v>
       </c>
       <c r="L120" s="9"/>
     </row>
-    <row r="121" ht="15.75" spans="1:12">
+    <row r="121" spans="1:12">
       <c r="A121" s="2"/>
       <c r="B121" s="7">
         <f t="shared" si="0"/>
         <v>119</v>
       </c>
       <c r="C121" s="11" t="s">
+        <v>528</v>
+      </c>
+      <c r="D121" s="12" t="s">
+        <v>529</v>
+      </c>
+      <c r="E121" s="13" t="s">
+        <v>530</v>
+      </c>
+      <c r="F121" s="12" t="s">
         <v>531</v>
       </c>
-      <c r="D121" s="12" t="s">
+      <c r="G121" s="13" t="s">
+        <v>531</v>
+      </c>
+      <c r="H121" s="12" t="s">
         <v>532</v>
       </c>
-      <c r="E121" s="13" t="s">
-        <v>533</v>
-      </c>
-      <c r="F121" s="12" t="s">
-        <v>534</v>
-      </c>
-      <c r="G121" s="13" t="s">
-        <v>534</v>
-      </c>
-      <c r="H121" s="12" t="s">
-        <v>535</v>
-      </c>
       <c r="I121" s="13" t="s">
-        <v>534</v>
-      </c>
-      <c r="J121" s="19"/>
-      <c r="K121" s="20">
+        <v>531</v>
+      </c>
+      <c r="J121" s="18"/>
+      <c r="K121" s="19">
         <v>1</v>
       </c>
       <c r="L121" s="12"/>
     </row>
-    <row r="122" ht="15.75" spans="1:12">
+    <row r="122" spans="1:12">
       <c r="A122" s="2"/>
       <c r="B122" s="7">
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D122" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="E122" s="10" t="s">
+        <v>534</v>
+      </c>
+      <c r="F122" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="G122" s="10" t="s">
         <v>536</v>
       </c>
-      <c r="E122" s="10" t="s">
+      <c r="H122" s="9" t="s">
         <v>537</v>
       </c>
-      <c r="F122" s="9" t="s">
-        <v>538</v>
-      </c>
-      <c r="G122" s="10" t="s">
-        <v>539</v>
-      </c>
-      <c r="H122" s="9" t="s">
-        <v>540</v>
-      </c>
       <c r="I122" s="10" t="s">
-        <v>539</v>
-      </c>
-      <c r="J122" s="17"/>
-      <c r="K122" s="18">
+        <v>536</v>
+      </c>
+      <c r="J122" s="16"/>
+      <c r="K122" s="17">
         <v>1</v>
       </c>
       <c r="L122" s="9"/>
     </row>
-    <row r="123" ht="15.75" spans="1:12">
+    <row r="123" spans="1:12">
       <c r="A123" s="2"/>
       <c r="B123" s="7">
         <f t="shared" si="0"/>
         <v>121</v>
       </c>
       <c r="C123" s="11" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D123" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="E123" s="13" t="s">
+        <v>539</v>
+      </c>
+      <c r="F123" s="12" t="s">
+        <v>540</v>
+      </c>
+      <c r="G123" s="13" t="s">
         <v>541</v>
       </c>
-      <c r="E123" s="13" t="s">
-        <v>542</v>
-      </c>
-      <c r="F123" s="12" t="s">
-        <v>543</v>
-      </c>
-      <c r="G123" s="13" t="s">
-        <v>544</v>
-      </c>
       <c r="H123" s="12" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="I123" s="13" t="s">
-        <v>544</v>
-      </c>
-      <c r="J123" s="19"/>
-      <c r="K123" s="20">
+        <v>541</v>
+      </c>
+      <c r="J123" s="18"/>
+      <c r="K123" s="19">
         <v>1</v>
       </c>
       <c r="L123" s="12"/>
     </row>
-    <row r="124" ht="15.75" spans="1:12">
+    <row r="124" spans="1:12">
       <c r="A124" s="2"/>
       <c r="B124" s="7">
         <f t="shared" si="0"/>
         <v>122</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D124" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="E124" s="10" t="s">
+        <v>543</v>
+      </c>
+      <c r="F124" s="9" t="s">
+        <v>544</v>
+      </c>
+      <c r="G124" s="10" t="s">
         <v>545</v>
       </c>
-      <c r="E124" s="10" t="s">
+      <c r="H124" s="9" t="s">
         <v>546</v>
       </c>
-      <c r="F124" s="9" t="s">
-        <v>547</v>
-      </c>
-      <c r="G124" s="10" t="s">
-        <v>548</v>
-      </c>
-      <c r="H124" s="9" t="s">
-        <v>549</v>
-      </c>
       <c r="I124" s="10" t="s">
-        <v>548</v>
-      </c>
-      <c r="J124" s="17"/>
-      <c r="K124" s="18">
+        <v>545</v>
+      </c>
+      <c r="J124" s="16"/>
+      <c r="K124" s="17">
         <v>1</v>
       </c>
       <c r="L124" s="9"/>
     </row>
-    <row r="125" ht="15.75" spans="1:12">
+    <row r="125" spans="1:12">
       <c r="A125" s="2"/>
       <c r="B125" s="7">
         <f t="shared" si="0"/>
         <v>123</v>
       </c>
       <c r="C125" s="11" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D125" s="12" t="s">
+        <v>547</v>
+      </c>
+      <c r="E125" s="13" t="s">
+        <v>548</v>
+      </c>
+      <c r="F125" s="12" t="s">
+        <v>549</v>
+      </c>
+      <c r="G125" s="13" t="s">
         <v>550</v>
       </c>
-      <c r="E125" s="13" t="s">
-        <v>551</v>
-      </c>
-      <c r="F125" s="12" t="s">
-        <v>552</v>
-      </c>
-      <c r="G125" s="13" t="s">
-        <v>553</v>
-      </c>
       <c r="H125" s="12" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="I125" s="13" t="s">
-        <v>553</v>
-      </c>
-      <c r="J125" s="19"/>
-      <c r="K125" s="20">
+        <v>550</v>
+      </c>
+      <c r="J125" s="18"/>
+      <c r="K125" s="19">
         <v>1</v>
       </c>
       <c r="L125" s="12"/>
     </row>
-    <row r="126" ht="15.75" spans="1:12">
+    <row r="126" spans="1:12">
       <c r="A126" s="2"/>
       <c r="B126" s="7">
         <f t="shared" si="0"/>
         <v>124</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D126" s="9" t="s">
+        <v>551</v>
+      </c>
+      <c r="E126" s="10" t="s">
+        <v>552</v>
+      </c>
+      <c r="F126" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="G126" s="10" t="s">
         <v>554</v>
       </c>
-      <c r="E126" s="10" t="s">
+      <c r="H126" s="9" t="s">
         <v>555</v>
       </c>
-      <c r="F126" s="9" t="s">
-        <v>556</v>
-      </c>
-      <c r="G126" s="10" t="s">
-        <v>557</v>
-      </c>
-      <c r="H126" s="9" t="s">
-        <v>558</v>
-      </c>
       <c r="I126" s="10" t="s">
-        <v>557</v>
-      </c>
-      <c r="J126" s="17"/>
-      <c r="K126" s="18">
+        <v>554</v>
+      </c>
+      <c r="J126" s="16"/>
+      <c r="K126" s="17">
         <v>1</v>
       </c>
       <c r="L126" s="9"/>
     </row>
-    <row r="127" ht="15.75" spans="1:12">
+    <row r="127" spans="1:12">
       <c r="A127" s="2"/>
       <c r="B127" s="7">
         <f t="shared" si="0"/>
         <v>125</v>
       </c>
       <c r="C127" s="11" t="s">
+        <v>556</v>
+      </c>
+      <c r="D127" s="12" t="s">
+        <v>557</v>
+      </c>
+      <c r="E127" s="13" t="s">
+        <v>558</v>
+      </c>
+      <c r="F127" s="12" t="s">
         <v>559</v>
       </c>
-      <c r="D127" s="12" t="s">
+      <c r="G127" s="13" t="s">
         <v>560</v>
       </c>
-      <c r="E127" s="13" t="s">
+      <c r="H127" s="12" t="s">
         <v>561</v>
       </c>
-      <c r="F127" s="12" t="s">
+      <c r="I127" s="13" t="s">
         <v>562</v>
       </c>
-      <c r="G127" s="13" t="s">
-        <v>563</v>
-      </c>
-      <c r="H127" s="12" t="s">
-        <v>564</v>
-      </c>
-      <c r="I127" s="13" t="s">
-        <v>565</v>
-      </c>
-      <c r="J127" s="19"/>
-      <c r="K127" s="20">
+      <c r="J127" s="18"/>
+      <c r="K127" s="19">
         <v>1</v>
       </c>
       <c r="L127" s="12"/>
     </row>
-    <row r="128" ht="15.75" spans="1:12">
+    <row r="128" spans="1:12">
       <c r="A128" s="2"/>
       <c r="B128" s="7">
         <f t="shared" si="0"/>
         <v>126</v>
       </c>
       <c r="C128" s="8" t="s">
+        <v>563</v>
+      </c>
+      <c r="D128" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="E128" s="10" t="s">
+        <v>565</v>
+      </c>
+      <c r="F128" s="9" t="s">
         <v>566</v>
       </c>
-      <c r="D128" s="9" t="s">
-        <v>567</v>
-      </c>
-      <c r="E128" s="10" t="s">
-        <v>568</v>
-      </c>
-      <c r="F128" s="9" t="s">
-        <v>569</v>
-      </c>
       <c r="G128" s="10" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="H128" s="9" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="I128" s="10" t="s">
-        <v>569</v>
-      </c>
-      <c r="J128" s="17"/>
-      <c r="K128" s="18">
+        <v>566</v>
+      </c>
+      <c r="J128" s="16"/>
+      <c r="K128" s="17">
         <v>4</v>
       </c>
       <c r="L128" s="9"/>
     </row>
-    <row r="129" ht="24.75" spans="1:12">
+    <row r="129" spans="1:12" ht="24">
       <c r="A129" s="2"/>
       <c r="B129" s="7">
         <f t="shared" si="0"/>
         <v>127</v>
       </c>
       <c r="C129" s="11" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D129" s="12" t="s">
+        <v>567</v>
+      </c>
+      <c r="E129" s="13" t="s">
+        <v>568</v>
+      </c>
+      <c r="F129" s="12" t="s">
+        <v>569</v>
+      </c>
+      <c r="G129" s="13" t="s">
         <v>570</v>
       </c>
-      <c r="E129" s="13" t="s">
+      <c r="H129" s="12" t="s">
         <v>571</v>
       </c>
-      <c r="F129" s="12" t="s">
-        <v>572</v>
-      </c>
-      <c r="G129" s="13" t="s">
-        <v>573</v>
-      </c>
-      <c r="H129" s="12" t="s">
-        <v>574</v>
-      </c>
       <c r="I129" s="13" t="s">
-        <v>573</v>
-      </c>
-      <c r="J129" s="19"/>
-      <c r="K129" s="20">
+        <v>570</v>
+      </c>
+      <c r="J129" s="18"/>
+      <c r="K129" s="19">
         <v>1</v>
       </c>
       <c r="L129" s="12"/>
     </row>
-    <row r="130" ht="15.75" spans="1:12">
+    <row r="130" spans="1:12">
       <c r="A130" s="2"/>
       <c r="B130" s="7">
         <f t="shared" si="0"/>
         <v>128</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D130" s="9" t="s">
+        <v>572</v>
+      </c>
+      <c r="E130" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="F130" s="9" t="s">
+        <v>574</v>
+      </c>
+      <c r="G130" s="10" t="s">
         <v>575</v>
       </c>
-      <c r="E130" s="10" t="s">
-        <v>576</v>
-      </c>
-      <c r="F130" s="9" t="s">
-        <v>577</v>
-      </c>
-      <c r="G130" s="10" t="s">
-        <v>578</v>
-      </c>
       <c r="H130" s="9" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="I130" s="10" t="s">
-        <v>578</v>
-      </c>
-      <c r="J130" s="17"/>
-      <c r="K130" s="18">
+        <v>575</v>
+      </c>
+      <c r="J130" s="16"/>
+      <c r="K130" s="17">
         <v>1</v>
       </c>
       <c r="L130" s="9"/>
     </row>
-    <row r="131" ht="15.75" spans="1:12">
+    <row r="131" spans="1:12">
       <c r="A131" s="2"/>
       <c r="B131" s="7">
         <f t="shared" si="0"/>
         <v>129</v>
       </c>
       <c r="C131" s="11" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D131" s="12" t="s">
+        <v>576</v>
+      </c>
+      <c r="E131" s="13" t="s">
+        <v>577</v>
+      </c>
+      <c r="F131" s="12" t="s">
+        <v>578</v>
+      </c>
+      <c r="G131" s="13" t="s">
         <v>579</v>
       </c>
-      <c r="E131" s="13" t="s">
-        <v>580</v>
-      </c>
-      <c r="F131" s="12" t="s">
-        <v>581</v>
-      </c>
-      <c r="G131" s="13" t="s">
-        <v>582</v>
-      </c>
       <c r="H131" s="12" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="I131" s="13" t="s">
-        <v>582</v>
-      </c>
-      <c r="J131" s="19"/>
-      <c r="K131" s="20">
+        <v>579</v>
+      </c>
+      <c r="J131" s="18"/>
+      <c r="K131" s="19">
         <v>1</v>
       </c>
       <c r="L131" s="12"/>
     </row>
-    <row r="132" ht="15.75" spans="1:12">
+    <row r="132" spans="1:12">
       <c r="A132" s="2"/>
       <c r="B132" s="7">
         <f t="shared" si="0"/>
         <v>130</v>
       </c>
       <c r="C132" s="8" t="s">
+        <v>580</v>
+      </c>
+      <c r="D132" s="9" t="s">
+        <v>581</v>
+      </c>
+      <c r="E132" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="F132" s="9" t="s">
         <v>583</v>
       </c>
-      <c r="D132" s="9" t="s">
+      <c r="G132" s="10" t="s">
         <v>584</v>
       </c>
-      <c r="E132" s="10" t="s">
-        <v>585</v>
-      </c>
-      <c r="F132" s="9" t="s">
-        <v>586</v>
-      </c>
-      <c r="G132" s="10" t="s">
-        <v>587</v>
-      </c>
       <c r="H132" s="9" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="I132" s="10" t="s">
-        <v>587</v>
-      </c>
-      <c r="J132" s="17"/>
-      <c r="K132" s="18">
+        <v>584</v>
+      </c>
+      <c r="J132" s="16"/>
+      <c r="K132" s="17">
         <v>1</v>
       </c>
       <c r="L132" s="9"/>
     </row>
-    <row r="133" ht="24.75" spans="1:12">
+    <row r="133" spans="1:12" ht="24">
       <c r="A133" s="2"/>
       <c r="B133" s="7">
         <f t="shared" si="0"/>
         <v>131</v>
       </c>
       <c r="C133" s="11" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D133" s="12" t="s">
+        <v>585</v>
+      </c>
+      <c r="E133" s="13" t="s">
+        <v>586</v>
+      </c>
+      <c r="F133" s="12" t="s">
+        <v>587</v>
+      </c>
+      <c r="G133" s="13" t="s">
         <v>588</v>
       </c>
-      <c r="E133" s="13" t="s">
+      <c r="H133" s="12" t="s">
         <v>589</v>
       </c>
-      <c r="F133" s="12" t="s">
-        <v>590</v>
-      </c>
-      <c r="G133" s="13" t="s">
-        <v>591</v>
-      </c>
-      <c r="H133" s="12" t="s">
-        <v>592</v>
-      </c>
       <c r="I133" s="13" t="s">
-        <v>591</v>
-      </c>
-      <c r="J133" s="19"/>
-      <c r="K133" s="20">
+        <v>588</v>
+      </c>
+      <c r="J133" s="18"/>
+      <c r="K133" s="19">
         <v>1</v>
       </c>
       <c r="L133" s="12"/>
     </row>
-    <row r="134" ht="15.75" spans="1:12">
+    <row r="134" spans="1:12">
       <c r="A134" s="2"/>
       <c r="B134" s="7">
         <f t="shared" si="0"/>
         <v>132</v>
       </c>
       <c r="C134" s="8" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D134" s="9" t="s">
+        <v>590</v>
+      </c>
+      <c r="E134" s="10" t="s">
+        <v>591</v>
+      </c>
+      <c r="F134" s="9" t="s">
+        <v>592</v>
+      </c>
+      <c r="G134" s="10" t="s">
         <v>593</v>
       </c>
-      <c r="E134" s="10" t="s">
+      <c r="H134" s="9" t="s">
         <v>594</v>
       </c>
-      <c r="F134" s="9" t="s">
-        <v>595</v>
-      </c>
-      <c r="G134" s="10" t="s">
-        <v>596</v>
-      </c>
-      <c r="H134" s="9" t="s">
-        <v>597</v>
-      </c>
       <c r="I134" s="10" t="s">
-        <v>596</v>
-      </c>
-      <c r="J134" s="17"/>
-      <c r="K134" s="18">
+        <v>593</v>
+      </c>
+      <c r="J134" s="16"/>
+      <c r="K134" s="17">
         <v>1</v>
       </c>
       <c r="L134" s="9"/>
     </row>
-    <row r="135" ht="15.75" spans="1:12">
+    <row r="135" spans="1:12" ht="24">
       <c r="A135" s="2"/>
       <c r="B135" s="7">
         <f t="shared" si="0"/>
         <v>133</v>
       </c>
       <c r="C135" s="11" t="s">
+        <v>595</v>
+      </c>
+      <c r="D135" s="12" t="s">
+        <v>596</v>
+      </c>
+      <c r="E135" s="13" t="s">
+        <v>597</v>
+      </c>
+      <c r="F135" s="12" t="s">
         <v>598</v>
       </c>
-      <c r="D135" s="12" t="s">
+      <c r="G135" s="13" t="s">
+        <v>598</v>
+      </c>
+      <c r="H135" s="12" t="s">
         <v>599</v>
       </c>
-      <c r="E135" s="13" t="s">
-        <v>600</v>
-      </c>
-      <c r="F135" s="12" t="s">
-        <v>601</v>
-      </c>
-      <c r="G135" s="13" t="s">
-        <v>601</v>
-      </c>
-      <c r="H135" s="12" t="s">
-        <v>602</v>
-      </c>
       <c r="I135" s="13" t="s">
-        <v>601</v>
-      </c>
-      <c r="J135" s="19"/>
-      <c r="K135" s="20">
+        <v>598</v>
+      </c>
+      <c r="J135" s="18"/>
+      <c r="K135" s="19">
         <v>1</v>
       </c>
       <c r="L135" s="12"/>
     </row>
-    <row r="136" ht="15.75" spans="1:12">
+    <row r="136" spans="1:12">
       <c r="A136" s="2"/>
       <c r="B136" s="7">
         <f t="shared" si="0"/>
         <v>134</v>
       </c>
       <c r="C136" s="8" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D136" s="9" t="s">
+        <v>600</v>
+      </c>
+      <c r="E136" s="10" t="s">
+        <v>601</v>
+      </c>
+      <c r="F136" s="9" t="s">
+        <v>602</v>
+      </c>
+      <c r="G136" s="10" t="s">
         <v>603</v>
       </c>
-      <c r="E136" s="10" t="s">
+      <c r="H136" s="9" t="s">
         <v>604</v>
       </c>
-      <c r="F136" s="9" t="s">
-        <v>605</v>
-      </c>
-      <c r="G136" s="10" t="s">
-        <v>606</v>
-      </c>
-      <c r="H136" s="9" t="s">
-        <v>607</v>
-      </c>
       <c r="I136" s="10" t="s">
-        <v>606</v>
-      </c>
-      <c r="J136" s="17"/>
-      <c r="K136" s="18">
+        <v>603</v>
+      </c>
+      <c r="J136" s="16"/>
+      <c r="K136" s="17">
         <v>1</v>
       </c>
       <c r="L136" s="9"/>
     </row>
-    <row r="137" ht="24.75" spans="1:12">
+    <row r="137" spans="1:12" ht="24">
       <c r="A137" s="2"/>
       <c r="B137" s="7">
         <f t="shared" si="0"/>
         <v>135</v>
       </c>
       <c r="C137" s="11" t="s">
+        <v>605</v>
+      </c>
+      <c r="D137" s="12" t="s">
+        <v>606</v>
+      </c>
+      <c r="E137" s="13" t="s">
+        <v>607</v>
+      </c>
+      <c r="F137" s="12" t="s">
         <v>608</v>
       </c>
-      <c r="D137" s="12" t="s">
+      <c r="G137" s="13" t="s">
         <v>609</v>
       </c>
-      <c r="E137" s="13" t="s">
+      <c r="H137" s="12" t="s">
         <v>610</v>
       </c>
-      <c r="F137" s="12" t="s">
+      <c r="I137" s="13" t="s">
         <v>611</v>
       </c>
-      <c r="G137" s="13" t="s">
-        <v>612</v>
-      </c>
-      <c r="H137" s="12" t="s">
-        <v>613</v>
-      </c>
-      <c r="I137" s="13" t="s">
-        <v>614</v>
-      </c>
-      <c r="J137" s="19"/>
-      <c r="K137" s="20">
+      <c r="J137" s="18"/>
+      <c r="K137" s="19">
         <v>1</v>
       </c>
       <c r="L137" s="12"/>
     </row>
-    <row r="138" ht="24.75" spans="1:12">
+    <row r="138" spans="1:12" ht="24">
       <c r="A138" s="2"/>
       <c r="B138" s="7">
         <f t="shared" si="0"/>
         <v>136</v>
       </c>
       <c r="C138" s="8" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="D138" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="E138" s="10" t="s">
+        <v>613</v>
+      </c>
+      <c r="F138" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="G138" s="10" t="s">
         <v>615</v>
       </c>
-      <c r="E138" s="10" t="s">
+      <c r="H138" s="9" t="s">
         <v>616</v>
       </c>
-      <c r="F138" s="9" t="s">
+      <c r="I138" s="10" t="s">
         <v>617</v>
       </c>
-      <c r="G138" s="10" t="s">
-        <v>618</v>
-      </c>
-      <c r="H138" s="9" t="s">
-        <v>619</v>
-      </c>
-      <c r="I138" s="10" t="s">
-        <v>620</v>
-      </c>
-      <c r="J138" s="17"/>
-      <c r="K138" s="18">
+      <c r="J138" s="16"/>
+      <c r="K138" s="17">
         <v>1</v>
       </c>
       <c r="L138" s="9"/>
     </row>
-    <row r="139" ht="15.75" spans="1:12">
+    <row r="139" spans="1:12">
       <c r="A139" s="2"/>
       <c r="B139" s="7">
         <f t="shared" si="0"/>
         <v>137</v>
       </c>
       <c r="C139" s="11" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="D139" s="12" t="s">
+        <v>618</v>
+      </c>
+      <c r="E139" s="13" t="s">
+        <v>619</v>
+      </c>
+      <c r="F139" s="12" t="s">
+        <v>620</v>
+      </c>
+      <c r="G139" s="13" t="s">
+        <v>620</v>
+      </c>
+      <c r="H139" s="12" t="s">
         <v>621</v>
       </c>
-      <c r="E139" s="13" t="s">
+      <c r="I139" s="13" t="s">
         <v>622</v>
       </c>
-      <c r="F139" s="12" t="s">
-        <v>623</v>
-      </c>
-      <c r="G139" s="13" t="s">
-        <v>623</v>
-      </c>
-      <c r="H139" s="12" t="s">
-        <v>624</v>
-      </c>
-      <c r="I139" s="13" t="s">
-        <v>625</v>
-      </c>
-      <c r="J139" s="19"/>
-      <c r="K139" s="20">
+      <c r="J139" s="18"/>
+      <c r="K139" s="19">
         <v>1</v>
       </c>
       <c r="L139" s="12"/>
     </row>
-    <row r="140" ht="24.75" spans="1:12">
+    <row r="140" spans="1:12" ht="24">
       <c r="A140" s="2"/>
       <c r="B140" s="7">
         <f t="shared" si="0"/>
         <v>138</v>
       </c>
       <c r="C140" s="8" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="D140" s="9" t="s">
+        <v>623</v>
+      </c>
+      <c r="E140" s="10" t="s">
+        <v>624</v>
+      </c>
+      <c r="F140" s="9" t="s">
+        <v>625</v>
+      </c>
+      <c r="G140" s="10" t="s">
         <v>626</v>
       </c>
-      <c r="E140" s="10" t="s">
+      <c r="H140" s="9" t="s">
+        <v>616</v>
+      </c>
+      <c r="I140" s="10" t="s">
         <v>627</v>
       </c>
-      <c r="F140" s="9" t="s">
-        <v>628</v>
-      </c>
-      <c r="G140" s="10" t="s">
-        <v>629</v>
-      </c>
-      <c r="H140" s="9" t="s">
-        <v>619</v>
-      </c>
-      <c r="I140" s="10" t="s">
-        <v>630</v>
-      </c>
-      <c r="J140" s="25"/>
-      <c r="K140" s="18">
+      <c r="J140" s="24"/>
+      <c r="K140" s="17">
         <v>1</v>
       </c>
       <c r="L140" s="9"/>
@@ -7833,128 +7256,128 @@
         <v>139</v>
       </c>
       <c r="C141" s="11" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="D141" s="12" t="s">
+        <v>628</v>
+      </c>
+      <c r="E141" s="13" t="s">
+        <v>629</v>
+      </c>
+      <c r="F141" s="12" t="s">
+        <v>630</v>
+      </c>
+      <c r="G141" s="13" t="s">
         <v>631</v>
-      </c>
-      <c r="E141" s="13" t="s">
-        <v>632</v>
-      </c>
-      <c r="F141" s="12" t="s">
-        <v>633</v>
-      </c>
-      <c r="G141" s="13" t="s">
-        <v>634</v>
       </c>
       <c r="H141" s="12" t="s">
         <v>37</v>
       </c>
       <c r="I141" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="J141" s="18"/>
+      <c r="K141" s="19">
+        <v>1</v>
+      </c>
+      <c r="L141" s="12"/>
+    </row>
+    <row r="142" spans="1:12" ht="48">
+      <c r="B142" s="7">
+        <f t="shared" si="0"/>
+        <v>140</v>
+      </c>
+      <c r="C142" s="11" t="s">
+        <v>633</v>
+      </c>
+      <c r="D142" s="12" t="s">
+        <v>634</v>
+      </c>
+      <c r="E142" s="13" t="s">
         <v>635</v>
       </c>
-      <c r="J141" s="19"/>
-      <c r="K141" s="20">
-        <v>1</v>
-      </c>
-      <c r="L141" s="12"/>
-    </row>
-    <row r="142" ht="48.75" spans="2:12">
-      <c r="B142" s="7">
-        <f t="shared" si="0"/>
-        <v>140</v>
-      </c>
-      <c r="C142" s="11" t="s">
+      <c r="F142" s="12" t="s">
+        <v>634</v>
+      </c>
+      <c r="G142" s="13" t="s">
         <v>636</v>
       </c>
-      <c r="D142" s="12" t="s">
+      <c r="H142" s="12" t="s">
+        <v>634</v>
+      </c>
+      <c r="I142" s="13" t="s">
         <v>637</v>
       </c>
-      <c r="E142" s="13" t="s">
+      <c r="J142" s="25" t="s">
         <v>638</v>
       </c>
-      <c r="F142" s="12" t="s">
-        <v>637</v>
-      </c>
-      <c r="G142" s="13" t="s">
+      <c r="K142" s="19">
+        <v>1</v>
+      </c>
+      <c r="L142" s="12"/>
+    </row>
+    <row r="143" spans="1:12">
+      <c r="B143" s="7">
+        <f t="shared" si="0"/>
+        <v>141</v>
+      </c>
+      <c r="C143" s="11" t="s">
+        <v>633</v>
+      </c>
+      <c r="D143" s="12" t="s">
+        <v>634</v>
+      </c>
+      <c r="E143" s="13" t="s">
         <v>639</v>
       </c>
-      <c r="H142" s="12" t="s">
-        <v>637</v>
-      </c>
-      <c r="I142" s="13" t="s">
+      <c r="F143" s="12" t="s">
+        <v>634</v>
+      </c>
+      <c r="G143" s="13" t="s">
         <v>640</v>
       </c>
-      <c r="J142" s="26" t="s">
+      <c r="H143" s="12" t="s">
+        <v>634</v>
+      </c>
+      <c r="I143" s="13" t="s">
+        <v>634</v>
+      </c>
+      <c r="J143" s="9"/>
+      <c r="K143" s="19">
+        <v>1</v>
+      </c>
+      <c r="L143" s="12"/>
+    </row>
+    <row r="144" spans="1:12">
+      <c r="B144" s="7">
+        <f t="shared" ref="B144" si="2">ROW(B144)-ROW($B$2)</f>
+        <v>142</v>
+      </c>
+      <c r="C144" s="11" t="s">
+        <v>633</v>
+      </c>
+      <c r="D144" s="12" t="s">
+        <v>634</v>
+      </c>
+      <c r="E144" s="13" t="s">
+        <v>639</v>
+      </c>
+      <c r="F144" s="12" t="s">
+        <v>634</v>
+      </c>
+      <c r="G144" s="13" t="s">
         <v>641</v>
       </c>
-      <c r="K142" s="20">
-        <v>1</v>
-      </c>
-      <c r="L142" s="12"/>
-    </row>
-    <row r="143" spans="2:12">
-      <c r="B143" s="7">
-        <f t="shared" si="0"/>
-        <v>141</v>
-      </c>
-      <c r="C143" s="11" t="s">
-        <v>636</v>
-      </c>
-      <c r="D143" s="12" t="s">
-        <v>637</v>
-      </c>
-      <c r="E143" s="13" t="s">
-        <v>642</v>
-      </c>
-      <c r="F143" s="12" t="s">
-        <v>637</v>
-      </c>
-      <c r="G143" s="13" t="s">
-        <v>643</v>
-      </c>
-      <c r="H143" s="12" t="s">
-        <v>637</v>
-      </c>
-      <c r="I143" s="13" t="s">
-        <v>637</v>
-      </c>
-      <c r="J143" s="9"/>
-      <c r="K143" s="20">
-        <v>1</v>
-      </c>
-      <c r="L143" s="12"/>
-    </row>
-    <row r="144" spans="2:12">
-      <c r="B144" s="7">
-        <f t="shared" ref="B144" si="1">ROW(B144)-ROW($B$2)</f>
-        <v>142</v>
-      </c>
-      <c r="C144" s="11" t="s">
-        <v>636</v>
-      </c>
-      <c r="D144" s="12" t="s">
-        <v>637</v>
-      </c>
-      <c r="E144" s="13" t="s">
-        <v>642</v>
-      </c>
-      <c r="F144" s="12" t="s">
-        <v>637</v>
-      </c>
-      <c r="G144" s="13" t="s">
-        <v>644</v>
-      </c>
       <c r="H144" s="12" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="I144" s="13" t="s">
-        <v>637</v>
-      </c>
-      <c r="J144" s="27" t="s">
-        <v>641</v>
-      </c>
-      <c r="K144" s="20">
+        <v>634</v>
+      </c>
+      <c r="J144" s="26" t="s">
+        <v>638</v>
+      </c>
+      <c r="K144" s="19">
         <v>1</v>
       </c>
       <c r="L144" s="12"/>
@@ -7964,11 +7387,10 @@
     <mergeCell ref="I1:L1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="J142" r:id="rId1" display="Aliexpress"/>
-    <hyperlink ref="J144" r:id="rId2" display="Aliexpress"/>
+    <hyperlink ref="J142" r:id="rId1"/>
+    <hyperlink ref="J144" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Design-Files/Tracker-pro-airbnb-v1.1/BOM/Altium_BOM_tracker-pro-airbnb-v1.1.xlsx
+++ b/Design-Files/Tracker-pro-airbnb-v1.1/BOM/Altium_BOM_tracker-pro-airbnb-v1.1.xlsx
@@ -5,21 +5,21 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ashan moten\Downloads\Tracker-pro-airbnb-v1.1\Tracker-pro-airbnb-v1.1\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Iftikhar Ahmed\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="644">
   <si>
     <t>#</t>
   </si>
@@ -1956,8 +1956,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="13">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2046,6 +2046,14 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2258,7 +2266,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2316,15 +2324,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2333,9 +2332,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2346,6 +2342,12 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2654,10 +2656,10 @@
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2"/>
@@ -3785,12 +3787,12 @@
       <c r="L35" s="9"/>
     </row>
     <row r="36" spans="1:12" ht="36">
-      <c r="A36" s="28"/>
-      <c r="B36" s="29">
+      <c r="A36" s="24"/>
+      <c r="B36" s="25">
         <f t="shared" ref="B36" si="1">ROW(B36) - ROW($B$2)</f>
         <v>34</v>
       </c>
-      <c r="C36" s="30" t="s">
+      <c r="C36" s="26" t="s">
         <v>16</v>
       </c>
       <c r="D36" s="9" t="s">
@@ -3811,7 +3813,7 @@
       <c r="I36" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="J36" s="31"/>
+      <c r="J36" s="27"/>
       <c r="K36" s="17">
         <v>1</v>
       </c>
@@ -3859,29 +3861,31 @@
       <c r="C38" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="D38" s="9" t="s">
+      <c r="D38" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="E38" s="10" t="s">
+      <c r="E38" s="28" t="s">
         <v>160</v>
       </c>
-      <c r="F38" s="9" t="s">
+      <c r="F38" s="28" t="s">
         <v>161</v>
       </c>
-      <c r="G38" s="10" t="s">
+      <c r="G38" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="H38" s="9" t="s">
+      <c r="H38" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="I38" s="10" t="s">
+      <c r="I38" s="28" t="s">
         <v>164</v>
       </c>
-      <c r="J38" s="16"/>
-      <c r="K38" s="17">
-        <v>1</v>
-      </c>
-      <c r="L38" s="9"/>
+      <c r="J38" s="28"/>
+      <c r="K38" s="28">
+        <v>1</v>
+      </c>
+      <c r="L38" s="20" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="39" spans="1:12" ht="24">
       <c r="A39" s="2"/>
@@ -4312,7 +4316,7 @@
       </c>
       <c r="L51" s="12"/>
     </row>
-    <row r="52" spans="1:12">
+    <row r="52" spans="1:12" ht="24">
       <c r="A52" s="2"/>
       <c r="B52" s="7">
         <f>ROW(B52)-ROW($B$2)</f>
@@ -4847,26 +4851,26 @@
       <c r="C68" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="D68" s="20" t="s">
+      <c r="D68" s="28" t="s">
         <v>303</v>
       </c>
-      <c r="E68" s="21" t="s">
+      <c r="E68" s="28" t="s">
         <v>304</v>
       </c>
-      <c r="F68" s="20" t="s">
+      <c r="F68" s="28" t="s">
         <v>305</v>
       </c>
-      <c r="G68" s="21" t="s">
+      <c r="G68" s="28" t="s">
         <v>306</v>
       </c>
-      <c r="H68" s="20" t="s">
+      <c r="H68" s="28" t="s">
         <v>307</v>
       </c>
-      <c r="I68" s="21" t="s">
+      <c r="I68" s="28" t="s">
         <v>164</v>
       </c>
-      <c r="J68" s="22"/>
-      <c r="K68" s="23">
+      <c r="J68" s="28"/>
+      <c r="K68" s="28">
         <v>1</v>
       </c>
       <c r="L68" s="20" t="s">
@@ -5377,29 +5381,31 @@
       <c r="C84" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="D84" s="9" t="s">
+      <c r="D84" s="28" t="s">
         <v>369</v>
       </c>
-      <c r="E84" s="10" t="s">
+      <c r="E84" s="28" t="s">
         <v>370</v>
       </c>
-      <c r="F84" s="9" t="s">
+      <c r="F84" s="28" t="s">
         <v>333</v>
       </c>
-      <c r="G84" s="10" t="s">
+      <c r="G84" s="28" t="s">
         <v>371</v>
       </c>
-      <c r="H84" s="9" t="s">
+      <c r="H84" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="I84" s="10" t="s">
+      <c r="I84" s="28" t="s">
         <v>164</v>
       </c>
-      <c r="J84" s="16"/>
-      <c r="K84" s="17">
-        <v>1</v>
-      </c>
-      <c r="L84" s="9"/>
+      <c r="J84" s="28"/>
+      <c r="K84" s="28">
+        <v>1</v>
+      </c>
+      <c r="L84" s="20" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="85" spans="1:12">
       <c r="A85" s="2"/>
@@ -7243,7 +7249,7 @@
       <c r="I140" s="10" t="s">
         <v>627</v>
       </c>
-      <c r="J140" s="24"/>
+      <c r="J140" s="21"/>
       <c r="K140" s="17">
         <v>1</v>
       </c>
@@ -7308,7 +7314,7 @@
       <c r="I142" s="13" t="s">
         <v>637</v>
       </c>
-      <c r="J142" s="25" t="s">
+      <c r="J142" s="22" t="s">
         <v>638</v>
       </c>
       <c r="K142" s="19">
@@ -7374,7 +7380,7 @@
       <c r="I144" s="13" t="s">
         <v>634</v>
       </c>
-      <c r="J144" s="26" t="s">
+      <c r="J144" s="23" t="s">
         <v>638</v>
       </c>
       <c r="K144" s="19">

--- a/Design-Files/Tracker-pro-airbnb-v1.1/BOM/Altium_BOM_tracker-pro-airbnb-v1.1.xlsx
+++ b/Design-Files/Tracker-pro-airbnb-v1.1/BOM/Altium_BOM_tracker-pro-airbnb-v1.1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Iftikhar Ahmed\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Faizan\GitHub\ezlo-ambienttrackerpro-airbnb-hardware\Design-Files\Tracker-pro-airbnb-v1.1\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="645">
   <si>
     <t>#</t>
   </si>
@@ -1951,12 +1951,15 @@
   </si>
   <si>
     <t>VKMD1451K101MV</t>
+  </si>
+  <si>
+    <t>Battery Holder</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="14">
     <font>
       <sz val="11"/>
@@ -2266,7 +2269,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2348,6 +2351,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2632,7 +2638,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L144"/>
+  <dimension ref="A1:L145"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="4.42578125" style="1" customWidth="1"/>
@@ -4316,7 +4322,7 @@
       </c>
       <c r="L51" s="12"/>
     </row>
-    <row r="52" spans="1:12" ht="24">
+    <row r="52" spans="1:12">
       <c r="A52" s="2"/>
       <c r="B52" s="7">
         <f>ROW(B52)-ROW($B$2)</f>
@@ -7354,9 +7360,9 @@
       </c>
       <c r="L143" s="12"/>
     </row>
-    <row r="144" spans="1:12">
+    <row r="144" spans="1:12" ht="15.75" thickBot="1">
       <c r="B144" s="7">
-        <f t="shared" ref="B144" si="2">ROW(B144)-ROW($B$2)</f>
+        <f t="shared" ref="B144:B145" si="2">ROW(B144)-ROW($B$2)</f>
         <v>142</v>
       </c>
       <c r="C144" s="11" t="s">
@@ -7387,6 +7393,40 @@
         <v>1</v>
       </c>
       <c r="L144" s="12"/>
+    </row>
+    <row r="145" spans="2:12" ht="15.75" thickBot="1">
+      <c r="B145" s="7">
+        <f t="shared" si="2"/>
+        <v>143</v>
+      </c>
+      <c r="C145" s="11" t="s">
+        <v>633</v>
+      </c>
+      <c r="D145" s="12" t="s">
+        <v>634</v>
+      </c>
+      <c r="E145" s="13" t="s">
+        <v>644</v>
+      </c>
+      <c r="F145" s="12" t="s">
+        <v>634</v>
+      </c>
+      <c r="G145" s="13" t="s">
+        <v>634</v>
+      </c>
+      <c r="H145" s="12" t="s">
+        <v>634</v>
+      </c>
+      <c r="I145" s="13" t="s">
+        <v>634</v>
+      </c>
+      <c r="J145" s="30" t="s">
+        <v>638</v>
+      </c>
+      <c r="K145" s="19">
+        <v>2</v>
+      </c>
+      <c r="L145" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7395,6 +7435,7 @@
   <hyperlinks>
     <hyperlink ref="J142" r:id="rId1"/>
     <hyperlink ref="J144" r:id="rId2"/>
+    <hyperlink ref="J145" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Design-Files/Tracker-pro-airbnb-v1.1/BOM/Altium_BOM_tracker-pro-airbnb-v1.1.xlsx
+++ b/Design-Files/Tracker-pro-airbnb-v1.1/BOM/Altium_BOM_tracker-pro-airbnb-v1.1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Faizan\GitHub\ezlo-ambienttrackerpro-airbnb-hardware\Design-Files\Tracker-pro-airbnb-v1.1\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\ezlo-ambienttrackerpro-airbnb-hardware\Design-Files\Tracker-pro-airbnb-v1.1\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="645">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="645">
   <si>
     <t>#</t>
   </si>
@@ -1959,7 +1959,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="14">
     <font>
       <sz val="11"/>
@@ -1972,14 +1972,14 @@
       <sz val="10"/>
       <color indexed="13"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1987,27 +1987,27 @@
       <sz val="10"/>
       <color theme="0"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2015,7 +2015,7 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2023,7 +2023,7 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2349,11 +2349,11 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2638,7 +2638,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L145"/>
+  <dimension ref="A1:L146"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="4.42578125" style="1" customWidth="1"/>
@@ -2662,10 +2662,10 @@
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2"/>
@@ -7362,7 +7362,7 @@
     </row>
     <row r="144" spans="1:12" ht="15.75" thickBot="1">
       <c r="B144" s="7">
-        <f t="shared" ref="B144:B145" si="2">ROW(B144)-ROW($B$2)</f>
+        <f t="shared" ref="B144:B146" si="2">ROW(B144)-ROW($B$2)</f>
         <v>142</v>
       </c>
       <c r="C144" s="11" t="s">
@@ -7420,13 +7420,47 @@
       <c r="I145" s="13" t="s">
         <v>634</v>
       </c>
-      <c r="J145" s="30" t="s">
+      <c r="J145" s="29" t="s">
         <v>638</v>
       </c>
       <c r="K145" s="19">
         <v>2</v>
       </c>
       <c r="L145" s="12"/>
+    </row>
+    <row r="146" spans="2:12" ht="15.75" thickBot="1">
+      <c r="B146" s="7">
+        <f t="shared" si="2"/>
+        <v>144</v>
+      </c>
+      <c r="C146" s="11" t="s">
+        <v>633</v>
+      </c>
+      <c r="D146" s="12" t="s">
+        <v>634</v>
+      </c>
+      <c r="E146" s="13" t="s">
+        <v>636</v>
+      </c>
+      <c r="F146" s="12" t="s">
+        <v>634</v>
+      </c>
+      <c r="G146" s="13" t="s">
+        <v>634</v>
+      </c>
+      <c r="H146" s="12" t="s">
+        <v>634</v>
+      </c>
+      <c r="I146" s="13" t="s">
+        <v>634</v>
+      </c>
+      <c r="J146" s="29" t="s">
+        <v>638</v>
+      </c>
+      <c r="K146" s="19">
+        <v>2</v>
+      </c>
+      <c r="L146" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7436,6 +7470,7 @@
     <hyperlink ref="J142" r:id="rId1"/>
     <hyperlink ref="J144" r:id="rId2"/>
     <hyperlink ref="J145" r:id="rId3"/>
+    <hyperlink ref="J146" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Design-Files/Tracker-pro-airbnb-v1.1/BOM/Altium_BOM_tracker-pro-airbnb-v1.1.xlsx
+++ b/Design-Files/Tracker-pro-airbnb-v1.1/BOM/Altium_BOM_tracker-pro-airbnb-v1.1.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="645">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="645">
   <si>
     <t>#</t>
   </si>
@@ -1926,15 +1926,9 @@
     <t>-</t>
   </si>
   <si>
-    <t>3.7V 3000mAh 505080 Polymer Lithium Lipo Rechargeable battery for GPS DVD PAD power bank e-book camera tablet 5*50*80mm</t>
-  </si>
-  <si>
     <t>Battery</t>
   </si>
   <si>
-    <t>3000mAh</t>
-  </si>
-  <si>
     <t>Aliexpress</t>
   </si>
   <si>
@@ -1954,6 +1948,12 @@
   </si>
   <si>
     <t>Battery Holder</t>
+  </si>
+  <si>
+    <t>1-2PCS 3.7V 1000mAh 10440 ICR10440 3A Lithium Rechargeable Battery For Flashlight Camera Shaver Power Torch Remote Li-ion Cell</t>
+  </si>
+  <si>
+    <t>3.7V</t>
   </si>
 </sst>
 </file>
@@ -2269,7 +2269,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2328,9 +2328,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2638,7 +2635,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L146"/>
+  <dimension ref="A1:L145"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="4.42578125" style="1" customWidth="1"/>
@@ -2662,10 +2659,10 @@
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2"/>
@@ -3793,25 +3790,25 @@
       <c r="L35" s="9"/>
     </row>
     <row r="36" spans="1:12" ht="36">
-      <c r="A36" s="24"/>
-      <c r="B36" s="25">
+      <c r="A36" s="23"/>
+      <c r="B36" s="24">
         <f t="shared" ref="B36" si="1">ROW(B36) - ROW($B$2)</f>
         <v>34</v>
       </c>
-      <c r="C36" s="26" t="s">
+      <c r="C36" s="25" t="s">
         <v>16</v>
       </c>
       <c r="D36" s="9" t="s">
         <v>152</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="H36" s="9" t="s">
         <v>107</v>
@@ -3819,7 +3816,7 @@
       <c r="I36" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="J36" s="27"/>
+      <c r="J36" s="26"/>
       <c r="K36" s="17">
         <v>1</v>
       </c>
@@ -3867,26 +3864,26 @@
       <c r="C38" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="D38" s="28" t="s">
+      <c r="D38" s="27" t="s">
         <v>159</v>
       </c>
-      <c r="E38" s="28" t="s">
+      <c r="E38" s="27" t="s">
         <v>160</v>
       </c>
-      <c r="F38" s="28" t="s">
+      <c r="F38" s="27" t="s">
         <v>161</v>
       </c>
-      <c r="G38" s="28" t="s">
+      <c r="G38" s="27" t="s">
         <v>162</v>
       </c>
-      <c r="H38" s="28" t="s">
+      <c r="H38" s="27" t="s">
         <v>163</v>
       </c>
-      <c r="I38" s="28" t="s">
+      <c r="I38" s="27" t="s">
         <v>164</v>
       </c>
-      <c r="J38" s="28"/>
-      <c r="K38" s="28">
+      <c r="J38" s="27"/>
+      <c r="K38" s="27">
         <v>1</v>
       </c>
       <c r="L38" s="20" t="s">
@@ -4857,26 +4854,26 @@
       <c r="C68" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="D68" s="28" t="s">
+      <c r="D68" s="27" t="s">
         <v>303</v>
       </c>
-      <c r="E68" s="28" t="s">
+      <c r="E68" s="27" t="s">
         <v>304</v>
       </c>
-      <c r="F68" s="28" t="s">
+      <c r="F68" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="G68" s="28" t="s">
+      <c r="G68" s="27" t="s">
         <v>306</v>
       </c>
-      <c r="H68" s="28" t="s">
+      <c r="H68" s="27" t="s">
         <v>307</v>
       </c>
-      <c r="I68" s="28" t="s">
+      <c r="I68" s="27" t="s">
         <v>164</v>
       </c>
-      <c r="J68" s="28"/>
-      <c r="K68" s="28">
+      <c r="J68" s="27"/>
+      <c r="K68" s="27">
         <v>1</v>
       </c>
       <c r="L68" s="20" t="s">
@@ -5387,26 +5384,26 @@
       <c r="C84" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="D84" s="28" t="s">
+      <c r="D84" s="27" t="s">
         <v>369</v>
       </c>
-      <c r="E84" s="28" t="s">
+      <c r="E84" s="27" t="s">
         <v>370</v>
       </c>
-      <c r="F84" s="28" t="s">
+      <c r="F84" s="27" t="s">
         <v>333</v>
       </c>
-      <c r="G84" s="28" t="s">
+      <c r="G84" s="27" t="s">
         <v>371</v>
       </c>
-      <c r="H84" s="28" t="s">
+      <c r="H84" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="I84" s="28" t="s">
+      <c r="I84" s="27" t="s">
         <v>164</v>
       </c>
-      <c r="J84" s="28"/>
-      <c r="K84" s="28">
+      <c r="J84" s="27"/>
+      <c r="K84" s="27">
         <v>1</v>
       </c>
       <c r="L84" s="20" t="s">
@@ -7261,7 +7258,7 @@
       </c>
       <c r="L140" s="9"/>
     </row>
-    <row r="141" spans="1:12">
+    <row r="141" spans="1:12" ht="15.75" thickBot="1">
       <c r="A141" s="2"/>
       <c r="B141" s="7">
         <f t="shared" si="0"/>
@@ -7294,7 +7291,7 @@
       </c>
       <c r="L141" s="12"/>
     </row>
-    <row r="142" spans="1:12" ht="48">
+    <row r="142" spans="1:12" ht="48.75" thickBot="1">
       <c r="B142" s="7">
         <f t="shared" si="0"/>
         <v>140</v>
@@ -7306,29 +7303,29 @@
         <v>634</v>
       </c>
       <c r="E142" s="13" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="F142" s="12" t="s">
         <v>634</v>
       </c>
       <c r="G142" s="13" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H142" s="12" t="s">
         <v>634</v>
       </c>
       <c r="I142" s="13" t="s">
-        <v>637</v>
-      </c>
-      <c r="J142" s="22" t="s">
-        <v>638</v>
+        <v>644</v>
+      </c>
+      <c r="J142" s="28" t="s">
+        <v>636</v>
       </c>
       <c r="K142" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L142" s="12"/>
     </row>
-    <row r="143" spans="1:12">
+    <row r="143" spans="1:12" ht="15.75" thickBot="1">
       <c r="B143" s="7">
         <f t="shared" si="0"/>
         <v>141</v>
@@ -7340,13 +7337,13 @@
         <v>634</v>
       </c>
       <c r="E143" s="13" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="F143" s="12" t="s">
         <v>634</v>
       </c>
       <c r="G143" s="13" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="H143" s="12" t="s">
         <v>634</v>
@@ -7362,7 +7359,7 @@
     </row>
     <row r="144" spans="1:12" ht="15.75" thickBot="1">
       <c r="B144" s="7">
-        <f t="shared" ref="B144:B146" si="2">ROW(B144)-ROW($B$2)</f>
+        <f t="shared" ref="B144:B145" si="2">ROW(B144)-ROW($B$2)</f>
         <v>142</v>
       </c>
       <c r="C144" s="11" t="s">
@@ -7372,13 +7369,13 @@
         <v>634</v>
       </c>
       <c r="E144" s="13" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="F144" s="12" t="s">
         <v>634</v>
       </c>
       <c r="G144" s="13" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="H144" s="12" t="s">
         <v>634</v>
@@ -7386,8 +7383,8 @@
       <c r="I144" s="13" t="s">
         <v>634</v>
       </c>
-      <c r="J144" s="23" t="s">
-        <v>638</v>
+      <c r="J144" s="22" t="s">
+        <v>636</v>
       </c>
       <c r="K144" s="19">
         <v>1</v>
@@ -7406,7 +7403,7 @@
         <v>634</v>
       </c>
       <c r="E145" s="13" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="F145" s="12" t="s">
         <v>634</v>
@@ -7420,57 +7417,22 @@
       <c r="I145" s="13" t="s">
         <v>634</v>
       </c>
-      <c r="J145" s="29" t="s">
-        <v>638</v>
+      <c r="J145" s="28" t="s">
+        <v>636</v>
       </c>
       <c r="K145" s="19">
         <v>2</v>
       </c>
       <c r="L145" s="12"/>
-    </row>
-    <row r="146" spans="2:12" ht="15.75" thickBot="1">
-      <c r="B146" s="7">
-        <f t="shared" si="2"/>
-        <v>144</v>
-      </c>
-      <c r="C146" s="11" t="s">
-        <v>633</v>
-      </c>
-      <c r="D146" s="12" t="s">
-        <v>634</v>
-      </c>
-      <c r="E146" s="13" t="s">
-        <v>636</v>
-      </c>
-      <c r="F146" s="12" t="s">
-        <v>634</v>
-      </c>
-      <c r="G146" s="13" t="s">
-        <v>634</v>
-      </c>
-      <c r="H146" s="12" t="s">
-        <v>634</v>
-      </c>
-      <c r="I146" s="13" t="s">
-        <v>634</v>
-      </c>
-      <c r="J146" s="29" t="s">
-        <v>638</v>
-      </c>
-      <c r="K146" s="19">
-        <v>2</v>
-      </c>
-      <c r="L146" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="I1:L1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="J142" r:id="rId1"/>
-    <hyperlink ref="J144" r:id="rId2"/>
-    <hyperlink ref="J145" r:id="rId3"/>
-    <hyperlink ref="J146" r:id="rId4"/>
+    <hyperlink ref="J144" r:id="rId1"/>
+    <hyperlink ref="J145" r:id="rId2"/>
+    <hyperlink ref="J142" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
